--- a/data/Randonnée.xlsx
+++ b/data/Randonnée.xlsx
@@ -16,14 +16,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plus beaux endroits'!$A$1:$D$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Randonnées!$A$1:$P$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sommets!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="391">
   <si>
     <t>Km</t>
   </si>
@@ -136,9 +136,6 @@
     <t>Dolomites</t>
   </si>
   <si>
-    <t>Italie</t>
-  </si>
-  <si>
     <t>Vallon de la Leisse</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>Camp d'Argent, Sospel</t>
   </si>
   <si>
-    <t>GR52 : St Martin Vésubie - Sospel</t>
-  </si>
-  <si>
     <t>Saint Martin Vésubie - Refuge de la Cougourde, par la Cime de Piagu</t>
   </si>
   <si>
@@ -376,9 +370,6 @@
     <t>Alpes Bavaroises</t>
   </si>
   <si>
-    <t>Allemagne</t>
-  </si>
-  <si>
     <t>Norvège</t>
   </si>
   <si>
@@ -496,9 +487,6 @@
     <t>Espagne</t>
   </si>
   <si>
-    <t>Taillefer, Venosc &amp; Emparis</t>
-  </si>
-  <si>
     <t>Taillefer</t>
   </si>
   <si>
@@ -877,9 +865,6 @@
     <t>Aiguille de Chalais et Charmelline</t>
   </si>
   <si>
-    <t>2 jours sous la Grande Sure</t>
-  </si>
-  <si>
     <t>3000 Haut Giffre : Mont Buet</t>
   </si>
   <si>
@@ -1082,6 +1067,135 @@
   </si>
   <si>
     <t>Apo, Magali</t>
+  </si>
+  <si>
+    <t>Avant l'anniv de Yann à Grenoble</t>
+  </si>
+  <si>
+    <t>Rando neige improvisée</t>
+  </si>
+  <si>
+    <t>Entrainement Ecosse</t>
+  </si>
+  <si>
+    <t>Test des nouvelles chaussures</t>
+  </si>
+  <si>
+    <t>Première fois en raquettes</t>
+  </si>
+  <si>
+    <t>Lac des Plagnes au refuge des Tinderets par les chalais de Lens</t>
+  </si>
+  <si>
+    <t>Retour en passant par les chalets d'Ardens</t>
+  </si>
+  <si>
+    <t>Haute Route - Chamonix Zermatt</t>
+  </si>
+  <si>
+    <t>Les Aiguilles d'Arves</t>
+  </si>
+  <si>
+    <t>France, Arves</t>
+  </si>
+  <si>
+    <t>France, Cerces</t>
+  </si>
+  <si>
+    <t>France, Chambeyron</t>
+  </si>
+  <si>
+    <t>France, Ecrins</t>
+  </si>
+  <si>
+    <t>France, Escreins</t>
+  </si>
+  <si>
+    <t>France, Haut Giffre</t>
+  </si>
+  <si>
+    <t>France, Mercantour</t>
+  </si>
+  <si>
+    <t>France, Mont Cenis</t>
+  </si>
+  <si>
+    <t>France, Pelat</t>
+  </si>
+  <si>
+    <t>France, Queyras</t>
+  </si>
+  <si>
+    <t>France, Vanoise</t>
+  </si>
+  <si>
+    <t>France, Mont Blanc</t>
+  </si>
+  <si>
+    <t>France, Vercors</t>
+  </si>
+  <si>
+    <t>France, Beaufortain</t>
+  </si>
+  <si>
+    <t>France, Chartreuse</t>
+  </si>
+  <si>
+    <t>France, Belledone</t>
+  </si>
+  <si>
+    <t>France, Corse</t>
+  </si>
+  <si>
+    <t>France, Pyrénées</t>
+  </si>
+  <si>
+    <t>France, Pilat</t>
+  </si>
+  <si>
+    <t>France, Mont de Vaucluse</t>
+  </si>
+  <si>
+    <t>France, Bornes</t>
+  </si>
+  <si>
+    <t>Traversée des Aravis</t>
+  </si>
+  <si>
+    <t>France, Aravis</t>
+  </si>
+  <si>
+    <t>Punta Basei</t>
+  </si>
+  <si>
+    <t>Vallée d'Aoste</t>
+  </si>
+  <si>
+    <t>Italie, Grand Paradis</t>
+  </si>
+  <si>
+    <t>Italie, Dolomites</t>
+  </si>
+  <si>
+    <t>Allemagne/Autriche</t>
+  </si>
+  <si>
+    <t>La Pointe d'Ardens</t>
+  </si>
+  <si>
+    <t>Prio</t>
+  </si>
+  <si>
+    <t>Chalais &amp; Charminelle</t>
+  </si>
+  <si>
+    <t>Raquettes dans le Chablais</t>
+  </si>
+  <si>
+    <t>Taillefer &amp; Emparis</t>
+  </si>
+  <si>
+    <t>L'Obiou</t>
   </si>
 </sst>
 </file>
@@ -1160,12 +1274,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1212,8 +1320,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1292,10 +1406,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1307,6 +1421,17 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1317,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1338,7 +1463,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1373,6 +1497,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1381,25 +1508,14 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1418,6 +1534,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1434,24 +1561,10 @@
     <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1460,16 +1573,16 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1497,20 +1610,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1862,74 +1991,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="76" customWidth="1"/>
     <col min="3" max="3" width="7.5546875" style="9" customWidth="1"/>
     <col min="4" max="4" width="7.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="82" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="82" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="76" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="76" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.44140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.21875" style="3" customWidth="1"/>
     <col min="11" max="11" width="27.21875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="29.77734375" style="66" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.77734375" style="61" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="45.88671875" style="10" customWidth="1"/>
     <col min="14" max="14" width="29.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23.77734375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="80" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:16" s="74" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="76" t="s">
+      <c r="E1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="81" t="s">
-        <v>263</v>
-      </c>
-      <c r="G1" s="81" t="s">
-        <v>264</v>
-      </c>
-      <c r="H1" s="76" t="s">
-        <v>144</v>
-      </c>
-      <c r="I1" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="77" t="s">
-        <v>48</v>
-      </c>
-      <c r="K1" s="77" t="s">
+      <c r="F1" s="75" t="s">
+        <v>259</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>260</v>
+      </c>
+      <c r="H1" s="70" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="78" t="s">
+      <c r="L1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="79" t="s">
+      <c r="M1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="79" t="s">
+      <c r="N1" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="P1" s="79" t="s">
+      <c r="O1" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="P1" s="73" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1937,7 +2066,7 @@
       <c r="A2" s="2">
         <v>44997</v>
       </c>
-      <c r="B2" s="82">
+      <c r="B2" s="76">
         <v>16.809999999999999</v>
       </c>
       <c r="C2" s="9">
@@ -1949,38 +2078,38 @@
       <c r="E2" s="3">
         <v>0.15972222222222224</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="76">
         <f t="shared" ref="F2:F33" si="0">C2/B2</f>
         <v>58.477096966091615</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="76">
         <f t="shared" ref="G2:G33" si="1">B2+C2/100+D2/300</f>
         <v>29.916666666666668</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" s="66" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="L2" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45010</v>
       </c>
-      <c r="B3" s="82">
+      <c r="B3" s="76">
         <v>39.5</v>
       </c>
       <c r="C3" s="9">
@@ -1992,38 +2121,38 @@
       <c r="E3" s="3">
         <v>0.4375</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="76">
         <f t="shared" si="0"/>
         <v>56.708860759493668</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="76">
         <f t="shared" si="1"/>
         <v>69.36666666666666</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="66" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45011</v>
       </c>
-      <c r="B4" s="82">
+      <c r="B4" s="76">
         <v>12.55</v>
       </c>
       <c r="C4" s="9">
@@ -2035,38 +2164,38 @@
       <c r="E4" s="3">
         <v>0.15972222222222224</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="76">
         <f t="shared" si="0"/>
         <v>42.788844621513945</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="76">
         <f t="shared" si="1"/>
         <v>19.71</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="66" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="L4" s="61" t="s">
+        <v>58</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45017</v>
       </c>
-      <c r="B5" s="82">
+      <c r="B5" s="76">
         <v>17.32</v>
       </c>
       <c r="C5" s="9">
@@ -2078,38 +2207,38 @@
       <c r="E5" s="3">
         <v>0.25</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="76">
         <f t="shared" si="0"/>
         <v>48.152424942263281</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="76">
         <f t="shared" si="1"/>
         <v>28.44</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="66" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="L5" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45038</v>
       </c>
-      <c r="B6" s="82">
+      <c r="B6" s="76">
         <v>15</v>
       </c>
       <c r="C6" s="9">
@@ -2121,35 +2250,35 @@
       <c r="E6" s="3">
         <v>0.25</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="76">
         <f t="shared" si="0"/>
         <v>53.333333333333336</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="76">
         <f t="shared" si="1"/>
         <v>25.666666666666668</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45039</v>
       </c>
-      <c r="B7" s="82">
+      <c r="B7" s="76">
         <v>18.5</v>
       </c>
       <c r="C7" s="9">
@@ -2161,38 +2290,38 @@
       <c r="E7" s="3">
         <v>0.1875</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="76">
         <f t="shared" si="0"/>
         <v>49.567567567567565</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="76">
         <f t="shared" si="1"/>
         <v>30.726666666666667</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="66" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="L7" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45060</v>
       </c>
-      <c r="B8" s="82">
+      <c r="B8" s="76">
         <v>18.02</v>
       </c>
       <c r="C8" s="9">
@@ -2204,38 +2333,38 @@
       <c r="E8" s="3">
         <v>0.1875</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="76">
         <f t="shared" si="0"/>
         <v>54.384017758046618</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="76">
         <f t="shared" si="1"/>
         <v>31.086666666666666</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="66" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="L8" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45073</v>
       </c>
-      <c r="B9" s="82">
+      <c r="B9" s="76">
         <v>30.5</v>
       </c>
       <c r="C9" s="9">
@@ -2247,38 +2376,38 @@
       <c r="E9" s="3">
         <v>0.34722222222222227</v>
       </c>
-      <c r="F9" s="82">
+      <c r="F9" s="76">
         <f t="shared" si="0"/>
         <v>65.704918032786878</v>
       </c>
-      <c r="G9" s="82">
+      <c r="G9" s="76">
         <f t="shared" si="1"/>
         <v>57.22</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="66" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="L9" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45074</v>
       </c>
-      <c r="B10" s="82">
+      <c r="B10" s="76">
         <v>13</v>
       </c>
       <c r="C10" s="9">
@@ -2290,38 +2419,38 @@
       <c r="E10" s="3">
         <v>0.125</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F10" s="76">
         <f t="shared" si="0"/>
         <v>44.846153846153847</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="76">
         <f t="shared" si="1"/>
         <v>20.773333333333333</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="66" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="L10" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45080</v>
       </c>
-      <c r="B11" s="82">
+      <c r="B11" s="76">
         <v>4.5</v>
       </c>
       <c r="C11" s="9">
@@ -2333,698 +2462,698 @@
       <c r="E11" s="3">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F11" s="82">
+      <c r="F11" s="76">
         <f t="shared" si="0"/>
         <v>122.22222222222223</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="76">
         <f t="shared" si="1"/>
         <v>11.833333333333334</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="66" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="L11" s="61" t="s">
+        <v>58</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="33">
+      <c r="A12" s="28">
         <v>45108</v>
       </c>
-      <c r="B12" s="83">
+      <c r="B12" s="77">
         <v>23.3</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="29">
         <v>1393</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="29">
         <v>854</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="30">
         <v>0.29166666666666669</v>
       </c>
-      <c r="F12" s="83">
+      <c r="F12" s="77">
         <f t="shared" si="0"/>
         <v>59.785407725321889</v>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="77">
         <f t="shared" si="1"/>
         <v>40.076666666666668</v>
       </c>
-      <c r="H12" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I12" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="37" t="s">
+      <c r="H12" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O12" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P12" s="36" t="s">
-        <v>132</v>
+      <c r="O12" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P12" s="31" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="33">
+      <c r="A13" s="28">
         <v>45109</v>
       </c>
-      <c r="B13" s="83">
+      <c r="B13" s="77">
         <v>20.3</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="29">
         <v>2319</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="29">
         <v>1355</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="30">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="77">
         <f t="shared" si="0"/>
         <v>114.23645320197043</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="77">
         <f t="shared" si="1"/>
         <v>48.006666666666668</v>
       </c>
-      <c r="H13" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="36" t="s">
+      <c r="H13" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="N13" s="36" t="s">
+      <c r="N13" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O13" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P13" s="36" t="s">
+      <c r="O13" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P13" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="33">
+      <c r="A14" s="28">
         <v>45110</v>
       </c>
-      <c r="B14" s="83">
+      <c r="B14" s="77">
         <v>35.200000000000003</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="29">
         <v>2001</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="29">
         <v>2218</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="30">
         <v>0.38541666666666669</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="77">
         <f t="shared" si="0"/>
         <v>56.846590909090907</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="77">
         <f t="shared" si="1"/>
         <v>62.603333333333339</v>
       </c>
-      <c r="H14" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="L14" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="M14" s="36" t="s">
+      <c r="H14" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="N14" s="36" t="s">
+      <c r="N14" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O14" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P14" s="36"/>
+      <c r="O14" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P14" s="31"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="33">
+      <c r="A15" s="28">
         <v>45111</v>
       </c>
-      <c r="B15" s="83">
+      <c r="B15" s="77">
         <v>32.700000000000003</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="29">
         <v>2086</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="29">
         <v>1741</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="30">
         <v>0.375</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="77">
         <f t="shared" si="0"/>
         <v>63.792048929663601</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="77">
         <f t="shared" si="1"/>
         <v>59.363333333333337</v>
       </c>
-      <c r="H15" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K15" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="M15" s="36" t="s">
+      <c r="H15" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I15" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="N15" s="36" t="s">
+      <c r="N15" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O15" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P15" s="36"/>
+      <c r="O15" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P15" s="31"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="33">
+      <c r="A16" s="28">
         <v>45112</v>
       </c>
-      <c r="B16" s="83">
+      <c r="B16" s="77">
         <v>27.1</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="29">
         <v>1832</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="29">
         <v>2748</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="30">
         <v>0.35416666666666669</v>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="77">
         <f t="shared" si="0"/>
         <v>67.601476014760138</v>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="77">
         <f t="shared" si="1"/>
         <v>54.58</v>
       </c>
-      <c r="H16" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="M16" s="36" t="s">
+      <c r="H16" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="N16" s="36" t="s">
+      <c r="N16" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O16" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P16" s="36" t="s">
+      <c r="O16" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P16" s="31" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="33">
+      <c r="A17" s="28">
         <v>45113</v>
       </c>
-      <c r="B17" s="83">
+      <c r="B17" s="77">
         <v>25.3</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="29">
         <v>2075</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="29">
         <v>1656</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="30">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="77">
         <f t="shared" si="0"/>
         <v>82.015810276679844</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="77">
         <f t="shared" si="1"/>
         <v>51.569999999999993</v>
       </c>
-      <c r="H17" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K17" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="M17" s="36" t="s">
+      <c r="H17" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="N17" s="36" t="s">
+      <c r="N17" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O17" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P17" s="36"/>
+      <c r="O17" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P17" s="31"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="33">
+      <c r="A18" s="28">
         <v>45114</v>
       </c>
-      <c r="B18" s="83">
+      <c r="B18" s="77">
         <v>34.299999999999997</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="29">
         <v>2270</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="29">
         <v>1350</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="30">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F18" s="83">
+      <c r="F18" s="77">
         <f t="shared" si="0"/>
         <v>66.180758017492721</v>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="77">
         <f t="shared" si="1"/>
         <v>61.5</v>
       </c>
-      <c r="H18" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="L18" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="M18" s="36" t="s">
+      <c r="H18" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="N18" s="36" t="s">
+      <c r="N18" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O18" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P18" s="36"/>
+      <c r="O18" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" s="31"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="33">
+      <c r="A19" s="28">
         <v>45115</v>
       </c>
-      <c r="B19" s="83">
-        <v>43</v>
-      </c>
-      <c r="C19" s="34">
+      <c r="B19" s="77">
+        <v>43</v>
+      </c>
+      <c r="C19" s="29">
         <v>1950</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="29">
         <v>1812</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="30">
         <v>0.42708333333333331</v>
       </c>
-      <c r="F19" s="83">
+      <c r="F19" s="77">
         <f t="shared" si="0"/>
         <v>45.348837209302324</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="77">
         <f t="shared" si="1"/>
         <v>68.540000000000006</v>
       </c>
-      <c r="H19" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K19" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="L19" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="M19" s="36" t="s">
+      <c r="H19" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="N19" s="36" t="s">
+      <c r="N19" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O19" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P19" s="36" t="s">
+      <c r="O19" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P19" s="31" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="33">
+      <c r="A20" s="28">
         <v>45116</v>
       </c>
-      <c r="B20" s="83">
+      <c r="B20" s="77">
         <v>32.200000000000003</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="29">
         <v>1213</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="29">
         <v>2440</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="30">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F20" s="83">
+      <c r="F20" s="77">
         <f t="shared" si="0"/>
         <v>37.670807453416145</v>
       </c>
-      <c r="G20" s="83">
+      <c r="G20" s="77">
         <f t="shared" si="1"/>
         <v>52.463333333333338</v>
       </c>
-      <c r="H20" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="L20" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="M20" s="36" t="s">
+      <c r="H20" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="N20" s="36" t="s">
+      <c r="N20" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O20" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="P20" s="36"/>
+      <c r="O20" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P20" s="31"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="25">
+      <c r="A21" s="87">
         <v>45123</v>
       </c>
-      <c r="B21" s="84">
+      <c r="B21" s="88">
         <v>23</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="89">
         <v>1183</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="89">
         <v>1183</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="46">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F21" s="84">
+      <c r="F21" s="88">
         <f t="shared" si="0"/>
         <v>51.434782608695649</v>
       </c>
-      <c r="G21" s="84">
+      <c r="G21" s="88">
         <f t="shared" si="1"/>
         <v>38.773333333333333</v>
       </c>
-      <c r="H21" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K21" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="L21" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="M21" s="28" t="s">
+      <c r="H21" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="M21" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="N21" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="O21" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="P21" s="28"/>
+      <c r="N21" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="O21" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="P21" s="41"/>
     </row>
     <row r="22" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="25">
+      <c r="A22" s="87">
         <v>45124</v>
       </c>
-      <c r="B22" s="84">
+      <c r="B22" s="88">
         <v>21.15</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="89">
         <v>1085</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="89">
         <v>1245</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="46">
         <v>0.34722222222222227</v>
       </c>
-      <c r="F22" s="84">
+      <c r="F22" s="88">
         <f t="shared" si="0"/>
         <v>51.300236406619391</v>
       </c>
-      <c r="G22" s="84">
+      <c r="G22" s="88">
         <f t="shared" si="1"/>
         <v>36.15</v>
       </c>
-      <c r="H22" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="J22" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K22" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="M22" s="28" t="s">
+      <c r="H22" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="M22" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="N22" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="O22" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="P22" s="28"/>
+      <c r="N22" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="O22" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="P22" s="41"/>
     </row>
     <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="25">
+      <c r="A23" s="87">
         <v>45125</v>
       </c>
-      <c r="B23" s="84">
+      <c r="B23" s="88">
         <v>35.22</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="89">
         <v>2140</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="89">
         <v>2140</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="46">
         <v>0.39583333333333331</v>
       </c>
-      <c r="F23" s="84">
+      <c r="F23" s="88">
         <f t="shared" si="0"/>
         <v>60.760931289040322</v>
       </c>
-      <c r="G23" s="84">
+      <c r="G23" s="88">
         <f t="shared" si="1"/>
         <v>63.75333333333333</v>
       </c>
-      <c r="H23" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K23" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="L23" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="28" t="s">
+      <c r="H23" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="N23" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="O23" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="P23" s="28" t="s">
-        <v>152</v>
+      <c r="N23" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="O23" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="P23" s="41" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="25">
+      <c r="A24" s="87">
         <v>45127</v>
       </c>
-      <c r="B24" s="84">
+      <c r="B24" s="88">
         <v>15.4</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="89">
         <v>677</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="89">
         <v>677</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="46">
         <v>0.22916666666666666</v>
       </c>
-      <c r="F24" s="84">
+      <c r="F24" s="88">
         <f t="shared" si="0"/>
         <v>43.961038961038959</v>
       </c>
-      <c r="G24" s="84">
+      <c r="G24" s="88">
         <f t="shared" si="1"/>
         <v>24.426666666666669</v>
       </c>
-      <c r="H24" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K24" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="L24" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="M24" s="28" t="s">
+      <c r="H24" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="O24" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="P24" s="28"/>
+      <c r="N24" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="O24" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="P24" s="41"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45150</v>
       </c>
-      <c r="B25" s="82">
+      <c r="B25" s="76">
         <v>18.54</v>
       </c>
       <c r="C25" s="9">
@@ -3036,41 +3165,41 @@
       <c r="E25" s="3">
         <v>0.25</v>
       </c>
-      <c r="F25" s="82">
+      <c r="F25" s="76">
         <f t="shared" si="0"/>
         <v>40.99244875943905</v>
       </c>
-      <c r="G25" s="82">
+      <c r="G25" s="76">
         <f t="shared" si="1"/>
         <v>28.673333333333332</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L25" s="66" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="L25" s="61" t="s">
+        <v>58</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45199</v>
       </c>
-      <c r="B26" s="82">
+      <c r="B26" s="76">
         <v>8.85</v>
       </c>
       <c r="C26" s="9">
@@ -3082,242 +3211,242 @@
       <c r="E26" s="3">
         <v>0.10416666666666667</v>
       </c>
-      <c r="F26" s="82">
+      <c r="F26" s="76">
         <f t="shared" si="0"/>
         <v>61.807909604519779</v>
       </c>
-      <c r="G26" s="82">
+      <c r="G26" s="76">
         <f t="shared" si="1"/>
         <v>16.143333333333334</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L26" s="66" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="L26" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="O26" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+      <c r="A27" s="16">
         <v>45205</v>
       </c>
-      <c r="B27" s="85">
+      <c r="B27" s="78">
         <v>14.5</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <v>1900</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="17">
         <v>750</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="18">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F27" s="85">
+      <c r="F27" s="78">
         <f t="shared" si="0"/>
         <v>131.0344827586207</v>
       </c>
-      <c r="G27" s="85">
+      <c r="G27" s="78">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="H27" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="K27" s="19" t="s">
+      <c r="H27" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L27" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="L27" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="M27" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="N27" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O27" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P27" s="20" t="s">
-        <v>131</v>
+      <c r="M27" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="N27" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="O27" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="P27" s="19" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="16">
         <v>45206</v>
       </c>
-      <c r="B28" s="85">
+      <c r="B28" s="78">
         <v>26.5</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <v>2450</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="17">
         <v>2475</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="18">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F28" s="85">
+      <c r="F28" s="78">
         <f t="shared" si="0"/>
         <v>92.452830188679243</v>
       </c>
-      <c r="G28" s="85">
+      <c r="G28" s="78">
         <f t="shared" si="1"/>
         <v>59.25</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="K28" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" s="68" t="s">
-        <v>76</v>
-      </c>
-      <c r="M28" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="N28" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P28" s="20" t="s">
-        <v>151</v>
+      <c r="H28" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L28" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="N28" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="P28" s="19" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="17">
+      <c r="A29" s="16">
         <v>45207</v>
       </c>
-      <c r="B29" s="85">
+      <c r="B29" s="78">
         <v>27</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <v>1700</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="17">
         <v>2300</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="18">
         <v>0.39583333333333331</v>
       </c>
-      <c r="F29" s="85">
+      <c r="F29" s="78">
         <f t="shared" si="0"/>
         <v>62.962962962962962</v>
       </c>
-      <c r="G29" s="85">
+      <c r="G29" s="78">
         <f t="shared" si="1"/>
         <v>51.666666666666664</v>
       </c>
-      <c r="H29" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="L29" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="M29" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="N29" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O29" s="20" t="s">
+      <c r="H29" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L29" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="P29" s="20"/>
+      <c r="N29" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="O29" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="P29" s="19"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
+      <c r="A30" s="16">
         <v>45208</v>
       </c>
-      <c r="B30" s="85">
+      <c r="B30" s="78">
         <v>22</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="17">
         <v>725</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="17">
         <v>1975</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="18">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F30" s="85">
+      <c r="F30" s="78">
         <f t="shared" si="0"/>
         <v>32.954545454545453</v>
       </c>
-      <c r="G30" s="85">
+      <c r="G30" s="78">
         <f t="shared" si="1"/>
         <v>35.833333333333336</v>
       </c>
-      <c r="H30" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="L30" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="M30" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="N30" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O30" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P30" s="20"/>
+      <c r="H30" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="O30" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="P30" s="19"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>45220</v>
       </c>
-      <c r="B31" s="82">
+      <c r="B31" s="76">
         <v>12.5</v>
       </c>
       <c r="C31" s="9">
@@ -3329,41 +3458,41 @@
       <c r="E31" s="3">
         <v>0.14583333333333334</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="76">
         <f t="shared" si="0"/>
         <v>61.2</v>
       </c>
-      <c r="G31" s="82">
+      <c r="G31" s="76">
         <f t="shared" si="1"/>
         <v>22.7</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L31" s="66" t="s">
-        <v>72</v>
+        <v>98</v>
+      </c>
+      <c r="L31" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>45227</v>
       </c>
-      <c r="B32" s="82">
+      <c r="B32" s="76">
         <v>8.5</v>
       </c>
       <c r="C32" s="9">
@@ -3375,41 +3504,41 @@
       <c r="E32" s="3">
         <v>0.14583333333333334</v>
       </c>
-      <c r="F32" s="82">
+      <c r="F32" s="76">
         <f t="shared" si="0"/>
         <v>38.235294117647058</v>
       </c>
-      <c r="G32" s="82">
+      <c r="G32" s="76">
         <f t="shared" si="1"/>
         <v>12.75</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K32" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L32" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="M32" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="L32" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="O32" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>45235</v>
       </c>
-      <c r="B33" s="82">
+      <c r="B33" s="76">
         <v>15</v>
       </c>
       <c r="C33" s="9">
@@ -3421,41 +3550,41 @@
       <c r="E33" s="3">
         <v>0.11805555555555557</v>
       </c>
-      <c r="F33" s="82">
+      <c r="F33" s="76">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="G33" s="82">
+      <c r="G33" s="76">
         <f t="shared" si="1"/>
         <v>23.400000000000002</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K33" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="L33" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="L33" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="M33" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="M33" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="O33" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>45339</v>
       </c>
-      <c r="B34" s="82">
+      <c r="B34" s="76">
         <v>8.5</v>
       </c>
       <c r="C34" s="9">
@@ -3467,41 +3596,41 @@
       <c r="E34" s="3">
         <v>9.7222222222222224E-2</v>
       </c>
-      <c r="F34" s="82">
-        <f t="shared" ref="F34:F71" si="2">C34/B34</f>
+      <c r="F34" s="76">
+        <f t="shared" ref="F34:F72" si="2">C34/B34</f>
         <v>63.529411764705884</v>
       </c>
-      <c r="G34" s="82">
-        <f t="shared" ref="G34:G71" si="3">B34+C34/100+D34/300</f>
+      <c r="G34" s="76">
+        <f t="shared" ref="G34:G72" si="3">B34+C34/100+D34/300</f>
         <v>15.700000000000001</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L34" s="66" t="s">
-        <v>108</v>
+        <v>48</v>
+      </c>
+      <c r="L34" s="61" t="s">
+        <v>106</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O34" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>45347</v>
       </c>
-      <c r="B35" s="82">
+      <c r="B35" s="76">
         <v>8</v>
       </c>
       <c r="C35" s="9">
@@ -3513,44 +3642,44 @@
       <c r="E35" s="3">
         <v>0.16666666666666666</v>
       </c>
-      <c r="F35" s="82">
+      <c r="F35" s="76">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="G35" s="82">
+      <c r="G35" s="76">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L35" s="66" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="L35" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>45374</v>
       </c>
-      <c r="B36" s="82">
+      <c r="B36" s="76">
         <v>23</v>
       </c>
       <c r="C36" s="9">
@@ -3562,41 +3691,41 @@
       <c r="E36" s="3">
         <v>0.25</v>
       </c>
-      <c r="F36" s="82">
+      <c r="F36" s="76">
         <f t="shared" si="2"/>
         <v>34.782608695652172</v>
       </c>
-      <c r="G36" s="82">
+      <c r="G36" s="76">
         <f t="shared" si="3"/>
         <v>33.666666666666664</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L36" s="66" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="L36" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O36" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>45388</v>
       </c>
-      <c r="B37" s="82">
+      <c r="B37" s="76">
         <v>15</v>
       </c>
       <c r="C37" s="9">
@@ -3608,853 +3737,853 @@
       <c r="E37" s="3">
         <v>0.20833333333333334</v>
       </c>
-      <c r="F37" s="82">
+      <c r="F37" s="76">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="G37" s="82">
+      <c r="G37" s="76">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L37" s="66" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="L37" s="61" t="s">
+        <v>59</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+      <c r="A38" s="20">
         <v>45416</v>
       </c>
-      <c r="B38" s="86">
+      <c r="B38" s="79">
         <v>28</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="21">
         <v>1450</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>1100</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="22">
         <v>0.375</v>
       </c>
-      <c r="F38" s="86">
+      <c r="F38" s="79">
         <f t="shared" si="2"/>
         <v>51.785714285714285</v>
       </c>
-      <c r="G38" s="86">
+      <c r="G38" s="79">
         <f t="shared" si="3"/>
         <v>46.166666666666664</v>
       </c>
-      <c r="H38" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="K38" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="L38" s="69" t="s">
+      <c r="H38" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K38" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="L38" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="M38" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="M38" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="N38" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="O38" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="P38" s="24" t="s">
-        <v>142</v>
+      <c r="N38" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="O38" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="P38" s="23" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="21">
+      <c r="A39" s="20">
         <v>45417</v>
       </c>
-      <c r="B39" s="86">
+      <c r="B39" s="79">
         <v>27</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="21">
         <v>800</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>900</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="22">
         <v>0.375</v>
       </c>
-      <c r="F39" s="86">
+      <c r="F39" s="79">
         <f t="shared" si="2"/>
         <v>29.62962962962963</v>
       </c>
-      <c r="G39" s="86">
+      <c r="G39" s="79">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="H39" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="J39" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="K39" s="23" t="s">
+      <c r="H39" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="L39" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="69" t="s">
+      <c r="M39" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="M39" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="N39" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="O39" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="P39" s="24"/>
+      <c r="N39" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="O39" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="P39" s="23"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="21">
+      <c r="A40" s="20">
         <v>45418</v>
       </c>
-      <c r="B40" s="86">
+      <c r="B40" s="79">
         <v>30</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="21">
         <v>1250</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>1500</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="22">
         <v>0.375</v>
       </c>
-      <c r="F40" s="86">
+      <c r="F40" s="79">
         <f t="shared" si="2"/>
         <v>41.666666666666664</v>
       </c>
-      <c r="G40" s="86">
+      <c r="G40" s="79">
         <f t="shared" si="3"/>
         <v>47.5</v>
       </c>
-      <c r="H40" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="K40" s="23" t="s">
+      <c r="H40" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="L40" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="L40" s="69" t="s">
+      <c r="M40" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="M40" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="N40" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="O40" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="P40" s="24"/>
+      <c r="N40" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="O40" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="P40" s="23"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" s="29">
+      <c r="A41" s="24">
         <v>45420</v>
       </c>
-      <c r="B41" s="87">
+      <c r="B41" s="80">
         <v>22</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="25">
         <v>950</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="25">
         <v>750</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="26">
         <v>0.375</v>
       </c>
-      <c r="F41" s="87">
+      <c r="F41" s="80">
         <f t="shared" si="2"/>
         <v>43.18181818181818</v>
       </c>
-      <c r="G41" s="87">
+      <c r="G41" s="80">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="H41" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="I41" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J41" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K41" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="L41" s="70" t="s">
-        <v>138</v>
-      </c>
-      <c r="M41" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="N41" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="O41" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P41" s="32" t="s">
+      <c r="H41" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L41" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="M41" s="27" t="s">
         <v>143</v>
       </c>
+      <c r="N41" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="O41" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="P41" s="27" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="29">
+      <c r="A42" s="24">
         <v>45421</v>
       </c>
-      <c r="B42" s="87">
+      <c r="B42" s="80">
         <v>26</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="25">
         <v>1250</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="25">
         <v>900</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="26">
         <v>0.5</v>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="80">
         <f t="shared" si="2"/>
         <v>48.07692307692308</v>
       </c>
-      <c r="G42" s="87">
+      <c r="G42" s="80">
         <f t="shared" si="3"/>
         <v>41.5</v>
       </c>
-      <c r="H42" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J42" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K42" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="L42" s="70" t="s">
-        <v>139</v>
-      </c>
-      <c r="M42" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="N42" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="O42" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P42" s="32"/>
+      <c r="H42" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K42" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L42" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="M42" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="N42" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="O42" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="P42" s="27"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="29">
+      <c r="A43" s="24">
         <v>45422</v>
       </c>
-      <c r="B43" s="87">
+      <c r="B43" s="80">
         <v>22</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="25">
         <v>800</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="25">
         <v>1100</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="26">
         <v>0.40625</v>
       </c>
-      <c r="F43" s="87">
+      <c r="F43" s="80">
         <f t="shared" si="2"/>
         <v>36.363636363636367</v>
       </c>
-      <c r="G43" s="87">
+      <c r="G43" s="80">
         <f t="shared" si="3"/>
         <v>33.666666666666664</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J43" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K43" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L43" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="M43" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="I43" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J43" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K43" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="L43" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="M43" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="N43" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="O43" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P43" s="32"/>
+      <c r="N43" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="O43" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="P43" s="27"/>
     </row>
     <row r="44" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="29">
+      <c r="A44" s="24">
         <v>45423</v>
       </c>
-      <c r="B44" s="87">
+      <c r="B44" s="80">
         <v>21</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="25">
         <v>1300</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="25">
         <v>1150</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="26">
         <v>0.38541666666666669</v>
       </c>
-      <c r="F44" s="87">
+      <c r="F44" s="80">
         <f t="shared" si="2"/>
         <v>61.904761904761905</v>
       </c>
-      <c r="G44" s="87">
+      <c r="G44" s="80">
         <f t="shared" si="3"/>
         <v>37.833333333333336</v>
       </c>
-      <c r="H44" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="I44" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J44" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K44" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="L44" s="70" t="s">
-        <v>141</v>
-      </c>
-      <c r="M44" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="N44" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="O44" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P44" s="32"/>
+      <c r="H44" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K44" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L44" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="M44" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="N44" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="O44" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="P44" s="27"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="29">
+      <c r="A45" s="24">
         <v>45424</v>
       </c>
-      <c r="B45" s="87">
+      <c r="B45" s="80">
         <v>7</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="25">
         <v>10</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="25">
         <v>300</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="26">
         <v>7.2916666666666671E-2</v>
       </c>
-      <c r="F45" s="87">
+      <c r="F45" s="80">
         <f t="shared" si="2"/>
         <v>1.4285714285714286</v>
       </c>
-      <c r="G45" s="87">
+      <c r="G45" s="80">
         <f t="shared" si="3"/>
         <v>8.1</v>
       </c>
-      <c r="H45" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="I45" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J45" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K45" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="L45" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="M45" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="N45" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="O45" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P45" s="32"/>
+      <c r="H45" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I45" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K45" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L45" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="M45" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="N45" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="O45" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="P45" s="27"/>
     </row>
     <row r="46" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="38">
+      <c r="A46" s="33">
         <v>45446</v>
       </c>
-      <c r="B46" s="88">
+      <c r="B46" s="81">
         <v>26.7</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="34">
         <v>2200</v>
       </c>
-      <c r="D46" s="39">
+      <c r="D46" s="34">
         <v>1250</v>
       </c>
-      <c r="E46" s="40">
+      <c r="E46" s="35">
         <v>0.34375</v>
       </c>
-      <c r="F46" s="88">
+      <c r="F46" s="81">
         <f t="shared" si="2"/>
         <v>82.397003745318358</v>
       </c>
-      <c r="G46" s="88">
+      <c r="G46" s="81">
         <f t="shared" si="3"/>
         <v>52.866666666666667</v>
       </c>
-      <c r="H46" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="I46" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="J46" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="K46" s="40" t="s">
+      <c r="H46" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="I46" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="J46" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="K46" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="L46" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="L46" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="M46" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="N46" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="O46" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="P46" s="41" t="s">
-        <v>198</v>
+      <c r="M46" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="N46" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="O46" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="P46" s="36" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="38">
+      <c r="A47" s="33">
         <v>45447</v>
       </c>
-      <c r="B47" s="88">
+      <c r="B47" s="81">
         <v>40.4</v>
       </c>
-      <c r="C47" s="39">
+      <c r="C47" s="34">
         <v>2590</v>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="34">
         <v>2710</v>
       </c>
-      <c r="E47" s="40">
+      <c r="E47" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="F47" s="88">
+      <c r="F47" s="81">
         <f t="shared" si="2"/>
         <v>64.10891089108911</v>
       </c>
-      <c r="G47" s="88">
+      <c r="G47" s="81">
         <f t="shared" si="3"/>
         <v>75.333333333333329</v>
       </c>
-      <c r="H47" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="I47" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="J47" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="K47" s="40" t="s">
-        <v>159</v>
-      </c>
-      <c r="L47" s="71"/>
-      <c r="M47" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="N47" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="O47" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="P47" s="41" t="s">
+      <c r="H47" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="I47" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="J47" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="K47" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="L47" s="65"/>
+      <c r="M47" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="N47" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="O47" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="P47" s="36" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="38">
+      <c r="A48" s="33">
         <v>45448</v>
       </c>
-      <c r="B48" s="88">
+      <c r="B48" s="81">
         <v>32.200000000000003</v>
       </c>
-      <c r="C48" s="39">
+      <c r="C48" s="34">
         <v>2050</v>
       </c>
-      <c r="D48" s="39">
+      <c r="D48" s="34">
         <v>2370</v>
       </c>
-      <c r="E48" s="40">
+      <c r="E48" s="35">
         <v>0.51041666666666663</v>
       </c>
-      <c r="F48" s="88">
+      <c r="F48" s="81">
         <f t="shared" si="2"/>
         <v>63.66459627329192</v>
       </c>
-      <c r="G48" s="88">
+      <c r="G48" s="81">
         <f t="shared" si="3"/>
         <v>60.6</v>
       </c>
-      <c r="H48" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="I48" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="J48" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="K48" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="L48" s="71" t="s">
-        <v>163</v>
-      </c>
-      <c r="M48" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="N48" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="O48" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="P48" s="41"/>
+      <c r="H48" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="I48" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="K48" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="L48" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="M48" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="N48" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="O48" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="P48" s="36"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="38">
+      <c r="A49" s="33">
         <v>45449</v>
       </c>
-      <c r="B49" s="88">
+      <c r="B49" s="81">
         <v>33.799999999999997</v>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="34">
         <v>1700</v>
       </c>
-      <c r="D49" s="39">
+      <c r="D49" s="34">
         <v>1290</v>
       </c>
-      <c r="E49" s="40">
+      <c r="E49" s="35">
         <v>0.48958333333333331</v>
       </c>
-      <c r="F49" s="88">
+      <c r="F49" s="81">
         <f t="shared" si="2"/>
         <v>50.295857988165686</v>
       </c>
-      <c r="G49" s="88">
+      <c r="G49" s="81">
         <f t="shared" si="3"/>
         <v>55.099999999999994</v>
       </c>
-      <c r="H49" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="I49" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="J49" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="K49" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L49" s="71" t="s">
+      <c r="H49" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="I49" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="J49" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="K49" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="L49" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="M49" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="N49" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="O49" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="P49" s="41" t="s">
-        <v>170</v>
+      <c r="M49" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="N49" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="O49" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="P49" s="36" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="44">
+      <c r="A50" s="39">
         <v>45535</v>
       </c>
-      <c r="B50" s="89">
+      <c r="B50" s="82">
         <v>23.5</v>
       </c>
-      <c r="C50" s="45">
+      <c r="C50" s="40">
         <v>1500</v>
       </c>
-      <c r="D50" s="45">
+      <c r="D50" s="40">
         <v>1350</v>
       </c>
-      <c r="E50" s="42">
+      <c r="E50" s="37">
         <v>0.51041666666666663</v>
       </c>
-      <c r="F50" s="89">
+      <c r="F50" s="82">
         <f t="shared" si="2"/>
         <v>63.829787234042556</v>
       </c>
-      <c r="G50" s="89">
+      <c r="G50" s="82">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="H50" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="I50" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="J50" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="K50" s="42" t="s">
+      <c r="H50" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="I50" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="K50" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="L50" s="66" t="s">
+        <v>169</v>
+      </c>
+      <c r="M50" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="L50" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="M50" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="N50" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="O50" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="P50" s="43" t="s">
-        <v>199</v>
+      <c r="N50" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="O50" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="P50" s="38" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="44">
+      <c r="A51" s="39">
         <v>45536</v>
       </c>
-      <c r="B51" s="89">
+      <c r="B51" s="82">
         <v>20</v>
       </c>
-      <c r="C51" s="45">
+      <c r="C51" s="40">
         <v>1250</v>
       </c>
-      <c r="D51" s="45">
+      <c r="D51" s="40">
         <v>1200</v>
       </c>
-      <c r="E51" s="42">
+      <c r="E51" s="37">
         <v>0.35069444444444442</v>
       </c>
-      <c r="F51" s="89">
+      <c r="F51" s="82">
         <f t="shared" si="2"/>
         <v>62.5</v>
       </c>
-      <c r="G51" s="89">
+      <c r="G51" s="82">
         <f t="shared" si="3"/>
         <v>36.5</v>
       </c>
-      <c r="H51" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="I51" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="J51" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="K51" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="L51" s="72" t="s">
-        <v>174</v>
-      </c>
-      <c r="M51" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="N51" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="O51" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="P51" s="43"/>
+      <c r="H51" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="I51" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="J51" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="K51" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="L51" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="M51" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="N51" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="O51" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="P51" s="38"/>
     </row>
     <row r="52" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="44">
+      <c r="A52" s="39">
         <v>45537</v>
       </c>
-      <c r="B52" s="89">
+      <c r="B52" s="82">
         <v>6.5</v>
       </c>
-      <c r="C52" s="45">
+      <c r="C52" s="40">
         <v>0</v>
       </c>
-      <c r="D52" s="45">
+      <c r="D52" s="40">
         <v>250</v>
       </c>
-      <c r="E52" s="42">
+      <c r="E52" s="37">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F52" s="89">
+      <c r="F52" s="82">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G52" s="89">
+      <c r="G52" s="82">
         <f t="shared" si="3"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="H52" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="I52" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="J52" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="K52" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="L52" s="72" t="s">
-        <v>172</v>
-      </c>
-      <c r="M52" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="N52" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="O52" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="P52" s="43"/>
-    </row>
-    <row r="53" spans="1:16" s="50" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="47">
+      <c r="H52" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="K52" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="L52" s="66" t="s">
+        <v>168</v>
+      </c>
+      <c r="M52" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="N52" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="O52" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="P52" s="38"/>
+    </row>
+    <row r="53" spans="1:16" s="45" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="42">
         <v>45540</v>
       </c>
-      <c r="B53" s="90">
+      <c r="B53" s="83">
         <v>65.5</v>
       </c>
-      <c r="C53" s="48">
+      <c r="C53" s="43">
         <v>1850</v>
       </c>
-      <c r="D53" s="48">
+      <c r="D53" s="43">
         <v>1700</v>
       </c>
-      <c r="E53" s="49">
+      <c r="E53" s="44">
         <v>0.59375</v>
       </c>
-      <c r="F53" s="90">
+      <c r="F53" s="83">
         <f t="shared" si="2"/>
         <v>28.244274809160306</v>
       </c>
-      <c r="G53" s="90">
+      <c r="G53" s="83">
         <f t="shared" si="3"/>
         <v>89.666666666666671</v>
       </c>
-      <c r="H53" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="I53" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="J53" s="49" t="s">
+      <c r="H53" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="I53" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J53" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K53" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="L53" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="M53" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="N53" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="O53" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="P53" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="K53" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="L53" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="M53" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="N53" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="O53" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="P53" s="46" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="47">
+      <c r="A54" s="42">
         <v>45542</v>
       </c>
-      <c r="B54" s="82">
+      <c r="B54" s="76">
         <v>18.5</v>
       </c>
       <c r="C54" s="9">
@@ -4463,602 +4592,605 @@
       <c r="D54" s="9">
         <v>513</v>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="46">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F54" s="82">
+      <c r="F54" s="76">
         <f t="shared" si="2"/>
         <v>27.72972972972973</v>
       </c>
-      <c r="G54" s="82">
+      <c r="G54" s="76">
         <f t="shared" si="3"/>
         <v>25.34</v>
       </c>
-      <c r="H54" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="I54" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="J54" s="49" t="s">
-        <v>179</v>
+      <c r="H54" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="I54" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J54" s="44" t="s">
+        <v>175</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="L54" s="66" t="s">
-        <v>184</v>
+        <v>189</v>
+      </c>
+      <c r="L54" s="61" t="s">
+        <v>180</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>349</v>
       </c>
       <c r="O54" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="52">
+      <c r="A55" s="47">
         <v>45556</v>
       </c>
-      <c r="B55" s="91">
+      <c r="B55" s="84">
         <v>35.5</v>
       </c>
-      <c r="C55" s="53">
+      <c r="C55" s="48">
         <v>1770</v>
       </c>
-      <c r="D55" s="53">
+      <c r="D55" s="48">
         <v>680</v>
       </c>
-      <c r="E55" s="54">
+      <c r="E55" s="49">
         <v>0.4375</v>
       </c>
-      <c r="F55" s="91">
+      <c r="F55" s="84">
         <f t="shared" si="2"/>
         <v>49.859154929577464</v>
       </c>
-      <c r="G55" s="91">
+      <c r="G55" s="84">
         <f t="shared" si="3"/>
         <v>55.466666666666669</v>
       </c>
-      <c r="H55" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="I55" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="J55" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="K55" s="54" t="s">
-        <v>193</v>
-      </c>
-      <c r="L55" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="M55" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="N55" s="56" t="s">
-        <v>268</v>
-      </c>
-      <c r="O55" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="P55" s="56" t="s">
-        <v>200</v>
+      <c r="H55" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="I55" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="K55" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="L55" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="M55" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="N55" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="O55" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="P55" s="51" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="52">
+      <c r="A56" s="47">
         <v>45557</v>
       </c>
-      <c r="B56" s="91">
+      <c r="B56" s="84">
         <v>30.1</v>
       </c>
-      <c r="C56" s="53">
+      <c r="C56" s="48">
         <v>390</v>
       </c>
-      <c r="D56" s="53">
+      <c r="D56" s="48">
         <v>1140</v>
       </c>
-      <c r="E56" s="55">
+      <c r="E56" s="50">
         <v>0.30208333333333331</v>
       </c>
-      <c r="F56" s="91">
+      <c r="F56" s="84">
         <f t="shared" si="2"/>
         <v>12.956810631229235</v>
       </c>
-      <c r="G56" s="91">
+      <c r="G56" s="84">
         <f t="shared" si="3"/>
         <v>37.799999999999997</v>
       </c>
-      <c r="H56" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="I56" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="J56" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="K56" s="54" t="s">
-        <v>193</v>
-      </c>
-      <c r="L56" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="M56" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="N56" s="56" t="s">
-        <v>268</v>
-      </c>
-      <c r="O56" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="P56" s="56"/>
+      <c r="H56" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="I56" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="J56" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="K56" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="L56" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="M56" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="N56" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="O56" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="P56" s="51"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="57">
+      <c r="A57" s="52">
         <v>45562</v>
       </c>
-      <c r="B57" s="92">
+      <c r="B57" s="85">
         <v>23.35</v>
       </c>
-      <c r="C57" s="58">
+      <c r="C57" s="53">
         <v>2520</v>
       </c>
-      <c r="D57" s="58">
+      <c r="D57" s="53">
         <v>1760</v>
       </c>
-      <c r="E57" s="59">
+      <c r="E57" s="54">
         <v>0.44791666666666669</v>
       </c>
-      <c r="F57" s="92">
+      <c r="F57" s="85">
         <f t="shared" si="2"/>
         <v>107.92291220556744</v>
       </c>
-      <c r="G57" s="92">
+      <c r="G57" s="85">
         <f t="shared" si="3"/>
         <v>54.416666666666664</v>
       </c>
-      <c r="H57" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="I57" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="J57" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="K57" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="L57" s="60" t="s">
-        <v>195</v>
-      </c>
-      <c r="M57" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="N57" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="O57" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="P57" s="61" t="s">
-        <v>201</v>
+      <c r="H57" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="I57" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="K57" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="L57" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="M57" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="N57" s="56" t="s">
+        <v>390</v>
+      </c>
+      <c r="O57" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="P57" s="56" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="57">
+      <c r="A58" s="52">
         <v>45563</v>
       </c>
-      <c r="B58" s="92">
+      <c r="B58" s="85">
         <v>27</v>
       </c>
-      <c r="C58" s="58">
+      <c r="C58" s="53">
         <v>1200</v>
       </c>
-      <c r="D58" s="58">
+      <c r="D58" s="53">
         <v>1960</v>
       </c>
-      <c r="E58" s="59">
+      <c r="E58" s="54">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F58" s="92">
+      <c r="F58" s="85">
         <f t="shared" si="2"/>
         <v>44.444444444444443</v>
       </c>
-      <c r="G58" s="92">
+      <c r="G58" s="85">
         <f t="shared" si="3"/>
         <v>45.533333333333331</v>
       </c>
-      <c r="H58" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="I58" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="J58" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="K58" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="L58" s="60" t="s">
-        <v>195</v>
-      </c>
-      <c r="M58" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="N58" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="O58" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="P58" s="61"/>
+      <c r="H58" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="I58" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="K58" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="L58" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="M58" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="N58" s="56" t="s">
+        <v>390</v>
+      </c>
+      <c r="O58" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="P58" s="56"/>
     </row>
     <row r="59" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="62">
+      <c r="A59" s="57">
         <v>45597</v>
       </c>
-      <c r="B59" s="93">
+      <c r="B59" s="86">
         <v>24.8</v>
       </c>
-      <c r="C59" s="63">
+      <c r="C59" s="58">
         <v>860</v>
       </c>
-      <c r="D59" s="63">
+      <c r="D59" s="58">
         <v>550</v>
       </c>
-      <c r="E59" s="64">
+      <c r="E59" s="59">
         <v>0.22916666666666666</v>
       </c>
-      <c r="F59" s="93">
+      <c r="F59" s="86">
         <f t="shared" si="2"/>
         <v>34.677419354838712</v>
       </c>
-      <c r="G59" s="93">
+      <c r="G59" s="86">
         <f t="shared" si="3"/>
         <v>35.233333333333334</v>
       </c>
-      <c r="H59" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I59" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J59" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K59" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L59" s="73" t="s">
-        <v>225</v>
-      </c>
-      <c r="M59" s="65" t="s">
-        <v>224</v>
-      </c>
-      <c r="N59" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="O59" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P59" s="65" t="s">
+      <c r="H59" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I59" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J59" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K59" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L59" s="67" t="s">
         <v>221</v>
       </c>
+      <c r="M59" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="N59" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O59" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P59" s="60" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="60" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="62">
+      <c r="A60" s="57">
         <v>45598</v>
       </c>
-      <c r="B60" s="93">
+      <c r="B60" s="86">
         <v>42.1</v>
       </c>
-      <c r="C60" s="63">
+      <c r="C60" s="58">
         <v>940</v>
       </c>
-      <c r="D60" s="63">
+      <c r="D60" s="58">
         <v>830</v>
       </c>
-      <c r="E60" s="64">
+      <c r="E60" s="59">
         <v>0.4375</v>
       </c>
-      <c r="F60" s="93">
+      <c r="F60" s="86">
         <f t="shared" si="2"/>
         <v>22.327790973871732</v>
       </c>
-      <c r="G60" s="93">
+      <c r="G60" s="86">
         <f t="shared" si="3"/>
         <v>54.266666666666666</v>
       </c>
-      <c r="H60" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I60" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J60" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K60" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L60" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="M60" s="65" t="s">
-        <v>226</v>
-      </c>
-      <c r="N60" s="65" t="s">
+      <c r="H60" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I60" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K60" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L60" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="M60" s="60" t="s">
         <v>222</v>
       </c>
-      <c r="O60" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P60" s="65"/>
+      <c r="N60" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O60" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P60" s="60"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="62">
+      <c r="A61" s="57">
         <v>45599</v>
       </c>
-      <c r="B61" s="93">
+      <c r="B61" s="86">
         <v>48.9</v>
       </c>
-      <c r="C61" s="63">
+      <c r="C61" s="58">
         <v>1210</v>
       </c>
-      <c r="D61" s="63">
+      <c r="D61" s="58">
         <v>1160</v>
       </c>
-      <c r="E61" s="64">
+      <c r="E61" s="59">
         <v>0.46875</v>
       </c>
-      <c r="F61" s="93">
+      <c r="F61" s="86">
         <f t="shared" si="2"/>
         <v>24.744376278118612</v>
       </c>
-      <c r="G61" s="93">
+      <c r="G61" s="86">
         <f t="shared" si="3"/>
         <v>64.86666666666666</v>
       </c>
-      <c r="H61" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I61" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J61" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K61" s="64" t="s">
+      <c r="H61" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I61" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J61" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K61" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L61" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="M61" s="60" t="s">
         <v>223</v>
       </c>
-      <c r="L61" s="73" t="s">
-        <v>233</v>
-      </c>
-      <c r="M61" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="N61" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="O61" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P61" s="65"/>
+      <c r="N61" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O61" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P61" s="60"/>
     </row>
     <row r="62" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="62">
+      <c r="A62" s="57">
         <v>45600</v>
       </c>
-      <c r="B62" s="93">
+      <c r="B62" s="86">
         <v>44.3</v>
       </c>
-      <c r="C62" s="63">
+      <c r="C62" s="58">
         <v>1520</v>
       </c>
-      <c r="D62" s="63">
+      <c r="D62" s="58">
         <v>1130</v>
       </c>
-      <c r="E62" s="64">
+      <c r="E62" s="59">
         <v>0.46527777777777773</v>
       </c>
-      <c r="F62" s="93">
+      <c r="F62" s="86">
         <f t="shared" si="2"/>
         <v>34.311512415349888</v>
       </c>
-      <c r="G62" s="93">
+      <c r="G62" s="86">
         <f t="shared" si="3"/>
         <v>63.266666666666666</v>
       </c>
-      <c r="H62" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I62" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J62" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K62" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L62" s="73" t="s">
-        <v>234</v>
-      </c>
-      <c r="M62" s="65" t="s">
-        <v>228</v>
-      </c>
-      <c r="N62" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="O62" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P62" s="65"/>
+      <c r="H62" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K62" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L62" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="M62" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="N62" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O62" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P62" s="60"/>
     </row>
     <row r="63" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="62">
+      <c r="A63" s="57">
         <v>45601</v>
       </c>
-      <c r="B63" s="93">
+      <c r="B63" s="86">
         <v>46.9</v>
       </c>
-      <c r="C63" s="63">
+      <c r="C63" s="58">
         <v>1010</v>
       </c>
-      <c r="D63" s="63">
+      <c r="D63" s="58">
         <v>1780</v>
       </c>
-      <c r="E63" s="64">
+      <c r="E63" s="59">
         <v>0.49305555555555558</v>
       </c>
-      <c r="F63" s="93">
+      <c r="F63" s="86">
         <f t="shared" si="2"/>
         <v>21.535181236673775</v>
       </c>
-      <c r="G63" s="93">
+      <c r="G63" s="86">
         <f t="shared" si="3"/>
         <v>62.933333333333337</v>
       </c>
-      <c r="H63" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I63" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J63" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K63" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L63" s="73" t="s">
-        <v>235</v>
-      </c>
-      <c r="M63" s="65" t="s">
-        <v>229</v>
-      </c>
-      <c r="N63" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="O63" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P63" s="65"/>
+      <c r="H63" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J63" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K63" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L63" s="67" t="s">
+        <v>231</v>
+      </c>
+      <c r="M63" s="60" t="s">
+        <v>225</v>
+      </c>
+      <c r="N63" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O63" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P63" s="60"/>
     </row>
     <row r="64" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="62">
+      <c r="A64" s="57">
         <v>45602</v>
       </c>
-      <c r="B64" s="93">
+      <c r="B64" s="86">
         <v>47.1</v>
       </c>
-      <c r="C64" s="63">
+      <c r="C64" s="58">
         <v>1220</v>
       </c>
-      <c r="D64" s="63">
+      <c r="D64" s="58">
         <v>1670</v>
       </c>
-      <c r="E64" s="64">
+      <c r="E64" s="59">
         <v>0.47569444444444442</v>
       </c>
-      <c r="F64" s="93">
+      <c r="F64" s="86">
         <f t="shared" si="2"/>
         <v>25.902335456475583</v>
       </c>
-      <c r="G64" s="93">
+      <c r="G64" s="86">
         <f t="shared" si="3"/>
         <v>64.86666666666666</v>
       </c>
-      <c r="H64" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I64" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J64" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K64" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L64" s="73" t="s">
-        <v>236</v>
-      </c>
-      <c r="M64" s="65" t="s">
-        <v>230</v>
-      </c>
-      <c r="N64" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="O64" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P64" s="65" t="s">
-        <v>241</v>
+      <c r="H64" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I64" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J64" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K64" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L64" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="M64" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="N64" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O64" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P64" s="60" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="62">
+      <c r="A65" s="57">
         <v>45603</v>
       </c>
-      <c r="B65" s="93">
+      <c r="B65" s="86">
         <v>23.5</v>
       </c>
-      <c r="C65" s="63">
+      <c r="C65" s="58">
         <v>750</v>
       </c>
-      <c r="D65" s="63">
+      <c r="D65" s="58">
         <v>870</v>
       </c>
-      <c r="E65" s="64">
+      <c r="E65" s="59">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F65" s="93">
+      <c r="F65" s="86">
         <f t="shared" si="2"/>
         <v>31.914893617021278</v>
       </c>
-      <c r="G65" s="93">
+      <c r="G65" s="86">
         <f t="shared" si="3"/>
         <v>33.9</v>
       </c>
-      <c r="H65" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="I65" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J65" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="K65" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L65" s="73" t="s">
-        <v>237</v>
-      </c>
-      <c r="M65" s="65" t="s">
-        <v>231</v>
-      </c>
-      <c r="N65" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="O65" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="P65" s="65"/>
+      <c r="H65" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I65" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K65" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="L65" s="67" t="s">
+        <v>233</v>
+      </c>
+      <c r="M65" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="N65" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="O65" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="P65" s="60"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>45641</v>
       </c>
-      <c r="B66" s="82">
+      <c r="B66" s="76">
         <v>9.4</v>
       </c>
       <c r="C66" s="9">
@@ -5070,44 +5202,44 @@
       <c r="E66" s="3">
         <v>0.19444444444444445</v>
       </c>
-      <c r="F66" s="82">
+      <c r="F66" s="76">
         <f t="shared" si="2"/>
         <v>89.361702127659569</v>
       </c>
-      <c r="G66" s="82">
+      <c r="G66" s="76">
         <f t="shared" si="3"/>
         <v>20.6</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="L66" s="66" t="s">
-        <v>243</v>
+        <v>238</v>
+      </c>
+      <c r="L66" s="61" t="s">
+        <v>239</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O66" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45660</v>
       </c>
-      <c r="B67" s="82">
+      <c r="B67" s="76">
         <v>21</v>
       </c>
       <c r="C67" s="9">
@@ -5119,44 +5251,47 @@
       <c r="E67" s="3">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F67" s="82">
+      <c r="F67" s="76">
         <f t="shared" si="2"/>
         <v>38.095238095238095</v>
       </c>
-      <c r="G67" s="82">
+      <c r="G67" s="76">
         <f t="shared" si="3"/>
         <v>31.666666666666668</v>
       </c>
       <c r="H67" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L67" s="61" t="s">
+        <v>244</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="L67" s="66" t="s">
-        <v>248</v>
-      </c>
-      <c r="M67" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>45675</v>
       </c>
-      <c r="B68" s="82">
+      <c r="B68" s="76">
         <v>27.2</v>
       </c>
       <c r="C68" s="9">
@@ -5168,141 +5303,144 @@
       <c r="E68" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="F68" s="82">
+      <c r="F68" s="76">
         <f t="shared" si="2"/>
         <v>72.794117647058826</v>
       </c>
-      <c r="G68" s="82">
+      <c r="G68" s="76">
         <f t="shared" si="3"/>
         <v>53.6</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L68" s="66" t="s">
-        <v>270</v>
+        <v>265</v>
+      </c>
+      <c r="L68" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>348</v>
       </c>
       <c r="O68" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="17">
+      <c r="A69" s="16">
         <v>45689</v>
       </c>
-      <c r="B69" s="85">
+      <c r="B69" s="78">
         <v>5.3</v>
       </c>
-      <c r="C69" s="18">
+      <c r="C69" s="17">
         <v>730</v>
       </c>
-      <c r="D69" s="18">
+      <c r="D69" s="17">
         <v>20</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="18">
         <v>6.25E-2</v>
       </c>
-      <c r="F69" s="85">
+      <c r="F69" s="78">
         <f t="shared" si="2"/>
         <v>137.73584905660377</v>
       </c>
-      <c r="G69" s="85">
+      <c r="G69" s="78">
         <f t="shared" si="3"/>
         <v>12.666666666666666</v>
       </c>
-      <c r="H69" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="I69" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J69" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="K69" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="L69" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="M69" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="N69" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="O69" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P69" s="20"/>
+      <c r="H69" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K69" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="L69" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="M69" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="N69" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="O69" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="P69" s="19"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" s="17">
+      <c r="A70" s="16">
         <v>45689</v>
       </c>
-      <c r="B70" s="85">
+      <c r="B70" s="78">
         <v>19.899999999999999</v>
       </c>
-      <c r="C70" s="18">
+      <c r="C70" s="17">
         <v>790</v>
       </c>
-      <c r="D70" s="18">
+      <c r="D70" s="17">
         <v>1500</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70" s="18">
         <v>0.25</v>
       </c>
-      <c r="F70" s="85">
+      <c r="F70" s="78">
         <f t="shared" si="2"/>
         <v>39.698492462311563</v>
       </c>
-      <c r="G70" s="85">
+      <c r="G70" s="78">
         <f t="shared" si="3"/>
         <v>32.799999999999997</v>
       </c>
-      <c r="H70" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="I70" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J70" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="K70" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="L70" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="M70" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="N70" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="O70" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P70" s="20"/>
+      <c r="H70" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="I70" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J70" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K70" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="L70" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="M70" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="N70" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="O70" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="P70" s="19"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>45697</v>
       </c>
-      <c r="B71" s="82">
+      <c r="B71" s="76">
         <v>24.3</v>
       </c>
       <c r="C71" s="9">
@@ -5314,35 +5452,140 @@
       <c r="E71" s="3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F71" s="82">
+      <c r="F71" s="76">
         <f t="shared" si="2"/>
         <v>56.79012345679012</v>
       </c>
-      <c r="G71" s="82">
+      <c r="G71" s="76">
         <f t="shared" si="3"/>
         <v>42.7</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="L71" s="66" t="s">
+        <v>243</v>
+      </c>
+      <c r="L71" s="61" t="s">
+        <v>345</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="N71" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="M71" s="10" t="s">
-        <v>351</v>
-      </c>
       <c r="O71" s="10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="90">
+        <v>45703</v>
+      </c>
+      <c r="B72" s="91">
+        <v>7</v>
+      </c>
+      <c r="C72" s="92">
+        <v>600</v>
+      </c>
+      <c r="D72" s="92">
+        <v>300</v>
+      </c>
+      <c r="E72" s="93">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F72" s="91">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="G72" s="91">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="H72" s="93" t="s">
+        <v>242</v>
+      </c>
+      <c r="I72" s="93" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="K72" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="L72" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="M72" s="95" t="s">
+        <v>353</v>
+      </c>
+      <c r="N72" s="95" t="s">
+        <v>388</v>
+      </c>
+      <c r="O72" s="95" t="s">
+        <v>215</v>
+      </c>
+      <c r="P72" s="95" t="s">
         <v>352</v>
       </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="90">
+        <v>45704</v>
+      </c>
+      <c r="B73" s="91">
+        <v>7</v>
+      </c>
+      <c r="C73" s="92">
+        <v>400</v>
+      </c>
+      <c r="D73" s="92">
+        <v>700</v>
+      </c>
+      <c r="E73" s="93">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F73" s="91">
+        <f t="shared" ref="F73" si="4">C73/B73</f>
+        <v>57.142857142857146</v>
+      </c>
+      <c r="G73" s="91">
+        <f t="shared" ref="G73" si="5">B73+C73/100+D73/300</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="H73" s="93" t="s">
+        <v>242</v>
+      </c>
+      <c r="I73" s="93" t="s">
+        <v>43</v>
+      </c>
+      <c r="J73" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="K73" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="L73" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="M73" s="95" t="s">
+        <v>354</v>
+      </c>
+      <c r="N73" s="95" t="s">
+        <v>388</v>
+      </c>
+      <c r="O73" s="95" t="s">
+        <v>215</v>
+      </c>
+      <c r="P73" s="95"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P70">
@@ -5367,60 +5610,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>120</v>
+      <c r="C1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="16">
-        <f t="shared" ref="D2:D26" si="0">IF(C2="Z", 1, IF(C2="S", 2, IF(C2="A", 3, IF(C2="B", 4, IF(C2="C", 5, IF(C2="D", 6, 7))))))</f>
+        <v>93</v>
+      </c>
+      <c r="D2" s="15">
+        <f t="shared" ref="D2:D27" si="0">IF(C2="Z", 1, IF(C2="S", 2, IF(C2="A", 3, IF(C2="B", 4, IF(C2="C", 5, IF(C2="D", 6, 7))))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="16">
+        <v>93</v>
+      </c>
+      <c r="D3" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="16">
+        <v>93</v>
+      </c>
+      <c r="D4" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5430,27 +5673,27 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="16">
+        <v>93</v>
+      </c>
+      <c r="D5" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="16">
+        <v>94</v>
+      </c>
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -5460,333 +5703,345 @@
         <v>34</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="16">
+        <v>94</v>
+      </c>
+      <c r="D7" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="16">
+        <v>94</v>
+      </c>
+      <c r="D8" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="16">
+        <v>94</v>
+      </c>
+      <c r="D9" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="16">
+        <v>94</v>
+      </c>
+      <c r="D10" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="16">
+        <v>94</v>
+      </c>
+      <c r="D11" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="16">
+        <v>95</v>
+      </c>
+      <c r="D12" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="16">
+        <v>95</v>
+      </c>
+      <c r="D13" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="16">
+        <v>95</v>
+      </c>
+      <c r="D14" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="16">
+        <v>95</v>
+      </c>
+      <c r="D15" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="16">
+        <v>95</v>
+      </c>
+      <c r="D16" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="16">
+        <v>95</v>
+      </c>
+      <c r="D17" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="16">
+        <v>116</v>
+      </c>
+      <c r="D18" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="16">
+        <v>116</v>
+      </c>
+      <c r="D19" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="16">
+        <v>116</v>
+      </c>
+      <c r="D20" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="16">
+        <v>116</v>
+      </c>
+      <c r="D21" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="16">
+        <v>116</v>
+      </c>
+      <c r="D22" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="16">
+        <v>116</v>
+      </c>
+      <c r="D23" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="16">
+        <v>116</v>
+      </c>
+      <c r="D24" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="16">
+        <v>116</v>
+      </c>
+      <c r="D25" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="16">
+        <v>94</v>
+      </c>
+      <c r="D26" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D27" s="16"/>
+      <c r="A27" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D28" s="16"/>
+      <c r="D28" s="15"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D29" s="16"/>
+      <c r="D29" s="15"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D30" s="16"/>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="16"/>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D32" s="16"/>
+      <c r="D32" s="15"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" s="16"/>
+      <c r="D33" s="15"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34" s="16"/>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35" s="16"/>
+      <c r="D35" s="15"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D36" s="16"/>
+      <c r="D36" s="15"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D37" s="16"/>
+      <c r="D37" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D18">
@@ -5818,7 +6073,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.88671875" style="5" bestFit="1" customWidth="1"/>
@@ -5835,7 +6090,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B2" s="5">
         <v>3172</v>
@@ -5843,7 +6098,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B3" s="5">
         <v>3045</v>
@@ -5851,7 +6106,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B4" s="5">
         <v>2789</v>
@@ -5859,7 +6114,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B5" s="5">
         <v>2685</v>
@@ -5867,7 +6122,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B6" s="5">
         <v>2663</v>
@@ -5875,7 +6130,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B7" s="5">
         <v>2662</v>
@@ -5883,7 +6138,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B8" s="5">
         <v>2525</v>
@@ -5891,7 +6146,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B9" s="5">
         <v>2459</v>
@@ -5899,7 +6154,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B10" s="5">
         <v>2432</v>
@@ -5907,7 +6162,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B11" s="5">
         <v>2338</v>
@@ -5915,7 +6170,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B12" s="5">
         <v>2284</v>
@@ -5923,7 +6178,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B13" s="5">
         <v>2276</v>
@@ -5931,7 +6186,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B14" s="5">
         <v>2222</v>
@@ -5939,7 +6194,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B15" s="5">
         <v>2219</v>
@@ -5947,7 +6202,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B16" s="5">
         <v>2175</v>
@@ -5955,7 +6210,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B17" s="5">
         <v>2156</v>
@@ -5963,7 +6218,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B18" s="5">
         <v>2080</v>
@@ -5971,7 +6226,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B19" s="5">
         <v>2051</v>
@@ -5979,7 +6234,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B20" s="5">
         <v>2049</v>
@@ -5987,7 +6242,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B21" s="5">
         <v>2037</v>
@@ -5995,7 +6250,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B22" s="5">
         <v>1992</v>
@@ -6003,7 +6258,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B23" s="5">
         <v>1976</v>
@@ -6011,7 +6266,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B24" s="5">
         <v>1966</v>
@@ -6019,7 +6274,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B25" s="5">
         <v>1930</v>
@@ -6027,7 +6282,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B26" s="5">
         <v>1901</v>
@@ -6035,7 +6290,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B27" s="5">
         <v>1850</v>
@@ -6043,7 +6298,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B28" s="5">
         <v>1821</v>
@@ -6051,7 +6306,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B29" s="5">
         <v>1811</v>
@@ -6059,7 +6314,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B30" s="5">
         <v>1699</v>
@@ -6067,7 +6322,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B31" s="5">
         <v>1635</v>
@@ -6075,7 +6330,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B32" s="5">
         <v>1597</v>
@@ -6083,7 +6338,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B33" s="5">
         <v>1570</v>
@@ -6091,7 +6346,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B34" s="5">
         <v>1566</v>
@@ -6099,7 +6354,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B35" s="5">
         <v>1548</v>
@@ -6107,7 +6362,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B36" s="5">
         <v>1435</v>
@@ -6115,7 +6370,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B37" s="5">
         <v>1432</v>
@@ -6123,7 +6378,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B38" s="5">
         <v>1421</v>
@@ -6131,7 +6386,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B39" s="5">
         <v>1413</v>
@@ -6139,7 +6394,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B40" s="5">
         <v>1379</v>
@@ -6147,7 +6402,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B41" s="5">
         <v>1365</v>
@@ -6155,7 +6410,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B42" s="5">
         <v>1364</v>
@@ -6163,7 +6418,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B43" s="5">
         <v>1357</v>
@@ -6171,7 +6426,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B44" s="5">
         <v>1342</v>
@@ -6179,7 +6434,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B45" s="5">
         <v>1297</v>
@@ -6187,7 +6442,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B46" s="5">
         <v>1291</v>
@@ -6195,7 +6450,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B47" s="5">
         <v>1050</v>
@@ -6203,7 +6458,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B48" s="5">
         <v>1011</v>
@@ -6211,7 +6466,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B49" s="5">
         <v>805</v>
@@ -6219,7 +6474,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B50" s="5">
         <v>656</v>
@@ -6227,7 +6482,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B51" s="5">
         <v>645</v>
@@ -6235,7 +6490,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B52" s="5">
         <v>634</v>
@@ -6243,7 +6498,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B53" s="5">
         <v>563</v>
@@ -6251,7 +6506,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B54" s="5">
         <v>433</v>
@@ -6259,7 +6514,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B55" s="5">
         <v>1089</v>
@@ -6267,10 +6522,18 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B56" s="5">
         <v>1534</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B57" s="5">
+        <v>1959</v>
       </c>
     </row>
   </sheetData>
@@ -6285,420 +6548,591 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" style="8" customWidth="1"/>
-    <col min="3" max="5" width="9.109375" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="11.5546875" style="4"/>
+    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="12" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" s="12" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="E1" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="F1" s="96" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="C2" s="8" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="C8" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>2</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>1</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="6">
+        <v>220</v>
+      </c>
+      <c r="E14" s="7">
+        <v>14000</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>3</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>3</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>1</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="C20" s="8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>1</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D22" s="6">
+        <v>125</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9000</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="98" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D23" s="6">
+        <v>85</v>
+      </c>
+      <c r="E23" s="7">
+        <v>5000</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>1</v>
+      </c>
+      <c r="B24" s="98" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="D24" s="6">
+        <v>45</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>2</v>
+      </c>
+      <c r="B26" s="98" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D26" s="6">
+        <v>55</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3500</v>
+      </c>
+      <c r="F26" s="8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>3</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>3</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>2</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="4">
-        <v>220</v>
-      </c>
-      <c r="D14" s="4">
-        <v>14000</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>2</v>
+      </c>
+      <c r="B31" s="98" t="s">
+        <v>247</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F31" s="8">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>2</v>
+      </c>
+      <c r="B32" s="98" t="s">
+        <v>257</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>3</v>
+      </c>
+      <c r="B33" s="98" t="s">
+        <v>272</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="D33" s="6">
+        <v>35</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1500</v>
+      </c>
+      <c r="F33" s="8">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>2</v>
+      </c>
+      <c r="B34" s="98" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F34" s="8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="4">
-        <v>125</v>
-      </c>
-      <c r="D22" s="4">
-        <v>9000</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="94" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4">
-        <v>85</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="C35" s="8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>3</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>2</v>
+      </c>
+      <c r="B37" s="98" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D37" s="6">
+        <v>90</v>
+      </c>
+      <c r="E37" s="7">
         <v>5000</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F37" s="8">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>1</v>
+      </c>
+      <c r="B38" s="98" t="s">
+        <v>269</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D38" s="6">
+        <v>35</v>
+      </c>
+      <c r="E38" s="7">
         <v>2000</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="94" t="s">
-        <v>205</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="4">
-        <v>45</v>
-      </c>
-      <c r="D24" s="4">
-        <v>2500</v>
-      </c>
-      <c r="E24" s="4">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="94" t="s">
-        <v>277</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="4">
-        <v>55</v>
-      </c>
-      <c r="D26" s="4">
-        <v>3500</v>
-      </c>
-      <c r="E26" s="4">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="F38" s="8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>2</v>
+      </c>
+      <c r="B39" s="98" t="s">
+        <v>342</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>3</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="94" t="s">
-        <v>251</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="4">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="94" t="s">
-        <v>276</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="4">
-        <v>35</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1500</v>
-      </c>
-      <c r="E33" s="4">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="94" t="s">
-        <v>206</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="4">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="94" t="s">
-        <v>280</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="4">
-        <v>90</v>
-      </c>
-      <c r="D37" s="4">
-        <v>5000</v>
-      </c>
-      <c r="E37" s="4">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="94" t="s">
-        <v>273</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="4">
-        <v>35</v>
-      </c>
-      <c r="D38" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E38" s="4">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="94" t="s">
-        <v>347</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>44</v>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>1</v>
+      </c>
+      <c r="B41" s="98" t="s">
+        <v>356</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>2</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>2</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>2</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E26">
-    <sortState ref="A2:E38">
-      <sortCondition ref="A1:A26"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Randonnée.xlsx
+++ b/data/Randonnée.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED5DCE1-28BE-4F98-9817-C8457F4A3119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="28680" yWindow="-2730" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Randonnées" sheetId="4" r:id="rId1"/>
@@ -18,7 +19,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sommets!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$F$44</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1201,7 +1213,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[h]:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1780,6 +1792,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1815,6 +1844,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1990,29 +2036,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="76" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="76" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="76" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" style="76" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="76" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="76" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="3" customWidth="1"/>
     <col min="9" max="9" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.21875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="27.21875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="29.77734375" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="45.88671875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="29.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="27.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="29.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="45.85546875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="29.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="74" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="74" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -2062,7 +2108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44997</v>
       </c>
@@ -2079,11 +2125,11 @@
         <v>0.15972222222222224</v>
       </c>
       <c r="F2" s="76">
-        <f t="shared" ref="F2:F33" si="0">C2/B2</f>
+        <f>C2/B2</f>
         <v>58.477096966091615</v>
       </c>
       <c r="G2" s="76">
-        <f t="shared" ref="G2:G33" si="1">B2+C2/100+D2/300</f>
+        <f>B2+C2/100+D2/300</f>
         <v>29.916666666666668</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -2105,7 +2151,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45010</v>
       </c>
@@ -2122,11 +2168,11 @@
         <v>0.4375</v>
       </c>
       <c r="F3" s="76">
-        <f t="shared" si="0"/>
+        <f>C3/B3</f>
         <v>56.708860759493668</v>
       </c>
       <c r="G3" s="76">
-        <f t="shared" si="1"/>
+        <f>B3+C3/100+D3/300</f>
         <v>69.36666666666666</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -2148,7 +2194,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45011</v>
       </c>
@@ -2165,11 +2211,11 @@
         <v>0.15972222222222224</v>
       </c>
       <c r="F4" s="76">
-        <f t="shared" si="0"/>
+        <f>C4/B4</f>
         <v>42.788844621513945</v>
       </c>
       <c r="G4" s="76">
-        <f t="shared" si="1"/>
+        <f>B4+C4/100+D4/300</f>
         <v>19.71</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -2191,7 +2237,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45017</v>
       </c>
@@ -2208,11 +2254,11 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="76">
-        <f t="shared" si="0"/>
+        <f>C5/B5</f>
         <v>48.152424942263281</v>
       </c>
       <c r="G5" s="76">
-        <f t="shared" si="1"/>
+        <f>B5+C5/100+D5/300</f>
         <v>28.44</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -2234,7 +2280,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45038</v>
       </c>
@@ -2251,11 +2297,11 @@
         <v>0.25</v>
       </c>
       <c r="F6" s="76">
-        <f t="shared" si="0"/>
+        <f>C6/B6</f>
         <v>53.333333333333336</v>
       </c>
       <c r="G6" s="76">
-        <f t="shared" si="1"/>
+        <f>B6+C6/100+D6/300</f>
         <v>25.666666666666668</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -2274,7 +2320,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45039</v>
       </c>
@@ -2291,11 +2337,11 @@
         <v>0.1875</v>
       </c>
       <c r="F7" s="76">
-        <f t="shared" si="0"/>
+        <f>C7/B7</f>
         <v>49.567567567567565</v>
       </c>
       <c r="G7" s="76">
-        <f t="shared" si="1"/>
+        <f>B7+C7/100+D7/300</f>
         <v>30.726666666666667</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -2317,7 +2363,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45060</v>
       </c>
@@ -2334,11 +2380,11 @@
         <v>0.1875</v>
       </c>
       <c r="F8" s="76">
-        <f t="shared" si="0"/>
+        <f>C8/B8</f>
         <v>54.384017758046618</v>
       </c>
       <c r="G8" s="76">
-        <f t="shared" si="1"/>
+        <f>B8+C8/100+D8/300</f>
         <v>31.086666666666666</v>
       </c>
       <c r="H8" s="3" t="s">
@@ -2360,7 +2406,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45073</v>
       </c>
@@ -2377,11 +2423,11 @@
         <v>0.34722222222222227</v>
       </c>
       <c r="F9" s="76">
-        <f t="shared" si="0"/>
+        <f>C9/B9</f>
         <v>65.704918032786878</v>
       </c>
       <c r="G9" s="76">
-        <f t="shared" si="1"/>
+        <f>B9+C9/100+D9/300</f>
         <v>57.22</v>
       </c>
       <c r="H9" s="3" t="s">
@@ -2403,7 +2449,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45074</v>
       </c>
@@ -2420,11 +2466,11 @@
         <v>0.125</v>
       </c>
       <c r="F10" s="76">
-        <f t="shared" si="0"/>
+        <f>C10/B10</f>
         <v>44.846153846153847</v>
       </c>
       <c r="G10" s="76">
-        <f t="shared" si="1"/>
+        <f>B10+C10/100+D10/300</f>
         <v>20.773333333333333</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -2446,7 +2492,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45080</v>
       </c>
@@ -2463,11 +2509,11 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="F11" s="76">
-        <f t="shared" si="0"/>
+        <f>C11/B11</f>
         <v>122.22222222222223</v>
       </c>
       <c r="G11" s="76">
-        <f t="shared" si="1"/>
+        <f>B11+C11/100+D11/300</f>
         <v>11.833333333333334</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -2489,7 +2535,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>45108</v>
       </c>
@@ -2506,11 +2552,11 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="F12" s="77">
-        <f t="shared" si="0"/>
+        <f>C12/B12</f>
         <v>59.785407725321889</v>
       </c>
       <c r="G12" s="77">
-        <f t="shared" si="1"/>
+        <f>B12+C12/100+D12/300</f>
         <v>40.076666666666668</v>
       </c>
       <c r="H12" s="30" t="s">
@@ -2541,7 +2587,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
         <v>45109</v>
       </c>
@@ -2558,11 +2604,11 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F13" s="77">
-        <f t="shared" si="0"/>
+        <f>C13/B13</f>
         <v>114.23645320197043</v>
       </c>
       <c r="G13" s="77">
-        <f t="shared" si="1"/>
+        <f>B13+C13/100+D13/300</f>
         <v>48.006666666666668</v>
       </c>
       <c r="H13" s="30" t="s">
@@ -2593,7 +2639,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>45110</v>
       </c>
@@ -2610,11 +2656,11 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="F14" s="77">
-        <f t="shared" si="0"/>
+        <f>C14/B14</f>
         <v>56.846590909090907</v>
       </c>
       <c r="G14" s="77">
-        <f t="shared" si="1"/>
+        <f>B14+C14/100+D14/300</f>
         <v>62.603333333333339</v>
       </c>
       <c r="H14" s="30" t="s">
@@ -2643,7 +2689,7 @@
       </c>
       <c r="P14" s="31"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="28">
         <v>45111</v>
       </c>
@@ -2660,11 +2706,11 @@
         <v>0.375</v>
       </c>
       <c r="F15" s="77">
-        <f t="shared" si="0"/>
+        <f>C15/B15</f>
         <v>63.792048929663601</v>
       </c>
       <c r="G15" s="77">
-        <f t="shared" si="1"/>
+        <f>B15+C15/100+D15/300</f>
         <v>59.363333333333337</v>
       </c>
       <c r="H15" s="30" t="s">
@@ -2693,7 +2739,7 @@
       </c>
       <c r="P15" s="31"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="28">
         <v>45112</v>
       </c>
@@ -2710,11 +2756,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="F16" s="77">
-        <f t="shared" si="0"/>
+        <f>C16/B16</f>
         <v>67.601476014760138</v>
       </c>
       <c r="G16" s="77">
-        <f t="shared" si="1"/>
+        <f>B16+C16/100+D16/300</f>
         <v>54.58</v>
       </c>
       <c r="H16" s="30" t="s">
@@ -2745,7 +2791,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="28">
         <v>45113</v>
       </c>
@@ -2762,11 +2808,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F17" s="77">
-        <f t="shared" si="0"/>
+        <f>C17/B17</f>
         <v>82.015810276679844</v>
       </c>
       <c r="G17" s="77">
-        <f t="shared" si="1"/>
+        <f>B17+C17/100+D17/300</f>
         <v>51.569999999999993</v>
       </c>
       <c r="H17" s="30" t="s">
@@ -2795,7 +2841,7 @@
       </c>
       <c r="P17" s="31"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="28">
         <v>45114</v>
       </c>
@@ -2812,11 +2858,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F18" s="77">
-        <f t="shared" si="0"/>
+        <f>C18/B18</f>
         <v>66.180758017492721</v>
       </c>
       <c r="G18" s="77">
-        <f t="shared" si="1"/>
+        <f>B18+C18/100+D18/300</f>
         <v>61.5</v>
       </c>
       <c r="H18" s="30" t="s">
@@ -2845,7 +2891,7 @@
       </c>
       <c r="P18" s="31"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="28">
         <v>45115</v>
       </c>
@@ -2862,11 +2908,11 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F19" s="77">
-        <f t="shared" si="0"/>
+        <f>C19/B19</f>
         <v>45.348837209302324</v>
       </c>
       <c r="G19" s="77">
-        <f t="shared" si="1"/>
+        <f>B19+C19/100+D19/300</f>
         <v>68.540000000000006</v>
       </c>
       <c r="H19" s="30" t="s">
@@ -2897,7 +2943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <v>45116</v>
       </c>
@@ -2914,11 +2960,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F20" s="77">
-        <f t="shared" si="0"/>
+        <f>C20/B20</f>
         <v>37.670807453416145</v>
       </c>
       <c r="G20" s="77">
-        <f t="shared" si="1"/>
+        <f>B20+C20/100+D20/300</f>
         <v>52.463333333333338</v>
       </c>
       <c r="H20" s="30" t="s">
@@ -2947,7 +2993,7 @@
       </c>
       <c r="P20" s="31"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="87">
         <v>45123</v>
       </c>
@@ -2964,11 +3010,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F21" s="88">
-        <f t="shared" si="0"/>
+        <f>C21/B21</f>
         <v>51.434782608695649</v>
       </c>
       <c r="G21" s="88">
-        <f t="shared" si="1"/>
+        <f>B21+C21/100+D21/300</f>
         <v>38.773333333333333</v>
       </c>
       <c r="H21" s="46" t="s">
@@ -2997,7 +3043,7 @@
       </c>
       <c r="P21" s="41"/>
     </row>
-    <row r="22" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="87">
         <v>45124</v>
       </c>
@@ -3014,11 +3060,11 @@
         <v>0.34722222222222227</v>
       </c>
       <c r="F22" s="88">
-        <f t="shared" si="0"/>
+        <f>C22/B22</f>
         <v>51.300236406619391</v>
       </c>
       <c r="G22" s="88">
-        <f t="shared" si="1"/>
+        <f>B22+C22/100+D22/300</f>
         <v>36.15</v>
       </c>
       <c r="H22" s="46" t="s">
@@ -3047,7 +3093,7 @@
       </c>
       <c r="P22" s="41"/>
     </row>
-    <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="87">
         <v>45125</v>
       </c>
@@ -3064,11 +3110,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="F23" s="88">
-        <f t="shared" si="0"/>
+        <f>C23/B23</f>
         <v>60.760931289040322</v>
       </c>
       <c r="G23" s="88">
-        <f t="shared" si="1"/>
+        <f>B23+C23/100+D23/300</f>
         <v>63.75333333333333</v>
       </c>
       <c r="H23" s="46" t="s">
@@ -3099,7 +3145,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="87">
         <v>45127</v>
       </c>
@@ -3116,11 +3162,11 @@
         <v>0.22916666666666666</v>
       </c>
       <c r="F24" s="88">
-        <f t="shared" si="0"/>
+        <f>C24/B24</f>
         <v>43.961038961038959</v>
       </c>
       <c r="G24" s="88">
-        <f t="shared" si="1"/>
+        <f>B24+C24/100+D24/300</f>
         <v>24.426666666666669</v>
       </c>
       <c r="H24" s="46" t="s">
@@ -3149,7 +3195,7 @@
       </c>
       <c r="P24" s="41"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45150</v>
       </c>
@@ -3166,11 +3212,11 @@
         <v>0.25</v>
       </c>
       <c r="F25" s="76">
-        <f t="shared" si="0"/>
+        <f>C25/B25</f>
         <v>40.99244875943905</v>
       </c>
       <c r="G25" s="76">
-        <f t="shared" si="1"/>
+        <f>B25+C25/100+D25/300</f>
         <v>28.673333333333332</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -3195,7 +3241,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45199</v>
       </c>
@@ -3212,11 +3258,11 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="F26" s="76">
-        <f t="shared" si="0"/>
+        <f>C26/B26</f>
         <v>61.807909604519779</v>
       </c>
       <c r="G26" s="76">
-        <f t="shared" si="1"/>
+        <f>B26+C26/100+D26/300</f>
         <v>16.143333333333334</v>
       </c>
       <c r="H26" s="3" t="s">
@@ -3238,7 +3284,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>45205</v>
       </c>
@@ -3255,11 +3301,11 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F27" s="78">
-        <f t="shared" si="0"/>
+        <f>C27/B27</f>
         <v>131.0344827586207</v>
       </c>
       <c r="G27" s="78">
-        <f t="shared" si="1"/>
+        <f>B27+C27/100+D27/300</f>
         <v>36</v>
       </c>
       <c r="H27" s="18" t="s">
@@ -3290,7 +3336,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>45206</v>
       </c>
@@ -3307,11 +3353,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F28" s="78">
-        <f t="shared" si="0"/>
+        <f>C28/B28</f>
         <v>92.452830188679243</v>
       </c>
       <c r="G28" s="78">
-        <f t="shared" si="1"/>
+        <f>B28+C28/100+D28/300</f>
         <v>59.25</v>
       </c>
       <c r="H28" s="18" t="s">
@@ -3342,7 +3388,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>45207</v>
       </c>
@@ -3359,11 +3405,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="F29" s="78">
-        <f t="shared" si="0"/>
+        <f>C29/B29</f>
         <v>62.962962962962962</v>
       </c>
       <c r="G29" s="78">
-        <f t="shared" si="1"/>
+        <f>B29+C29/100+D29/300</f>
         <v>51.666666666666664</v>
       </c>
       <c r="H29" s="18" t="s">
@@ -3392,7 +3438,7 @@
       </c>
       <c r="P29" s="19"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>45208</v>
       </c>
@@ -3409,11 +3455,11 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F30" s="78">
-        <f t="shared" si="0"/>
+        <f>C30/B30</f>
         <v>32.954545454545453</v>
       </c>
       <c r="G30" s="78">
-        <f t="shared" si="1"/>
+        <f>B30+C30/100+D30/300</f>
         <v>35.833333333333336</v>
       </c>
       <c r="H30" s="18" t="s">
@@ -3442,7 +3488,7 @@
       </c>
       <c r="P30" s="19"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45220</v>
       </c>
@@ -3459,11 +3505,11 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="F31" s="76">
-        <f t="shared" si="0"/>
+        <f>C31/B31</f>
         <v>61.2</v>
       </c>
       <c r="G31" s="76">
-        <f t="shared" si="1"/>
+        <f>B31+C31/100+D31/300</f>
         <v>22.7</v>
       </c>
       <c r="H31" s="3" t="s">
@@ -3488,7 +3534,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45227</v>
       </c>
@@ -3505,11 +3551,11 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="F32" s="76">
-        <f t="shared" si="0"/>
+        <f>C32/B32</f>
         <v>38.235294117647058</v>
       </c>
       <c r="G32" s="76">
-        <f t="shared" si="1"/>
+        <f>B32+C32/100+D32/300</f>
         <v>12.75</v>
       </c>
       <c r="H32" s="3" t="s">
@@ -3534,7 +3580,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45235</v>
       </c>
@@ -3551,11 +3597,11 @@
         <v>0.11805555555555557</v>
       </c>
       <c r="F33" s="76">
-        <f t="shared" si="0"/>
+        <f>C33/B33</f>
         <v>42</v>
       </c>
       <c r="G33" s="76">
-        <f t="shared" si="1"/>
+        <f>B33+C33/100+D33/300</f>
         <v>23.400000000000002</v>
       </c>
       <c r="H33" s="3" t="s">
@@ -3580,7 +3626,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45339</v>
       </c>
@@ -3597,11 +3643,11 @@
         <v>9.7222222222222224E-2</v>
       </c>
       <c r="F34" s="76">
-        <f t="shared" ref="F34:F72" si="2">C34/B34</f>
+        <f>C34/B34</f>
         <v>63.529411764705884</v>
       </c>
       <c r="G34" s="76">
-        <f t="shared" ref="G34:G72" si="3">B34+C34/100+D34/300</f>
+        <f>B34+C34/100+D34/300</f>
         <v>15.700000000000001</v>
       </c>
       <c r="H34" s="3" t="s">
@@ -3626,7 +3672,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45347</v>
       </c>
@@ -3643,11 +3689,11 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F35" s="76">
-        <f t="shared" si="2"/>
+        <f>C35/B35</f>
         <v>75</v>
       </c>
       <c r="G35" s="76">
-        <f t="shared" si="3"/>
+        <f>B35+C35/100+D35/300</f>
         <v>16</v>
       </c>
       <c r="H35" s="3" t="s">
@@ -3675,7 +3721,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45374</v>
       </c>
@@ -3692,11 +3738,11 @@
         <v>0.25</v>
       </c>
       <c r="F36" s="76">
-        <f t="shared" si="2"/>
+        <f>C36/B36</f>
         <v>34.782608695652172</v>
       </c>
       <c r="G36" s="76">
-        <f t="shared" si="3"/>
+        <f>B36+C36/100+D36/300</f>
         <v>33.666666666666664</v>
       </c>
       <c r="H36" s="3" t="s">
@@ -3721,7 +3767,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45388</v>
       </c>
@@ -3738,11 +3784,11 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="F37" s="76">
-        <f t="shared" si="2"/>
+        <f>C37/B37</f>
         <v>30</v>
       </c>
       <c r="G37" s="76">
-        <f t="shared" si="3"/>
+        <f>B37+C37/100+D37/300</f>
         <v>21</v>
       </c>
       <c r="H37" s="3" t="s">
@@ -3767,7 +3813,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>45416</v>
       </c>
@@ -3784,11 +3830,11 @@
         <v>0.375</v>
       </c>
       <c r="F38" s="79">
-        <f t="shared" si="2"/>
+        <f>C38/B38</f>
         <v>51.785714285714285</v>
       </c>
       <c r="G38" s="79">
-        <f t="shared" si="3"/>
+        <f>B38+C38/100+D38/300</f>
         <v>46.166666666666664</v>
       </c>
       <c r="H38" s="22" t="s">
@@ -3819,7 +3865,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>45417</v>
       </c>
@@ -3836,11 +3882,11 @@
         <v>0.375</v>
       </c>
       <c r="F39" s="79">
-        <f t="shared" si="2"/>
+        <f>C39/B39</f>
         <v>29.62962962962963</v>
       </c>
       <c r="G39" s="79">
-        <f t="shared" si="3"/>
+        <f>B39+C39/100+D39/300</f>
         <v>38</v>
       </c>
       <c r="H39" s="22" t="s">
@@ -3869,7 +3915,7 @@
       </c>
       <c r="P39" s="23"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>45418</v>
       </c>
@@ -3886,11 +3932,11 @@
         <v>0.375</v>
       </c>
       <c r="F40" s="79">
-        <f t="shared" si="2"/>
+        <f>C40/B40</f>
         <v>41.666666666666664</v>
       </c>
       <c r="G40" s="79">
-        <f t="shared" si="3"/>
+        <f>B40+C40/100+D40/300</f>
         <v>47.5</v>
       </c>
       <c r="H40" s="22" t="s">
@@ -3919,7 +3965,7 @@
       </c>
       <c r="P40" s="23"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="24">
         <v>45420</v>
       </c>
@@ -3936,11 +3982,11 @@
         <v>0.375</v>
       </c>
       <c r="F41" s="80">
-        <f t="shared" si="2"/>
+        <f>C41/B41</f>
         <v>43.18181818181818</v>
       </c>
       <c r="G41" s="80">
-        <f t="shared" si="3"/>
+        <f>B41+C41/100+D41/300</f>
         <v>34</v>
       </c>
       <c r="H41" s="26" t="s">
@@ -3971,7 +4017,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="24">
         <v>45421</v>
       </c>
@@ -3988,11 +4034,11 @@
         <v>0.5</v>
       </c>
       <c r="F42" s="80">
-        <f t="shared" si="2"/>
+        <f>C42/B42</f>
         <v>48.07692307692308</v>
       </c>
       <c r="G42" s="80">
-        <f t="shared" si="3"/>
+        <f>B42+C42/100+D42/300</f>
         <v>41.5</v>
       </c>
       <c r="H42" s="26" t="s">
@@ -4021,7 +4067,7 @@
       </c>
       <c r="P42" s="27"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="24">
         <v>45422</v>
       </c>
@@ -4038,11 +4084,11 @@
         <v>0.40625</v>
       </c>
       <c r="F43" s="80">
-        <f t="shared" si="2"/>
+        <f>C43/B43</f>
         <v>36.363636363636367</v>
       </c>
       <c r="G43" s="80">
-        <f t="shared" si="3"/>
+        <f>B43+C43/100+D43/300</f>
         <v>33.666666666666664</v>
       </c>
       <c r="H43" s="26" t="s">
@@ -4071,7 +4117,7 @@
       </c>
       <c r="P43" s="27"/>
     </row>
-    <row r="44" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="24">
         <v>45423</v>
       </c>
@@ -4088,11 +4134,11 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="F44" s="80">
-        <f t="shared" si="2"/>
+        <f>C44/B44</f>
         <v>61.904761904761905</v>
       </c>
       <c r="G44" s="80">
-        <f t="shared" si="3"/>
+        <f>B44+C44/100+D44/300</f>
         <v>37.833333333333336</v>
       </c>
       <c r="H44" s="26" t="s">
@@ -4121,7 +4167,7 @@
       </c>
       <c r="P44" s="27"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="24">
         <v>45424</v>
       </c>
@@ -4138,11 +4184,11 @@
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="F45" s="80">
-        <f t="shared" si="2"/>
+        <f>C45/B45</f>
         <v>1.4285714285714286</v>
       </c>
       <c r="G45" s="80">
-        <f t="shared" si="3"/>
+        <f>B45+C45/100+D45/300</f>
         <v>8.1</v>
       </c>
       <c r="H45" s="26" t="s">
@@ -4171,7 +4217,7 @@
       </c>
       <c r="P45" s="27"/>
     </row>
-    <row r="46" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>45446</v>
       </c>
@@ -4188,11 +4234,11 @@
         <v>0.34375</v>
       </c>
       <c r="F46" s="81">
-        <f t="shared" si="2"/>
+        <f>C46/B46</f>
         <v>82.397003745318358</v>
       </c>
       <c r="G46" s="81">
-        <f t="shared" si="3"/>
+        <f>B46+C46/100+D46/300</f>
         <v>52.866666666666667</v>
       </c>
       <c r="H46" s="35" t="s">
@@ -4223,7 +4269,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>45447</v>
       </c>
@@ -4240,11 +4286,11 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="F47" s="81">
-        <f t="shared" si="2"/>
+        <f>C47/B47</f>
         <v>64.10891089108911</v>
       </c>
       <c r="G47" s="81">
-        <f t="shared" si="3"/>
+        <f>B47+C47/100+D47/300</f>
         <v>75.333333333333329</v>
       </c>
       <c r="H47" s="35" t="s">
@@ -4273,7 +4319,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>45448</v>
       </c>
@@ -4290,11 +4336,11 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="F48" s="81">
-        <f t="shared" si="2"/>
+        <f>C48/B48</f>
         <v>63.66459627329192</v>
       </c>
       <c r="G48" s="81">
-        <f t="shared" si="3"/>
+        <f>B48+C48/100+D48/300</f>
         <v>60.6</v>
       </c>
       <c r="H48" s="35" t="s">
@@ -4323,7 +4369,7 @@
       </c>
       <c r="P48" s="36"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>45449</v>
       </c>
@@ -4340,11 +4386,11 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="F49" s="81">
-        <f t="shared" si="2"/>
+        <f>C49/B49</f>
         <v>50.295857988165686</v>
       </c>
       <c r="G49" s="81">
-        <f t="shared" si="3"/>
+        <f>B49+C49/100+D49/300</f>
         <v>55.099999999999994</v>
       </c>
       <c r="H49" s="35" t="s">
@@ -4375,7 +4421,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>45535</v>
       </c>
@@ -4392,11 +4438,11 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="F50" s="82">
-        <f t="shared" si="2"/>
+        <f>C50/B50</f>
         <v>63.829787234042556</v>
       </c>
       <c r="G50" s="82">
-        <f t="shared" si="3"/>
+        <f>B50+C50/100+D50/300</f>
         <v>43</v>
       </c>
       <c r="H50" s="37" t="s">
@@ -4427,7 +4473,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>45536</v>
       </c>
@@ -4444,11 +4490,11 @@
         <v>0.35069444444444442</v>
       </c>
       <c r="F51" s="82">
-        <f t="shared" si="2"/>
+        <f>C51/B51</f>
         <v>62.5</v>
       </c>
       <c r="G51" s="82">
-        <f t="shared" si="3"/>
+        <f>B51+C51/100+D51/300</f>
         <v>36.5</v>
       </c>
       <c r="H51" s="37" t="s">
@@ -4477,7 +4523,7 @@
       </c>
       <c r="P51" s="38"/>
     </row>
-    <row r="52" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>45537</v>
       </c>
@@ -4494,11 +4540,11 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="F52" s="82">
-        <f t="shared" si="2"/>
+        <f>C52/B52</f>
         <v>0</v>
       </c>
       <c r="G52" s="82">
-        <f t="shared" si="3"/>
+        <f>B52+C52/100+D52/300</f>
         <v>7.333333333333333</v>
       </c>
       <c r="H52" s="37" t="s">
@@ -4527,7 +4573,7 @@
       </c>
       <c r="P52" s="38"/>
     </row>
-    <row r="53" spans="1:16" s="45" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="42">
         <v>45540</v>
       </c>
@@ -4544,11 +4590,11 @@
         <v>0.59375</v>
       </c>
       <c r="F53" s="83">
-        <f t="shared" si="2"/>
+        <f>C53/B53</f>
         <v>28.244274809160306</v>
       </c>
       <c r="G53" s="83">
-        <f t="shared" si="3"/>
+        <f>B53+C53/100+D53/300</f>
         <v>89.666666666666671</v>
       </c>
       <c r="H53" s="44" t="s">
@@ -4579,7 +4625,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="42">
         <v>45542</v>
       </c>
@@ -4596,11 +4642,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F54" s="76">
-        <f t="shared" si="2"/>
+        <f>C54/B54</f>
         <v>27.72972972972973</v>
       </c>
       <c r="G54" s="76">
-        <f t="shared" si="3"/>
+        <f>B54+C54/100+D54/300</f>
         <v>25.34</v>
       </c>
       <c r="H54" s="44" t="s">
@@ -4628,7 +4674,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="47">
         <v>45556</v>
       </c>
@@ -4645,11 +4691,11 @@
         <v>0.4375</v>
       </c>
       <c r="F55" s="84">
-        <f t="shared" si="2"/>
+        <f>C55/B55</f>
         <v>49.859154929577464</v>
       </c>
       <c r="G55" s="84">
-        <f t="shared" si="3"/>
+        <f>B55+C55/100+D55/300</f>
         <v>55.466666666666669</v>
       </c>
       <c r="H55" s="50" t="s">
@@ -4680,7 +4726,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="47">
         <v>45557</v>
       </c>
@@ -4697,11 +4743,11 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="F56" s="84">
-        <f t="shared" si="2"/>
+        <f>C56/B56</f>
         <v>12.956810631229235</v>
       </c>
       <c r="G56" s="84">
-        <f t="shared" si="3"/>
+        <f>B56+C56/100+D56/300</f>
         <v>37.799999999999997</v>
       </c>
       <c r="H56" s="50" t="s">
@@ -4730,7 +4776,7 @@
       </c>
       <c r="P56" s="51"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="52">
         <v>45562</v>
       </c>
@@ -4747,11 +4793,11 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="F57" s="85">
-        <f t="shared" si="2"/>
+        <f>C57/B57</f>
         <v>107.92291220556744</v>
       </c>
       <c r="G57" s="85">
-        <f t="shared" si="3"/>
+        <f>B57+C57/100+D57/300</f>
         <v>54.416666666666664</v>
       </c>
       <c r="H57" s="55" t="s">
@@ -4782,7 +4828,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="52">
         <v>45563</v>
       </c>
@@ -4799,11 +4845,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F58" s="85">
-        <f t="shared" si="2"/>
+        <f>C58/B58</f>
         <v>44.444444444444443</v>
       </c>
       <c r="G58" s="85">
-        <f t="shared" si="3"/>
+        <f>B58+C58/100+D58/300</f>
         <v>45.533333333333331</v>
       </c>
       <c r="H58" s="55" t="s">
@@ -4832,7 +4878,7 @@
       </c>
       <c r="P58" s="56"/>
     </row>
-    <row r="59" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="57">
         <v>45597</v>
       </c>
@@ -4849,11 +4895,11 @@
         <v>0.22916666666666666</v>
       </c>
       <c r="F59" s="86">
-        <f t="shared" si="2"/>
+        <f>C59/B59</f>
         <v>34.677419354838712</v>
       </c>
       <c r="G59" s="86">
-        <f t="shared" si="3"/>
+        <f>B59+C59/100+D59/300</f>
         <v>35.233333333333334</v>
       </c>
       <c r="H59" s="59" t="s">
@@ -4884,7 +4930,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="57">
         <v>45598</v>
       </c>
@@ -4901,11 +4947,11 @@
         <v>0.4375</v>
       </c>
       <c r="F60" s="86">
-        <f t="shared" si="2"/>
+        <f>C60/B60</f>
         <v>22.327790973871732</v>
       </c>
       <c r="G60" s="86">
-        <f t="shared" si="3"/>
+        <f>B60+C60/100+D60/300</f>
         <v>54.266666666666666</v>
       </c>
       <c r="H60" s="59" t="s">
@@ -4934,7 +4980,7 @@
       </c>
       <c r="P60" s="60"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="57">
         <v>45599</v>
       </c>
@@ -4951,11 +4997,11 @@
         <v>0.46875</v>
       </c>
       <c r="F61" s="86">
-        <f t="shared" si="2"/>
+        <f>C61/B61</f>
         <v>24.744376278118612</v>
       </c>
       <c r="G61" s="86">
-        <f t="shared" si="3"/>
+        <f>B61+C61/100+D61/300</f>
         <v>64.86666666666666</v>
       </c>
       <c r="H61" s="59" t="s">
@@ -4984,7 +5030,7 @@
       </c>
       <c r="P61" s="60"/>
     </row>
-    <row r="62" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="57">
         <v>45600</v>
       </c>
@@ -5001,11 +5047,11 @@
         <v>0.46527777777777773</v>
       </c>
       <c r="F62" s="86">
-        <f t="shared" si="2"/>
+        <f>C62/B62</f>
         <v>34.311512415349888</v>
       </c>
       <c r="G62" s="86">
-        <f t="shared" si="3"/>
+        <f>B62+C62/100+D62/300</f>
         <v>63.266666666666666</v>
       </c>
       <c r="H62" s="59" t="s">
@@ -5034,7 +5080,7 @@
       </c>
       <c r="P62" s="60"/>
     </row>
-    <row r="63" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="57">
         <v>45601</v>
       </c>
@@ -5051,11 +5097,11 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="F63" s="86">
-        <f t="shared" si="2"/>
+        <f>C63/B63</f>
         <v>21.535181236673775</v>
       </c>
       <c r="G63" s="86">
-        <f t="shared" si="3"/>
+        <f>B63+C63/100+D63/300</f>
         <v>62.933333333333337</v>
       </c>
       <c r="H63" s="59" t="s">
@@ -5084,7 +5130,7 @@
       </c>
       <c r="P63" s="60"/>
     </row>
-    <row r="64" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="57">
         <v>45602</v>
       </c>
@@ -5101,11 +5147,11 @@
         <v>0.47569444444444442</v>
       </c>
       <c r="F64" s="86">
-        <f t="shared" si="2"/>
+        <f>C64/B64</f>
         <v>25.902335456475583</v>
       </c>
       <c r="G64" s="86">
-        <f t="shared" si="3"/>
+        <f>B64+C64/100+D64/300</f>
         <v>64.86666666666666</v>
       </c>
       <c r="H64" s="59" t="s">
@@ -5136,7 +5182,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="57">
         <v>45603</v>
       </c>
@@ -5153,11 +5199,11 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F65" s="86">
-        <f t="shared" si="2"/>
+        <f>C65/B65</f>
         <v>31.914893617021278</v>
       </c>
       <c r="G65" s="86">
-        <f t="shared" si="3"/>
+        <f>B65+C65/100+D65/300</f>
         <v>33.9</v>
       </c>
       <c r="H65" s="59" t="s">
@@ -5186,7 +5232,7 @@
       </c>
       <c r="P65" s="60"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>45641</v>
       </c>
@@ -5203,11 +5249,11 @@
         <v>0.19444444444444445</v>
       </c>
       <c r="F66" s="76">
-        <f t="shared" si="2"/>
+        <f>C66/B66</f>
         <v>89.361702127659569</v>
       </c>
       <c r="G66" s="76">
-        <f t="shared" si="3"/>
+        <f>B66+C66/100+D66/300</f>
         <v>20.6</v>
       </c>
       <c r="H66" s="3" t="s">
@@ -5235,7 +5281,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>45660</v>
       </c>
@@ -5252,11 +5298,11 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F67" s="76">
-        <f t="shared" si="2"/>
+        <f>C67/B67</f>
         <v>38.095238095238095</v>
       </c>
       <c r="G67" s="76">
-        <f t="shared" si="3"/>
+        <f>B67+C67/100+D67/300</f>
         <v>31.666666666666668</v>
       </c>
       <c r="H67" s="3" t="s">
@@ -5287,7 +5333,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>45675</v>
       </c>
@@ -5304,11 +5350,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="F68" s="76">
-        <f t="shared" si="2"/>
+        <f>C68/B68</f>
         <v>72.794117647058826</v>
       </c>
       <c r="G68" s="76">
-        <f t="shared" si="3"/>
+        <f>B68+C68/100+D68/300</f>
         <v>53.6</v>
       </c>
       <c r="H68" s="3" t="s">
@@ -5336,7 +5382,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>45689</v>
       </c>
@@ -5353,11 +5399,11 @@
         <v>6.25E-2</v>
       </c>
       <c r="F69" s="78">
-        <f t="shared" si="2"/>
+        <f>C69/B69</f>
         <v>137.73584905660377</v>
       </c>
       <c r="G69" s="78">
-        <f t="shared" si="3"/>
+        <f>B69+C69/100+D69/300</f>
         <v>12.666666666666666</v>
       </c>
       <c r="H69" s="18" t="s">
@@ -5386,7 +5432,7 @@
       </c>
       <c r="P69" s="19"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>45689</v>
       </c>
@@ -5403,11 +5449,11 @@
         <v>0.25</v>
       </c>
       <c r="F70" s="78">
-        <f t="shared" si="2"/>
+        <f>C70/B70</f>
         <v>39.698492462311563</v>
       </c>
       <c r="G70" s="78">
-        <f t="shared" si="3"/>
+        <f>B70+C70/100+D70/300</f>
         <v>32.799999999999997</v>
       </c>
       <c r="H70" s="18" t="s">
@@ -5436,7 +5482,7 @@
       </c>
       <c r="P70" s="19"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>45697</v>
       </c>
@@ -5453,11 +5499,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F71" s="76">
-        <f t="shared" si="2"/>
+        <f>C71/B71</f>
         <v>56.79012345679012</v>
       </c>
       <c r="G71" s="76">
-        <f t="shared" si="3"/>
+        <f>B71+C71/100+D71/300</f>
         <v>42.7</v>
       </c>
       <c r="H71" s="3" t="s">
@@ -5485,7 +5531,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="90">
         <v>45703</v>
       </c>
@@ -5502,11 +5548,11 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="F72" s="91">
-        <f t="shared" si="2"/>
+        <f>C72/B72</f>
         <v>85.714285714285708</v>
       </c>
       <c r="G72" s="91">
-        <f t="shared" si="3"/>
+        <f>B72+C72/100+D72/300</f>
         <v>14</v>
       </c>
       <c r="H72" s="93" t="s">
@@ -5537,7 +5583,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="90">
         <v>45704</v>
       </c>
@@ -5554,11 +5600,11 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="F73" s="91">
-        <f t="shared" ref="F73" si="4">C73/B73</f>
+        <f>C73/B73</f>
         <v>57.142857142857146</v>
       </c>
       <c r="G73" s="91">
-        <f t="shared" ref="G73" si="5">B73+C73/100+D73/300</f>
+        <f>B73+C73/100+D73/300</f>
         <v>13.333333333333334</v>
       </c>
       <c r="H73" s="93" t="s">
@@ -5588,8 +5634,8 @@
       <c r="P73" s="95"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P70">
-    <sortState ref="A2:P70">
+  <autoFilter ref="A1:P70" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P70">
       <sortCondition ref="A1:A65"/>
     </sortState>
   </autoFilter>
@@ -5599,17 +5645,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
@@ -5623,7 +5669,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
@@ -5638,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>38</v>
       </c>
@@ -5653,7 +5699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>199</v>
       </c>
@@ -5668,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -5683,7 +5729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -5698,7 +5744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>34</v>
       </c>
@@ -5713,7 +5759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>40</v>
       </c>
@@ -5728,7 +5774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>188</v>
       </c>
@@ -5743,7 +5789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>134</v>
       </c>
@@ -5758,7 +5804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>83</v>
       </c>
@@ -5773,7 +5819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>96</v>
       </c>
@@ -5788,7 +5834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>97</v>
       </c>
@@ -5803,7 +5849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>85</v>
       </c>
@@ -5818,7 +5864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>91</v>
       </c>
@@ -5833,7 +5879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>186</v>
       </c>
@@ -5848,7 +5894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>234</v>
       </c>
@@ -5863,7 +5909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>84</v>
       </c>
@@ -5878,7 +5924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>92</v>
       </c>
@@ -5893,7 +5939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>90</v>
       </c>
@@ -5908,7 +5954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>81</v>
       </c>
@@ -5923,7 +5969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>89</v>
       </c>
@@ -5938,7 +5984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>88</v>
       </c>
@@ -5953,7 +5999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>187</v>
       </c>
@@ -5968,7 +6014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>270</v>
       </c>
@@ -5983,7 +6029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>343</v>
       </c>
@@ -5998,7 +6044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>385</v>
       </c>
@@ -6013,39 +6059,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D28" s="15"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D29" s="15"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D30" s="15"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D31" s="15"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D32" s="15"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33" s="15"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35" s="15"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D36" s="15"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D37" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D18">
-    <sortState ref="A2:D24">
+  <autoFilter ref="A1:D18" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D24">
       <sortCondition ref="D1:D18"/>
     </sortState>
   </autoFilter>
@@ -6072,15 +6118,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
@@ -6088,7 +6134,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>292</v>
       </c>
@@ -6096,7 +6142,7 @@
         <v>3172</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>293</v>
       </c>
@@ -6104,7 +6150,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>294</v>
       </c>
@@ -6112,7 +6158,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>295</v>
       </c>
@@ -6120,7 +6166,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>296</v>
       </c>
@@ -6128,7 +6174,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>297</v>
       </c>
@@ -6136,7 +6182,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>133</v>
       </c>
@@ -6144,7 +6190,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>298</v>
       </c>
@@ -6152,7 +6198,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>299</v>
       </c>
@@ -6160,7 +6206,7 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>313</v>
       </c>
@@ -6168,7 +6214,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>324</v>
       </c>
@@ -6176,7 +6222,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>320</v>
       </c>
@@ -6184,7 +6230,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>325</v>
       </c>
@@ -6192,7 +6238,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>314</v>
       </c>
@@ -6200,7 +6246,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>315</v>
       </c>
@@ -6208,7 +6254,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>326</v>
       </c>
@@ -6216,7 +6262,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>316</v>
       </c>
@@ -6224,7 +6270,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>321</v>
       </c>
@@ -6232,7 +6278,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>327</v>
       </c>
@@ -6240,7 +6286,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>198</v>
       </c>
@@ -6248,7 +6294,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>317</v>
       </c>
@@ -6256,7 +6302,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>318</v>
       </c>
@@ -6264,7 +6310,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>323</v>
       </c>
@@ -6272,7 +6318,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>322</v>
       </c>
@@ -6280,7 +6326,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>328</v>
       </c>
@@ -6288,7 +6334,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>319</v>
       </c>
@@ -6296,7 +6342,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>329</v>
       </c>
@@ -6304,7 +6350,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>300</v>
       </c>
@@ -6312,7 +6358,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>301</v>
       </c>
@@ -6320,7 +6366,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>131</v>
       </c>
@@ -6328,7 +6374,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>330</v>
       </c>
@@ -6336,7 +6382,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>132</v>
       </c>
@@ -6344,7 +6390,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>302</v>
       </c>
@@ -6352,7 +6398,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>303</v>
       </c>
@@ -6360,7 +6406,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>331</v>
       </c>
@@ -6368,7 +6414,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>333</v>
       </c>
@@ -6376,7 +6422,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>332</v>
       </c>
@@ -6384,7 +6430,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>304</v>
       </c>
@@ -6392,7 +6438,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>305</v>
       </c>
@@ -6400,7 +6446,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>334</v>
       </c>
@@ -6408,7 +6454,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>335</v>
       </c>
@@ -6416,7 +6462,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>337</v>
       </c>
@@ -6424,7 +6470,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>336</v>
       </c>
@@ -6432,7 +6478,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>302</v>
       </c>
@@ -6440,7 +6486,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>306</v>
       </c>
@@ -6448,7 +6494,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>307</v>
       </c>
@@ -6456,7 +6502,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>308</v>
       </c>
@@ -6464,7 +6510,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>309</v>
       </c>
@@ -6472,7 +6518,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>338</v>
       </c>
@@ -6480,7 +6526,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>310</v>
       </c>
@@ -6488,7 +6534,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>311</v>
       </c>
@@ -6496,7 +6542,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>312</v>
       </c>
@@ -6504,7 +6550,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>339</v>
       </c>
@@ -6512,7 +6558,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>340</v>
       </c>
@@ -6520,7 +6566,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>341</v>
       </c>
@@ -6528,7 +6574,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>385</v>
       </c>
@@ -6537,8 +6583,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5">
-    <sortState ref="A2:B54">
+  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B54">
       <sortCondition descending="1" ref="B1:B5"/>
     </sortState>
   </autoFilter>
@@ -6547,20 +6593,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="4"/>
+    <col min="1" max="1" width="7.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="11.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="12" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="12" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>386</v>
       </c>
@@ -6580,7 +6626,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -6591,7 +6637,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -6602,7 +6648,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -6613,7 +6659,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -6624,7 +6670,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -6635,7 +6681,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -6646,7 +6692,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -6657,7 +6703,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -6668,7 +6714,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>3</v>
       </c>
@@ -6679,7 +6725,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>2</v>
       </c>
@@ -6690,7 +6736,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>2</v>
       </c>
@@ -6701,7 +6747,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>2</v>
       </c>
@@ -6712,7 +6758,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>1</v>
       </c>
@@ -6732,7 +6778,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>3</v>
       </c>
@@ -6743,7 +6789,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>1</v>
       </c>
@@ -6754,7 +6800,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>1</v>
       </c>
@@ -6765,7 +6811,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>3</v>
       </c>
@@ -6776,7 +6822,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>1</v>
       </c>
@@ -6787,7 +6833,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>1</v>
       </c>
@@ -6798,7 +6844,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>2</v>
       </c>
@@ -6809,7 +6855,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>1</v>
       </c>
@@ -6829,7 +6875,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>2</v>
       </c>
@@ -6849,7 +6895,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>1</v>
       </c>
@@ -6869,7 +6915,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>3</v>
       </c>
@@ -6880,7 +6926,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>2</v>
       </c>
@@ -6900,7 +6946,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>3</v>
       </c>
@@ -6911,7 +6957,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>3</v>
       </c>
@@ -6922,7 +6968,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>1</v>
       </c>
@@ -6933,7 +6979,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>2</v>
       </c>
@@ -6944,7 +6990,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>2</v>
       </c>
@@ -6958,7 +7004,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>2</v>
       </c>
@@ -6969,7 +7015,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>3</v>
       </c>
@@ -6989,7 +7035,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>2</v>
       </c>
@@ -7003,7 +7049,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>1</v>
       </c>
@@ -7014,7 +7060,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>3</v>
       </c>
@@ -7025,7 +7071,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>2</v>
       </c>
@@ -7045,7 +7091,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>1</v>
       </c>
@@ -7065,7 +7111,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>2</v>
       </c>
@@ -7076,7 +7122,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>3</v>
       </c>
@@ -7087,7 +7133,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>1</v>
       </c>
@@ -7098,7 +7144,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>2</v>
       </c>
@@ -7109,7 +7155,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>2</v>
       </c>
@@ -7120,7 +7166,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>2</v>
       </c>
@@ -7132,7 +7178,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F44" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Randonnée.xlsx
+++ b/data/Randonnée.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED5DCE1-28BE-4F98-9817-C8457F4A3119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2730" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Randonnées" sheetId="4" r:id="rId1"/>
@@ -15,27 +14,16 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plus beaux endroits'!$A$1:$D$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Randonnées!$A$1:$P$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Randonnées!$A$1:$O$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sommets!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$F$41</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="444">
   <si>
     <t>Km</t>
   </si>
@@ -421,9 +409,6 @@
     <t>Chalet de la Maline-Moustier par le Grand Margès</t>
   </si>
   <si>
-    <t>2eme trek</t>
-  </si>
-  <si>
     <t>1er trek</t>
   </si>
   <si>
@@ -457,9 +442,6 @@
     <t>3eme trek, 1er accompagné</t>
   </si>
   <si>
-    <t>4eme trek, 1er bivouac</t>
-  </si>
-  <si>
     <t>Chaussures</t>
   </si>
   <si>
@@ -481,9 +463,6 @@
     <t>Terres Noires, Pas de l'Archail et retour vers Digne par l'Archail</t>
   </si>
   <si>
-    <t>PB D+, 2eme 3000m</t>
-  </si>
-  <si>
     <t>PB Alt, 1er 3000m (3172m)</t>
   </si>
   <si>
@@ -619,18 +598,6 @@
     <t>Tour de l'Obiou par le Nord</t>
   </si>
   <si>
-    <t>5eme trek, 1er bivouac solo, 1er abandon</t>
-  </si>
-  <si>
-    <t>6eme trek, 2eme abandon</t>
-  </si>
-  <si>
-    <t>7eme trek</t>
-  </si>
-  <si>
-    <t>8eme trek</t>
-  </si>
-  <si>
     <t>L'Aiguille</t>
   </si>
   <si>
@@ -640,9 +607,6 @@
     <t>Devoluy, Alpes du Nord, France</t>
   </si>
   <si>
-    <t>Grand Veymont</t>
-  </si>
-  <si>
     <t>Mont Ventoux</t>
   </si>
   <si>
@@ -676,9 +640,6 @@
     <t>JM, Bakri</t>
   </si>
   <si>
-    <t>Dernière à Marseille</t>
-  </si>
-  <si>
     <t>Thomas</t>
   </si>
   <si>
@@ -688,9 +649,6 @@
     <t>Mathieu</t>
   </si>
   <si>
-    <t>9eme trek</t>
-  </si>
-  <si>
     <t>GR70 : Chemin de Stevenson</t>
   </si>
   <si>
@@ -775,9 +733,6 @@
     <t>Circuit des 4 Chateaux et Mont Luisange</t>
   </si>
   <si>
-    <t>Première de 2025 et inauguration des Lowa</t>
-  </si>
-  <si>
     <t>La Grande Sure</t>
   </si>
   <si>
@@ -808,15 +763,9 @@
     <t>GR20 - Corse</t>
   </si>
   <si>
-    <t>Le Fort du Saint-Eynard</t>
-  </si>
-  <si>
     <t>GR738 - Haute Traversée de Belledone</t>
   </si>
   <si>
-    <t>D+/Km</t>
-  </si>
-  <si>
     <t>KmEff</t>
   </si>
   <si>
@@ -829,9 +778,6 @@
     <t>Traversée du Vercors : Saint-Nizier - Corrençon</t>
   </si>
   <si>
-    <t>Traversée du Pilat : Givors - Saint-Etienne</t>
-  </si>
-  <si>
     <t>Chartreuse</t>
   </si>
   <si>
@@ -841,9 +787,6 @@
     <t>Aller-retour Bastile - Fort du Saint-Eynard</t>
   </si>
   <si>
-    <t>Première rando neige</t>
-  </si>
-  <si>
     <t>Tour du Plateau d'Emparis</t>
   </si>
   <si>
@@ -853,12 +796,6 @@
     <t>Chartreuse, Alpes du Nord, France</t>
   </si>
   <si>
-    <t>Les Crêts du Pilat</t>
-  </si>
-  <si>
-    <t>GRP - Tour de la Chartreuse</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -874,9 +811,6 @@
     <t>Voreppe - Monastère de Chalais</t>
   </si>
   <si>
-    <t>Aiguille de Chalais et Charmelline</t>
-  </si>
-  <si>
     <t>3000 Haut Giffre : Mont Buet</t>
   </si>
   <si>
@@ -1063,9 +997,6 @@
     <t>Le Grand Colombier</t>
   </si>
   <si>
-    <t>Gorges du Nan</t>
-  </si>
-  <si>
     <t>Le Grand Clombier</t>
   </si>
   <si>
@@ -1087,15 +1018,9 @@
     <t>Rando neige improvisée</t>
   </si>
   <si>
-    <t>Entrainement Ecosse</t>
-  </si>
-  <si>
     <t>Test des nouvelles chaussures</t>
   </si>
   <si>
-    <t>Première fois en raquettes</t>
-  </si>
-  <si>
     <t>Lac des Plagnes au refuge des Tinderets par les chalais de Lens</t>
   </si>
   <si>
@@ -1162,9 +1087,6 @@
     <t>France, Pyrénées</t>
   </si>
   <si>
-    <t>France, Pilat</t>
-  </si>
-  <si>
     <t>France, Mont de Vaucluse</t>
   </si>
   <si>
@@ -1208,12 +1130,237 @@
   </si>
   <si>
     <t>L'Obiou</t>
+  </si>
+  <si>
+    <t>Beaujolais</t>
+  </si>
+  <si>
+    <t>Anse</t>
+  </si>
+  <si>
+    <t>Tarare</t>
+  </si>
+  <si>
+    <t>Anse, Jarnioux, Theizé, Moiré</t>
+  </si>
+  <si>
+    <t>Montagne de Tarare</t>
+  </si>
+  <si>
+    <t>Entrainement Ecosse pour Apo</t>
+  </si>
+  <si>
+    <t>Moiré, Oingt, Ternand, Tarare</t>
+  </si>
+  <si>
+    <t>Boucle Gorges du Nan &amp; la lunette de Malleval depuis Cognin</t>
+  </si>
+  <si>
+    <t>Cognin-les-Gorges, Malleval-en-Vercors</t>
+  </si>
+  <si>
+    <t>Apo, Célia</t>
+  </si>
+  <si>
+    <t>Balade avec Daniel</t>
+  </si>
+  <si>
+    <t>Rocher du Baconnet</t>
+  </si>
+  <si>
+    <t>La Lunette</t>
+  </si>
+  <si>
+    <t>Monts d'Or</t>
+  </si>
+  <si>
+    <t>Poleymieux</t>
+  </si>
+  <si>
+    <t>Boucle autour de Poleymieux</t>
+  </si>
+  <si>
+    <t>Balade vélo + rando</t>
+  </si>
+  <si>
+    <t>Le Mont Thou</t>
+  </si>
+  <si>
+    <t>Le Mont Verdun</t>
+  </si>
+  <si>
+    <t>Le Mont Py</t>
+  </si>
+  <si>
+    <t>Désert de Platé</t>
+  </si>
+  <si>
+    <t>Boucle à la croix du Nivolet depuis Chambéry</t>
+  </si>
+  <si>
+    <t>Bauges</t>
+  </si>
+  <si>
+    <t>Chambéry</t>
+  </si>
+  <si>
+    <t>Le Nivolet</t>
+  </si>
+  <si>
+    <t>France, Jura</t>
+  </si>
+  <si>
+    <t>Grand Veymont &amp; Chaumailloux</t>
+  </si>
+  <si>
+    <t>Le Crêt de la Neige (de Bellegarde à Gex)</t>
+  </si>
+  <si>
+    <t>Gorges du Flumen</t>
+  </si>
+  <si>
+    <t>Chaine des Puys</t>
+  </si>
+  <si>
+    <t>France, Massif Central</t>
+  </si>
+  <si>
+    <t>Flaine : Grandes Platières/Tête du Colonney/Désert de Platé, Bout du Monde, Montagne d'Anterne, Lac de Gers</t>
+  </si>
+  <si>
+    <t>Champagny : Col du Palet/Lac de la Plagne, Becca Motta, La Grande Rochette/lac de Blanchets, Col de la Vanoise</t>
+  </si>
+  <si>
+    <t>Aiguille de Chalais et Charminelle</t>
+  </si>
+  <si>
+    <t>Saint Chamond</t>
+  </si>
+  <si>
+    <t>Les Rcohes de Condrieu</t>
+  </si>
+  <si>
+    <t>De Saint Chamond au Crêt de l'Oeillon par le GR7</t>
+  </si>
+  <si>
+    <t>Descente de l'autre côté par les sentiers et le GR65</t>
+  </si>
+  <si>
+    <t>Les Trois Dents</t>
+  </si>
+  <si>
+    <t>Le Pic du Midi</t>
+  </si>
+  <si>
+    <t>Le Crêt du Rachat</t>
+  </si>
+  <si>
+    <t>Le Crêt de la Chèvre</t>
+  </si>
+  <si>
+    <t>Cols d'Hurtières et de la Sure</t>
+  </si>
+  <si>
+    <t>Le Quichat</t>
+  </si>
+  <si>
+    <t>La Pinéa</t>
+  </si>
+  <si>
+    <t>Le Mollard de la Chaleur</t>
+  </si>
+  <si>
+    <t>Le Rocher de Chalves</t>
+  </si>
+  <si>
+    <t>Le Rocher de Lorzier</t>
+  </si>
+  <si>
+    <t>Sarcenas, Grenoble</t>
+  </si>
+  <si>
+    <t>De Voreppe au refuge d'Hurtière + La grande Sure</t>
+  </si>
+  <si>
+    <t>Du refuge à Grenoble par la Pinéa et le Quichat</t>
+  </si>
+  <si>
+    <t>Traversée Ouest-Est du Pilat</t>
+  </si>
+  <si>
+    <t>Traversée du Bas Beaujolais</t>
+  </si>
+  <si>
+    <t>Traversée Nord-Sud du Pilat</t>
+  </si>
+  <si>
+    <t>Le Petit Som</t>
+  </si>
+  <si>
+    <t>Cirque de Saint Meme</t>
+  </si>
+  <si>
+    <t>Col de l'Emeindras</t>
+  </si>
+  <si>
+    <t>Grenoble, Sappey en Chartreuse</t>
+  </si>
+  <si>
+    <t>Saint Pierre de Chartreuse</t>
+  </si>
+  <si>
+    <t>Chambery</t>
+  </si>
+  <si>
+    <t>Saint Pierre d'Entremont</t>
+  </si>
+  <si>
+    <t>De Grenoble au col de l'Emeindra, par le Saint Eynard et le Sappey</t>
+  </si>
+  <si>
+    <t>Jusqu'au Habert de Bovinant par St Pierre en Chartreuse et le Monastère</t>
+  </si>
+  <si>
+    <t>Jusqu'à St Piere d'Entremont avec détour par le cirque de Saint Même</t>
+  </si>
+  <si>
+    <t>Descente à Chambéry</t>
+  </si>
+  <si>
+    <t>07:30;00</t>
+  </si>
+  <si>
+    <t>1er rando neige</t>
+  </si>
+  <si>
+    <t>1er bivouac avec Apo</t>
+  </si>
+  <si>
+    <t>2000 Km, 100K D+</t>
+  </si>
+  <si>
+    <t>10eme trek</t>
+  </si>
+  <si>
+    <t>1er bivouac</t>
+  </si>
+  <si>
+    <t>1er bivouac solo</t>
+  </si>
+  <si>
+    <t>Traversée de la Chartreuse (GRP)</t>
+  </si>
+  <si>
+    <t>1er raquettes</t>
+  </si>
+  <si>
+    <t>500h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[h]:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1259,7 +1406,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1335,6 +1482,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1454,7 +1625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1652,6 +1823,43 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1696,13 +1904,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFC3E7CE"/>
       <color rgb="FFE1C4B9"/>
       <color rgb="FFDDA89F"/>
       <color rgb="FFDDEEEF"/>
       <color rgb="FFFFE1FF"/>
       <color rgb="FFFFCCFF"/>
-      <color rgb="FFFFFF99"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1792,23 +2000,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1844,23 +2035,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2036,29 +2210,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O86"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="76" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="76" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="76" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.28515625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="27.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="29.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="45.85546875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="29.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="76" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="76" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="27.21875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="29.77734375" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="57.77734375" style="10" customWidth="1"/>
+    <col min="13" max="13" width="29.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.77734375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="74" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="74" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -2075,40 +2248,37 @@
         <v>1</v>
       </c>
       <c r="F1" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="G1" s="75" t="s">
-        <v>260</v>
-      </c>
-      <c r="H1" s="70" t="s">
-        <v>141</v>
+        <v>247</v>
+      </c>
+      <c r="G1" s="70" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>42</v>
       </c>
       <c r="I1" s="71" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J1" s="71" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="72" t="s">
+      <c r="K1" s="72" t="s">
         <v>3</v>
       </c>
+      <c r="L1" s="73" t="s">
+        <v>5</v>
+      </c>
       <c r="M1" s="73" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="N1" s="73" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="O1" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="P1" s="73" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>44997</v>
       </c>
@@ -2125,33 +2295,29 @@
         <v>0.15972222222222224</v>
       </c>
       <c r="F2" s="76">
-        <f>C2/B2</f>
-        <v>58.477096966091615</v>
-      </c>
-      <c r="G2" s="76">
-        <f>B2+C2/100+D2/300</f>
+        <f t="shared" ref="F2:F33" si="0">B2+C2/100+D2/300</f>
         <v>29.916666666666668</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="H2" s="3" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="61" t="s">
+      <c r="K2" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45010</v>
       </c>
@@ -2168,33 +2334,29 @@
         <v>0.4375</v>
       </c>
       <c r="F3" s="76">
-        <f>C3/B3</f>
-        <v>56.708860759493668</v>
-      </c>
-      <c r="G3" s="76">
-        <f>B3+C3/100+D3/300</f>
+        <f t="shared" si="0"/>
         <v>69.36666666666666</v>
       </c>
+      <c r="G3" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="61" t="s">
+      <c r="K3" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="N3" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45011</v>
       </c>
@@ -2211,33 +2373,29 @@
         <v>0.15972222222222224</v>
       </c>
       <c r="F4" s="76">
-        <f>C4/B4</f>
-        <v>42.788844621513945</v>
-      </c>
-      <c r="G4" s="76">
-        <f>B4+C4/100+D4/300</f>
+        <f t="shared" si="0"/>
         <v>19.71</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H4" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="61" t="s">
+      <c r="K4" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45017</v>
       </c>
@@ -2254,33 +2412,29 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="76">
-        <f>C5/B5</f>
-        <v>48.152424942263281</v>
-      </c>
-      <c r="G5" s="76">
-        <f>B5+C5/100+D5/300</f>
+        <f t="shared" si="0"/>
         <v>28.44</v>
       </c>
+      <c r="G5" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L5" s="61" t="s">
+      <c r="K5" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="O5" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N5" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45038</v>
       </c>
@@ -2297,30 +2451,26 @@
         <v>0.25</v>
       </c>
       <c r="F6" s="76">
-        <f>C6/B6</f>
-        <v>53.333333333333336</v>
-      </c>
-      <c r="G6" s="76">
-        <f>B6+C6/100+D6/300</f>
+        <f t="shared" si="0"/>
         <v>25.666666666666668</v>
       </c>
+      <c r="G6" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="H6" s="3" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="O6" s="10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N6" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45039</v>
       </c>
@@ -2337,33 +2487,29 @@
         <v>0.1875</v>
       </c>
       <c r="F7" s="76">
-        <f>C7/B7</f>
-        <v>49.567567567567565</v>
-      </c>
-      <c r="G7" s="76">
-        <f>B7+C7/100+D7/300</f>
+        <f t="shared" si="0"/>
         <v>30.726666666666667</v>
       </c>
+      <c r="G7" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H7" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="K7" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="N7" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45060</v>
       </c>
@@ -2380,33 +2526,29 @@
         <v>0.1875</v>
       </c>
       <c r="F8" s="76">
-        <f>C8/B8</f>
-        <v>54.384017758046618</v>
-      </c>
-      <c r="G8" s="76">
-        <f>B8+C8/100+D8/300</f>
+        <f t="shared" si="0"/>
         <v>31.086666666666666</v>
       </c>
+      <c r="G8" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H8" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="61" t="s">
+      <c r="K8" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="N8" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45073</v>
       </c>
@@ -2423,33 +2565,29 @@
         <v>0.34722222222222227</v>
       </c>
       <c r="F9" s="76">
-        <f>C9/B9</f>
-        <v>65.704918032786878</v>
-      </c>
-      <c r="G9" s="76">
-        <f>B9+C9/100+D9/300</f>
+        <f t="shared" si="0"/>
         <v>57.22</v>
       </c>
+      <c r="G9" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H9" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L9" s="61" t="s">
+      <c r="K9" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="N9" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45074</v>
       </c>
@@ -2466,33 +2604,29 @@
         <v>0.125</v>
       </c>
       <c r="F10" s="76">
-        <f>C10/B10</f>
-        <v>44.846153846153847</v>
-      </c>
-      <c r="G10" s="76">
-        <f>B10+C10/100+D10/300</f>
+        <f t="shared" si="0"/>
         <v>20.773333333333333</v>
       </c>
+      <c r="G10" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H10" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="61" t="s">
+      <c r="K10" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="O10" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N10" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45080</v>
       </c>
@@ -2509,33 +2643,29 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="F11" s="76">
-        <f>C11/B11</f>
-        <v>122.22222222222223</v>
-      </c>
-      <c r="G11" s="76">
-        <f>B11+C11/100+D11/300</f>
+        <f t="shared" si="0"/>
         <v>11.833333333333334</v>
       </c>
+      <c r="G11" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H11" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L11" s="61" t="s">
+      <c r="K11" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="N11" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>45108</v>
       </c>
@@ -2552,42 +2682,38 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="F12" s="77">
-        <f>C12/B12</f>
-        <v>59.785407725321889</v>
-      </c>
-      <c r="G12" s="77">
-        <f>B12+C12/100+D12/300</f>
+        <f t="shared" si="0"/>
         <v>40.076666666666668</v>
       </c>
+      <c r="G12" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H12" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="K12" s="32" t="s">
         <v>35</v>
       </c>
+      <c r="L12" s="31" t="s">
+        <v>10</v>
+      </c>
       <c r="M12" s="31" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="O12" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="P12" s="31" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>45109</v>
       </c>
@@ -2604,42 +2730,38 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F13" s="77">
-        <f>C13/B13</f>
-        <v>114.23645320197043</v>
-      </c>
-      <c r="G13" s="77">
-        <f>B13+C13/100+D13/300</f>
+        <f t="shared" si="0"/>
         <v>48.006666666666668</v>
       </c>
+      <c r="G13" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H13" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="L13" s="32" t="s">
+      <c r="K13" s="32" t="s">
         <v>66</v>
       </c>
+      <c r="L13" s="31" t="s">
+        <v>16</v>
+      </c>
       <c r="M13" s="31" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="O13" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="P13" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="28">
         <v>45110</v>
       </c>
@@ -2656,40 +2778,36 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="F14" s="77">
-        <f>C14/B14</f>
-        <v>56.846590909090907</v>
-      </c>
-      <c r="G14" s="77">
-        <f>B14+C14/100+D14/300</f>
+        <f t="shared" si="0"/>
         <v>62.603333333333339</v>
       </c>
+      <c r="G14" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H14" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="L14" s="32" t="s">
+      <c r="K14" s="32" t="s">
         <v>67</v>
       </c>
+      <c r="L14" s="31" t="s">
+        <v>29</v>
+      </c>
       <c r="M14" s="31" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="P14" s="31"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O14" s="31"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="28">
         <v>45111</v>
       </c>
@@ -2706,40 +2824,36 @@
         <v>0.375</v>
       </c>
       <c r="F15" s="77">
-        <f>C15/B15</f>
-        <v>63.792048929663601</v>
-      </c>
-      <c r="G15" s="77">
-        <f>B15+C15/100+D15/300</f>
+        <f t="shared" si="0"/>
         <v>59.363333333333337</v>
       </c>
+      <c r="G15" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H15" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="L15" s="32" t="s">
+      <c r="K15" s="32" t="s">
         <v>69</v>
       </c>
+      <c r="L15" s="31" t="s">
+        <v>30</v>
+      </c>
       <c r="M15" s="31" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="O15" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="P15" s="31"/>
-    </row>
-    <row r="16" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O15" s="31"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="28">
         <v>45112</v>
       </c>
@@ -2756,42 +2870,38 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="F16" s="77">
-        <f>C16/B16</f>
-        <v>67.601476014760138</v>
-      </c>
-      <c r="G16" s="77">
-        <f>B16+C16/100+D16/300</f>
+        <f t="shared" si="0"/>
         <v>54.58</v>
       </c>
+      <c r="G16" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H16" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" s="30" t="s">
         <v>45</v>
       </c>
+      <c r="J16" s="32" t="s">
+        <v>53</v>
+      </c>
       <c r="K16" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="32" t="s">
         <v>63</v>
       </c>
+      <c r="L16" s="31" t="s">
+        <v>31</v>
+      </c>
       <c r="M16" s="31" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="O16" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="P16" s="31" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="28">
         <v>45113</v>
       </c>
@@ -2808,40 +2918,36 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F17" s="77">
-        <f>C17/B17</f>
-        <v>82.015810276679844</v>
-      </c>
-      <c r="G17" s="77">
-        <f>B17+C17/100+D17/300</f>
+        <f t="shared" si="0"/>
         <v>51.569999999999993</v>
       </c>
+      <c r="G17" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H17" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K17" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="L17" s="32" t="s">
+      <c r="K17" s="32" t="s">
         <v>64</v>
       </c>
+      <c r="L17" s="31" t="s">
+        <v>11</v>
+      </c>
       <c r="M17" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="P17" s="31"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O17" s="31"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="28">
         <v>45114</v>
       </c>
@@ -2858,40 +2964,36 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F18" s="77">
-        <f>C18/B18</f>
-        <v>66.180758017492721</v>
-      </c>
-      <c r="G18" s="77">
-        <f>B18+C18/100+D18/300</f>
+        <f t="shared" si="0"/>
         <v>61.5</v>
       </c>
+      <c r="G18" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H18" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="L18" s="32" t="s">
+      <c r="K18" s="32" t="s">
         <v>68</v>
       </c>
+      <c r="L18" s="31" t="s">
+        <v>13</v>
+      </c>
       <c r="M18" s="31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="O18" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="31"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O18" s="31"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>45115</v>
       </c>
@@ -2908,42 +3010,38 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F19" s="77">
-        <f>C19/B19</f>
-        <v>45.348837209302324</v>
-      </c>
-      <c r="G19" s="77">
-        <f>B19+C19/100+D19/300</f>
+        <f t="shared" si="0"/>
         <v>68.540000000000006</v>
       </c>
+      <c r="G19" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H19" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I19" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="L19" s="32" t="s">
+      <c r="K19" s="32" t="s">
         <v>65</v>
       </c>
+      <c r="L19" s="31" t="s">
+        <v>15</v>
+      </c>
       <c r="M19" s="31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="O19" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="P19" s="31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="28">
         <v>45116</v>
       </c>
@@ -2960,40 +3058,36 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F20" s="77">
-        <f>C20/B20</f>
-        <v>37.670807453416145</v>
-      </c>
-      <c r="G20" s="77">
-        <f>B20+C20/100+D20/300</f>
+        <f t="shared" si="0"/>
         <v>52.463333333333338</v>
       </c>
+      <c r="G20" s="30" t="s">
+        <v>140</v>
+      </c>
       <c r="H20" s="30" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="32" t="s">
+      <c r="K20" s="32" t="s">
         <v>62</v>
       </c>
+      <c r="L20" s="31" t="s">
+        <v>14</v>
+      </c>
       <c r="M20" s="31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="O20" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="P20" s="31"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O20" s="31"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="87">
         <v>45123</v>
       </c>
@@ -3010,40 +3104,36 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F21" s="88">
-        <f>C21/B21</f>
-        <v>51.434782608695649</v>
-      </c>
-      <c r="G21" s="88">
-        <f>B21+C21/100+D21/300</f>
+        <f t="shared" si="0"/>
         <v>38.773333333333333</v>
       </c>
+      <c r="G21" s="46" t="s">
+        <v>140</v>
+      </c>
       <c r="H21" s="46" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J21" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="44" t="s">
+      <c r="K21" s="44" t="s">
         <v>70</v>
       </c>
+      <c r="L21" s="41" t="s">
+        <v>17</v>
+      </c>
       <c r="M21" s="41" t="s">
-        <v>17</v>
+        <v>201</v>
       </c>
       <c r="N21" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="O21" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="P21" s="41"/>
-    </row>
-    <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="O21" s="41"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="87">
         <v>45124</v>
       </c>
@@ -3060,40 +3150,36 @@
         <v>0.34722222222222227</v>
       </c>
       <c r="F22" s="88">
-        <f>C22/B22</f>
-        <v>51.300236406619391</v>
-      </c>
-      <c r="G22" s="88">
-        <f>B22+C22/100+D22/300</f>
+        <f t="shared" si="0"/>
         <v>36.15</v>
       </c>
+      <c r="G22" s="46" t="s">
+        <v>140</v>
+      </c>
       <c r="H22" s="46" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="K22" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="L22" s="44" t="s">
+      <c r="K22" s="44" t="s">
         <v>70</v>
       </c>
+      <c r="L22" s="41" t="s">
+        <v>23</v>
+      </c>
       <c r="M22" s="41" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="N22" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="O22" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="P22" s="41"/>
-    </row>
-    <row r="23" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="O22" s="41"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="87">
         <v>45125</v>
       </c>
@@ -3110,42 +3196,38 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="F23" s="88">
-        <f>C23/B23</f>
-        <v>60.760931289040322</v>
-      </c>
-      <c r="G23" s="88">
-        <f>B23+C23/100+D23/300</f>
+        <f t="shared" si="0"/>
         <v>63.75333333333333</v>
       </c>
+      <c r="G23" s="46" t="s">
+        <v>140</v>
+      </c>
       <c r="H23" s="46" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I23" s="46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J23" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="K23" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="L23" s="44" t="s">
+      <c r="K23" s="44" t="s">
         <v>60</v>
       </c>
+      <c r="L23" s="41" t="s">
+        <v>24</v>
+      </c>
       <c r="M23" s="41" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="N23" s="41" t="s">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="O23" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="P23" s="41" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="87">
         <v>45127</v>
       </c>
@@ -3162,40 +3244,36 @@
         <v>0.22916666666666666</v>
       </c>
       <c r="F24" s="88">
-        <f>C24/B24</f>
-        <v>43.961038961038959</v>
-      </c>
-      <c r="G24" s="88">
-        <f>B24+C24/100+D24/300</f>
+        <f t="shared" si="0"/>
         <v>24.426666666666669</v>
       </c>
+      <c r="G24" s="46" t="s">
+        <v>140</v>
+      </c>
       <c r="H24" s="46" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="K24" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="L24" s="44" t="s">
+      <c r="K24" s="44" t="s">
         <v>61</v>
       </c>
+      <c r="L24" s="41" t="s">
+        <v>32</v>
+      </c>
       <c r="M24" s="41" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="N24" s="41" t="s">
-        <v>209</v>
-      </c>
-      <c r="O24" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="P24" s="41"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="O24" s="41"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45150</v>
       </c>
@@ -3212,36 +3290,32 @@
         <v>0.25</v>
       </c>
       <c r="F25" s="76">
-        <f>C25/B25</f>
-        <v>40.99244875943905</v>
-      </c>
-      <c r="G25" s="76">
-        <f>B25+C25/100+D25/300</f>
+        <f t="shared" si="0"/>
         <v>28.673333333333332</v>
       </c>
+      <c r="G25" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H25" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L25" s="61" t="s">
+      <c r="K25" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="L25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="O25" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N25" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45199</v>
       </c>
@@ -3258,33 +3332,29 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="F26" s="76">
-        <f>C26/B26</f>
-        <v>61.807909604519779</v>
-      </c>
-      <c r="G26" s="76">
-        <f>B26+C26/100+D26/300</f>
+        <f t="shared" si="0"/>
         <v>16.143333333333334</v>
       </c>
+      <c r="G26" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H26" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L26" s="61" t="s">
+      <c r="K26" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="O26" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="N26" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <v>45205</v>
       </c>
@@ -3301,42 +3371,36 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F27" s="78">
-        <f>C27/B27</f>
-        <v>131.0344827586207</v>
-      </c>
-      <c r="G27" s="78">
-        <f>B27+C27/100+D27/300</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
+      <c r="G27" s="18" t="s">
+        <v>140</v>
+      </c>
       <c r="H27" s="18" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L27" s="62" t="s">
+      <c r="K27" s="62" t="s">
         <v>74</v>
       </c>
+      <c r="L27" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="M27" s="19" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="N27" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="O27" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="P27" s="19" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O27" s="19"/>
+    </row>
+    <row r="28" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
         <v>45206</v>
       </c>
@@ -3353,42 +3417,38 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F28" s="78">
-        <f>C28/B28</f>
-        <v>92.452830188679243</v>
-      </c>
-      <c r="G28" s="78">
-        <f>B28+C28/100+D28/300</f>
+        <f t="shared" si="0"/>
         <v>59.25</v>
       </c>
+      <c r="G28" s="18" t="s">
+        <v>140</v>
+      </c>
       <c r="H28" s="18" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L28" s="62" t="s">
+      <c r="K28" s="62" t="s">
         <v>75</v>
       </c>
+      <c r="L28" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="M28" s="19" t="s">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="N28" s="19" t="s">
-        <v>261</v>
+        <v>103</v>
       </c>
       <c r="O28" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="P28" s="19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
         <v>45207</v>
       </c>
@@ -3405,40 +3465,36 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="F29" s="78">
-        <f>C29/B29</f>
-        <v>62.962962962962962</v>
-      </c>
-      <c r="G29" s="78">
-        <f>B29+C29/100+D29/300</f>
+        <f t="shared" si="0"/>
         <v>51.666666666666664</v>
       </c>
+      <c r="G29" s="18" t="s">
+        <v>140</v>
+      </c>
       <c r="H29" s="18" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L29" s="62" t="s">
+      <c r="K29" s="62" t="s">
         <v>76</v>
       </c>
+      <c r="L29" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="M29" s="19" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="N29" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="O29" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="P29" s="19"/>
-    </row>
-    <row r="30" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O29" s="19"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="16">
         <v>45208</v>
       </c>
@@ -3455,40 +3511,36 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F30" s="78">
-        <f>C30/B30</f>
-        <v>32.954545454545453</v>
-      </c>
-      <c r="G30" s="78">
-        <f>B30+C30/100+D30/300</f>
+        <f t="shared" si="0"/>
         <v>35.833333333333336</v>
       </c>
+      <c r="G30" s="18" t="s">
+        <v>140</v>
+      </c>
       <c r="H30" s="18" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L30" s="62" t="s">
+      <c r="K30" s="62" t="s">
         <v>77</v>
       </c>
+      <c r="L30" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="M30" s="19" t="s">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="N30" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="O30" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="P30" s="19"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O30" s="19"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>45220</v>
       </c>
@@ -3505,36 +3557,32 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="F31" s="76">
-        <f>C31/B31</f>
-        <v>61.2</v>
-      </c>
-      <c r="G31" s="76">
-        <f>B31+C31/100+D31/300</f>
+        <f t="shared" si="0"/>
         <v>22.7</v>
       </c>
+      <c r="G31" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H31" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K31" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="L31" s="61" t="s">
+      <c r="K31" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="M31" s="10" t="s">
+      <c r="L31" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N31" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>45227</v>
       </c>
@@ -3551,36 +3599,32 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="F32" s="76">
-        <f>C32/B32</f>
-        <v>38.235294117647058</v>
-      </c>
-      <c r="G32" s="76">
-        <f>B32+C32/100+D32/300</f>
+        <f t="shared" si="0"/>
         <v>12.75</v>
       </c>
+      <c r="G32" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H32" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K32" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="L32" s="61" t="s">
+      <c r="K32" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="M32" s="10" t="s">
+      <c r="L32" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="O32" s="10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N32" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>45235</v>
       </c>
@@ -3597,36 +3641,32 @@
         <v>0.11805555555555557</v>
       </c>
       <c r="F33" s="76">
-        <f>C33/B33</f>
-        <v>42</v>
-      </c>
-      <c r="G33" s="76">
-        <f>B33+C33/100+D33/300</f>
+        <f t="shared" si="0"/>
         <v>23.400000000000002</v>
       </c>
+      <c r="G33" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H33" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K33" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="L33" s="61" t="s">
+      <c r="K33" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="L33" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="O33" s="10" t="s">
+      <c r="N33" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>45339</v>
       </c>
@@ -3643,36 +3683,32 @@
         <v>9.7222222222222224E-2</v>
       </c>
       <c r="F34" s="76">
-        <f>C34/B34</f>
-        <v>63.529411764705884</v>
-      </c>
-      <c r="G34" s="76">
-        <f>B34+C34/100+D34/300</f>
+        <f t="shared" ref="F34:F65" si="1">B34+C34/100+D34/300</f>
         <v>15.700000000000001</v>
       </c>
+      <c r="G34" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H34" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K34" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L34" s="61" t="s">
+      <c r="K34" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="M34" s="10" t="s">
+      <c r="L34" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="O34" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="N34" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>45347</v>
       </c>
@@ -3689,39 +3725,32 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F35" s="76">
-        <f>C35/B35</f>
-        <v>75</v>
-      </c>
-      <c r="G35" s="76">
-        <f>B35+C35/100+D35/300</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
+      <c r="G35" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H35" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K35" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L35" s="61" t="s">
+      <c r="K35" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="M35" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L35" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>45374</v>
       </c>
@@ -3738,36 +3767,32 @@
         <v>0.25</v>
       </c>
       <c r="F36" s="76">
-        <f>C36/B36</f>
-        <v>34.782608695652172</v>
-      </c>
-      <c r="G36" s="76">
-        <f>B36+C36/100+D36/300</f>
+        <f t="shared" si="1"/>
         <v>33.666666666666664</v>
       </c>
+      <c r="G36" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H36" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L36" s="61" t="s">
+      <c r="K36" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="M36" s="10" t="s">
+      <c r="L36" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="O36" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N36" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>45388</v>
       </c>
@@ -3784,36 +3809,32 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="F37" s="76">
-        <f>C37/B37</f>
-        <v>30</v>
-      </c>
-      <c r="G37" s="76">
-        <f>B37+C37/100+D37/300</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
+      <c r="G37" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H37" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K37" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L37" s="61" t="s">
+      <c r="K37" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="M37" s="10" t="s">
+      <c r="L37" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="N37" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="20">
         <v>45416</v>
       </c>
@@ -3830,42 +3851,38 @@
         <v>0.375</v>
       </c>
       <c r="F38" s="79">
-        <f>C38/B38</f>
-        <v>51.785714285714285</v>
-      </c>
-      <c r="G38" s="79">
-        <f>B38+C38/100+D38/300</f>
+        <f t="shared" si="1"/>
         <v>46.166666666666664</v>
       </c>
+      <c r="G38" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="H38" s="22" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K38" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="L38" s="63" t="s">
+      <c r="K38" s="63" t="s">
         <v>122</v>
       </c>
+      <c r="L38" s="23" t="s">
+        <v>125</v>
+      </c>
       <c r="M38" s="23" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="N38" s="23" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="O38" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="P38" s="23" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="20">
         <v>45417</v>
       </c>
@@ -3882,40 +3899,36 @@
         <v>0.375</v>
       </c>
       <c r="F39" s="79">
-        <f>C39/B39</f>
-        <v>29.62962962962963</v>
-      </c>
-      <c r="G39" s="79">
-        <f>B39+C39/100+D39/300</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
+      <c r="G39" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="H39" s="22" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K39" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="L39" s="63" t="s">
+      <c r="K39" s="63" t="s">
         <v>123</v>
       </c>
+      <c r="L39" s="23" t="s">
+        <v>126</v>
+      </c>
       <c r="M39" s="23" t="s">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="N39" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="O39" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="P39" s="23"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="O39" s="23"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="20">
         <v>45418</v>
       </c>
@@ -3932,40 +3945,36 @@
         <v>0.375</v>
       </c>
       <c r="F40" s="79">
-        <f>C40/B40</f>
-        <v>41.666666666666664</v>
-      </c>
-      <c r="G40" s="79">
-        <f>B40+C40/100+D40/300</f>
+        <f t="shared" si="1"/>
         <v>47.5</v>
       </c>
+      <c r="G40" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="H40" s="22" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K40" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="L40" s="63" t="s">
+      <c r="K40" s="63" t="s">
         <v>124</v>
       </c>
+      <c r="L40" s="23" t="s">
+        <v>127</v>
+      </c>
       <c r="M40" s="23" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="N40" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="O40" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="P40" s="23"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="O40" s="23"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="24">
         <v>45420</v>
       </c>
@@ -3982,42 +3991,38 @@
         <v>0.375</v>
       </c>
       <c r="F41" s="80">
-        <f>C41/B41</f>
-        <v>43.18181818181818</v>
-      </c>
-      <c r="G41" s="80">
-        <f>B41+C41/100+D41/300</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
+      <c r="G41" s="26" t="s">
+        <v>140</v>
+      </c>
       <c r="H41" s="26" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K41" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="L41" s="64" t="s">
-        <v>135</v>
+      <c r="K41" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="M41" s="27" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="N41" s="27" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="O41" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="P41" s="27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="24">
         <v>45421</v>
       </c>
@@ -4034,40 +4039,36 @@
         <v>0.5</v>
       </c>
       <c r="F42" s="80">
-        <f>C42/B42</f>
-        <v>48.07692307692308</v>
-      </c>
-      <c r="G42" s="80">
-        <f>B42+C42/100+D42/300</f>
+        <f t="shared" si="1"/>
         <v>41.5</v>
       </c>
+      <c r="G42" s="26" t="s">
+        <v>140</v>
+      </c>
       <c r="H42" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="K42" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="L42" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="I42" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K42" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="L42" s="64" t="s">
-        <v>136</v>
-      </c>
       <c r="M42" s="27" t="s">
-        <v>144</v>
+        <v>249</v>
       </c>
       <c r="N42" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="O42" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="P42" s="27"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="O42" s="27"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="24">
         <v>45422</v>
       </c>
@@ -4084,40 +4085,36 @@
         <v>0.40625</v>
       </c>
       <c r="F43" s="80">
-        <f>C43/B43</f>
-        <v>36.363636363636367</v>
-      </c>
-      <c r="G43" s="80">
-        <f>B43+C43/100+D43/300</f>
+        <f t="shared" si="1"/>
         <v>33.666666666666664</v>
       </c>
+      <c r="G43" s="26" t="s">
+        <v>140</v>
+      </c>
       <c r="H43" s="26" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J43" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K43" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="L43" s="64" t="s">
-        <v>137</v>
+      <c r="K43" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="L43" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="M43" s="27" t="s">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="N43" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="O43" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="P43" s="27"/>
-    </row>
-    <row r="44" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="O43" s="27"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="24">
         <v>45423</v>
       </c>
@@ -4134,40 +4131,36 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="F44" s="80">
-        <f>C44/B44</f>
-        <v>61.904761904761905</v>
-      </c>
-      <c r="G44" s="80">
-        <f>B44+C44/100+D44/300</f>
+        <f t="shared" si="1"/>
         <v>37.833333333333336</v>
       </c>
+      <c r="G44" s="26" t="s">
+        <v>140</v>
+      </c>
       <c r="H44" s="26" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J44" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K44" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="L44" s="64" t="s">
-        <v>138</v>
+      <c r="K44" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="L44" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="M44" s="27" t="s">
-        <v>147</v>
+        <v>249</v>
       </c>
       <c r="N44" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="O44" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="P44" s="27"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="O44" s="27"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="24">
         <v>45424</v>
       </c>
@@ -4184,40 +4177,36 @@
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="F45" s="80">
-        <f>C45/B45</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="G45" s="80">
-        <f>B45+C45/100+D45/300</f>
+        <f t="shared" si="1"/>
         <v>8.1</v>
       </c>
+      <c r="G45" s="26" t="s">
+        <v>140</v>
+      </c>
       <c r="H45" s="26" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I45" s="26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J45" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K45" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="L45" s="64" t="s">
-        <v>137</v>
+      <c r="K45" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="L45" s="27" t="s">
+        <v>144</v>
       </c>
       <c r="M45" s="27" t="s">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="N45" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="O45" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="P45" s="27"/>
-    </row>
-    <row r="46" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="O45" s="27"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
         <v>45446</v>
       </c>
@@ -4234,42 +4223,38 @@
         <v>0.34375</v>
       </c>
       <c r="F46" s="81">
-        <f>C46/B46</f>
-        <v>82.397003745318358</v>
-      </c>
-      <c r="G46" s="81">
-        <f>B46+C46/100+D46/300</f>
+        <f t="shared" si="1"/>
         <v>52.866666666666667</v>
       </c>
+      <c r="G46" s="35" t="s">
+        <v>140</v>
+      </c>
       <c r="H46" s="35" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I46" s="35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J46" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="K46" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="L46" s="65" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="K46" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="L46" s="36" t="s">
+        <v>157</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>160</v>
+        <v>367</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>389</v>
+        <v>103</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="P46" s="36" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>45447</v>
       </c>
@@ -4286,40 +4271,36 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="F47" s="81">
-        <f>C47/B47</f>
-        <v>64.10891089108911</v>
-      </c>
-      <c r="G47" s="81">
-        <f>B47+C47/100+D47/300</f>
+        <f t="shared" si="1"/>
         <v>75.333333333333329</v>
       </c>
+      <c r="G47" s="35" t="s">
+        <v>140</v>
+      </c>
       <c r="H47" s="35" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I47" s="35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J47" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="K47" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="L47" s="65"/>
+        <v>152</v>
+      </c>
+      <c r="K47" s="65"/>
+      <c r="L47" s="36" t="s">
+        <v>158</v>
+      </c>
       <c r="M47" s="36" t="s">
-        <v>161</v>
+        <v>367</v>
       </c>
       <c r="N47" s="36" t="s">
-        <v>389</v>
+        <v>103</v>
       </c>
       <c r="O47" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="P47" s="36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
         <v>45448</v>
       </c>
@@ -4336,40 +4317,36 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="F48" s="81">
-        <f>C48/B48</f>
-        <v>63.66459627329192</v>
-      </c>
-      <c r="G48" s="81">
-        <f>B48+C48/100+D48/300</f>
+        <f t="shared" si="1"/>
         <v>60.6</v>
       </c>
+      <c r="G48" s="35" t="s">
+        <v>140</v>
+      </c>
       <c r="H48" s="35" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I48" s="35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="K48" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="K48" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="L48" s="65" t="s">
+      <c r="L48" s="36" t="s">
         <v>159</v>
       </c>
       <c r="M48" s="36" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="N48" s="36" t="s">
-        <v>389</v>
-      </c>
-      <c r="O48" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="P48" s="36"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O48" s="36"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>45449</v>
       </c>
@@ -4386,42 +4363,38 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="F49" s="81">
-        <f>C49/B49</f>
-        <v>50.295857988165686</v>
-      </c>
-      <c r="G49" s="81">
-        <f>B49+C49/100+D49/300</f>
+        <f t="shared" si="1"/>
         <v>55.099999999999994</v>
       </c>
+      <c r="G49" s="35" t="s">
+        <v>140</v>
+      </c>
       <c r="H49" s="35" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I49" s="35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J49" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="K49" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="L49" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="K49" s="65" t="s">
         <v>9</v>
       </c>
+      <c r="L49" s="36" t="s">
+        <v>160</v>
+      </c>
       <c r="M49" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="N49" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="O49" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="N49" s="36" t="s">
-        <v>389</v>
-      </c>
-      <c r="O49" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="P49" s="36" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>45535</v>
       </c>
@@ -4438,42 +4411,36 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="F50" s="82">
-        <f>C50/B50</f>
-        <v>63.829787234042556</v>
-      </c>
-      <c r="G50" s="82">
-        <f>B50+C50/100+D50/300</f>
-        <v>43</v>
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>140</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="K50" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="L50" s="66" t="s">
-        <v>169</v>
+        <v>164</v>
+      </c>
+      <c r="K50" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="L50" s="38" t="s">
+        <v>168</v>
       </c>
       <c r="M50" s="38" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="N50" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="O50" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="P50" s="38" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="O50" s="38"/>
+    </row>
+    <row r="51" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>45536</v>
       </c>
@@ -4490,40 +4457,36 @@
         <v>0.35069444444444442</v>
       </c>
       <c r="F51" s="82">
-        <f>C51/B51</f>
-        <v>62.5</v>
-      </c>
-      <c r="G51" s="82">
-        <f>B51+C51/100+D51/300</f>
+        <f t="shared" si="1"/>
         <v>36.5</v>
       </c>
+      <c r="G51" s="37" t="s">
+        <v>140</v>
+      </c>
       <c r="H51" s="37" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J51" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="K51" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="K51" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="L51" s="66" t="s">
-        <v>170</v>
+      <c r="L51" s="38" t="s">
+        <v>169</v>
       </c>
       <c r="M51" s="38" t="s">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="N51" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="O51" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="P51" s="38"/>
-    </row>
-    <row r="52" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="O51" s="38"/>
+    </row>
+    <row r="52" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>45537</v>
       </c>
@@ -4540,40 +4503,36 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="F52" s="82">
-        <f>C52/B52</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="82">
-        <f>B52+C52/100+D52/300</f>
+        <f t="shared" si="1"/>
         <v>7.333333333333333</v>
       </c>
+      <c r="G52" s="37" t="s">
+        <v>140</v>
+      </c>
       <c r="H52" s="37" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J52" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="K52" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="L52" s="66" t="s">
-        <v>168</v>
+        <v>164</v>
+      </c>
+      <c r="K52" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="L52" s="38" t="s">
+        <v>170</v>
       </c>
       <c r="M52" s="38" t="s">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="N52" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="O52" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="P52" s="38"/>
-    </row>
-    <row r="53" spans="1:16" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="O52" s="38"/>
+    </row>
+    <row r="53" spans="1:15" s="45" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="42">
         <v>45540</v>
       </c>
@@ -4590,42 +4549,38 @@
         <v>0.59375</v>
       </c>
       <c r="F53" s="83">
-        <f>C53/B53</f>
-        <v>28.244274809160306</v>
-      </c>
-      <c r="G53" s="83">
-        <f>B53+C53/100+D53/300</f>
+        <f t="shared" si="1"/>
         <v>89.666666666666671</v>
       </c>
+      <c r="G53" s="44" t="s">
+        <v>140</v>
+      </c>
       <c r="H53" s="44" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I53" s="44" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J53" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="K53" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="L53" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K53" s="44" t="s">
+      <c r="M53" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="N53" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="O53" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="L53" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="M53" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="N53" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="O53" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="P53" s="41" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="42">
         <v>45542</v>
       </c>
@@ -4642,39 +4597,35 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F54" s="76">
-        <f>C54/B54</f>
-        <v>27.72972972972973</v>
-      </c>
-      <c r="G54" s="76">
-        <f>B54+C54/100+D54/300</f>
+        <f t="shared" si="1"/>
         <v>25.34</v>
       </c>
+      <c r="G54" s="44" t="s">
+        <v>140</v>
+      </c>
       <c r="H54" s="44" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I54" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J54" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="L54" s="61" t="s">
-        <v>180</v>
+        <v>172</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K54" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>181</v>
+        <v>330</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="O54" s="10" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="47">
         <v>45556</v>
       </c>
@@ -4691,42 +4642,36 @@
         <v>0.4375</v>
       </c>
       <c r="F55" s="84">
-        <f>C55/B55</f>
-        <v>49.859154929577464</v>
-      </c>
-      <c r="G55" s="84">
-        <f>B55+C55/100+D55/300</f>
+        <f t="shared" si="1"/>
         <v>55.466666666666669</v>
       </c>
+      <c r="G55" s="50" t="s">
+        <v>140</v>
+      </c>
       <c r="H55" s="50" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="J55" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="K55" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="L55" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="J55" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="K55" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="L55" s="51" t="s">
         <v>180</v>
       </c>
       <c r="M55" s="51" t="s">
-        <v>183</v>
+        <v>422</v>
       </c>
       <c r="N55" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="O55" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="P55" s="51" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O55" s="51"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="47">
         <v>45557</v>
       </c>
@@ -4743,40 +4688,36 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="F56" s="84">
-        <f>C56/B56</f>
-        <v>12.956810631229235</v>
-      </c>
-      <c r="G56" s="84">
-        <f>B56+C56/100+D56/300</f>
+        <f t="shared" si="1"/>
         <v>37.799999999999997</v>
       </c>
+      <c r="G56" s="50" t="s">
+        <v>140</v>
+      </c>
       <c r="H56" s="50" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I56" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="J56" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="K56" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="L56" s="50" t="s">
-        <v>182</v>
+        <v>172</v>
+      </c>
+      <c r="J56" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="K56" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="L56" s="51" t="s">
+        <v>181</v>
       </c>
       <c r="M56" s="51" t="s">
-        <v>184</v>
+        <v>422</v>
       </c>
       <c r="N56" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="O56" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="P56" s="51"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O56" s="51"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="52">
         <v>45562</v>
       </c>
@@ -4793,42 +4734,36 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="F57" s="85">
-        <f>C57/B57</f>
-        <v>107.92291220556744</v>
-      </c>
-      <c r="G57" s="85">
-        <f>B57+C57/100+D57/300</f>
+        <f t="shared" si="1"/>
         <v>54.416666666666664</v>
       </c>
+      <c r="G57" s="55" t="s">
+        <v>140</v>
+      </c>
       <c r="H57" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="I57" s="55" t="s">
-        <v>43</v>
+        <v>43</v>
+      </c>
+      <c r="I57" s="54" t="s">
+        <v>45</v>
       </c>
       <c r="J57" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="K57" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="L57" s="55" t="s">
-        <v>191</v>
+        <v>187</v>
+      </c>
+      <c r="K57" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="L57" s="56" t="s">
+        <v>189</v>
       </c>
       <c r="M57" s="56" t="s">
-        <v>192</v>
+        <v>368</v>
       </c>
       <c r="N57" s="56" t="s">
-        <v>390</v>
-      </c>
-      <c r="O57" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="P57" s="56" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="O57" s="56"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="52">
         <v>45563</v>
       </c>
@@ -4845,40 +4780,36 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F58" s="85">
-        <f>C58/B58</f>
-        <v>44.444444444444443</v>
-      </c>
-      <c r="G58" s="85">
-        <f>B58+C58/100+D58/300</f>
+        <f t="shared" si="1"/>
         <v>45.533333333333331</v>
       </c>
+      <c r="G58" s="55" t="s">
+        <v>140</v>
+      </c>
       <c r="H58" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="I58" s="55" t="s">
-        <v>43</v>
+        <v>43</v>
+      </c>
+      <c r="I58" s="54" t="s">
+        <v>45</v>
       </c>
       <c r="J58" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="K58" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="K58" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="L58" s="56" t="s">
         <v>190</v>
       </c>
-      <c r="L58" s="55" t="s">
-        <v>191</v>
-      </c>
       <c r="M58" s="56" t="s">
-        <v>193</v>
+        <v>368</v>
       </c>
       <c r="N58" s="56" t="s">
-        <v>390</v>
-      </c>
-      <c r="O58" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="P58" s="56"/>
-    </row>
-    <row r="59" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="O58" s="56"/>
+    </row>
+    <row r="59" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="57">
         <v>45597</v>
       </c>
@@ -4895,42 +4826,36 @@
         <v>0.22916666666666666</v>
       </c>
       <c r="F59" s="86">
-        <f>C59/B59</f>
-        <v>34.677419354838712</v>
-      </c>
-      <c r="G59" s="86">
-        <f>B59+C59/100+D59/300</f>
+        <f t="shared" si="1"/>
         <v>35.233333333333334</v>
       </c>
+      <c r="G59" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H59" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I59" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J59" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K59" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="L59" s="67" t="s">
-        <v>221</v>
+        <v>209</v>
+      </c>
+      <c r="K59" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="L59" s="60" t="s">
+        <v>210</v>
       </c>
       <c r="M59" s="60" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="N59" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="O59" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="P59" s="60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O59" s="60"/>
+    </row>
+    <row r="60" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="57">
         <v>45598</v>
       </c>
@@ -4947,40 +4872,36 @@
         <v>0.4375</v>
       </c>
       <c r="F60" s="86">
-        <f>C60/B60</f>
-        <v>22.327790973871732</v>
-      </c>
-      <c r="G60" s="86">
-        <f>B60+C60/100+D60/300</f>
+        <f t="shared" si="1"/>
         <v>54.266666666666666</v>
       </c>
+      <c r="G60" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H60" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I60" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J60" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K60" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="L60" s="67" t="s">
-        <v>228</v>
+        <v>209</v>
+      </c>
+      <c r="K60" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="L60" s="60" t="s">
+        <v>212</v>
       </c>
       <c r="M60" s="60" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="N60" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="O60" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="P60" s="60"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O60" s="60"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="57">
         <v>45599</v>
       </c>
@@ -4997,40 +4918,36 @@
         <v>0.46875</v>
       </c>
       <c r="F61" s="86">
-        <f>C61/B61</f>
-        <v>24.744376278118612</v>
-      </c>
-      <c r="G61" s="86">
-        <f>B61+C61/100+D61/300</f>
+        <f t="shared" si="1"/>
         <v>64.86666666666666</v>
       </c>
+      <c r="G61" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H61" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I61" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J61" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K61" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="K61" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="L61" s="67" t="s">
-        <v>229</v>
+      <c r="L61" s="60" t="s">
+        <v>213</v>
       </c>
       <c r="M61" s="60" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="N61" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="O61" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="P61" s="60"/>
-    </row>
-    <row r="62" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O61" s="60"/>
+    </row>
+    <row r="62" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="57">
         <v>45600</v>
       </c>
@@ -5047,40 +4964,36 @@
         <v>0.46527777777777773</v>
       </c>
       <c r="F62" s="86">
-        <f>C62/B62</f>
-        <v>34.311512415349888</v>
-      </c>
-      <c r="G62" s="86">
-        <f>B62+C62/100+D62/300</f>
+        <f t="shared" si="1"/>
         <v>63.266666666666666</v>
       </c>
+      <c r="G62" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H62" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I62" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J62" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K62" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="L62" s="67" t="s">
-        <v>230</v>
+        <v>209</v>
+      </c>
+      <c r="K62" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="L62" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="M62" s="60" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="N62" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="O62" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="P62" s="60"/>
-    </row>
-    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="O62" s="60"/>
+    </row>
+    <row r="63" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="57">
         <v>45601</v>
       </c>
@@ -5097,40 +5010,36 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="F63" s="86">
-        <f>C63/B63</f>
-        <v>21.535181236673775</v>
-      </c>
-      <c r="G63" s="86">
-        <f>B63+C63/100+D63/300</f>
+        <f t="shared" si="1"/>
         <v>62.933333333333337</v>
       </c>
+      <c r="G63" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H63" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I63" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J63" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K63" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="L63" s="67" t="s">
-        <v>231</v>
+        <v>209</v>
+      </c>
+      <c r="K63" s="67" t="s">
+        <v>221</v>
+      </c>
+      <c r="L63" s="60" t="s">
+        <v>215</v>
       </c>
       <c r="M63" s="60" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="N63" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="O63" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="P63" s="60"/>
-    </row>
-    <row r="64" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="O63" s="60"/>
+    </row>
+    <row r="64" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="57">
         <v>45602</v>
       </c>
@@ -5147,42 +5056,38 @@
         <v>0.47569444444444442</v>
       </c>
       <c r="F64" s="86">
-        <f>C64/B64</f>
-        <v>25.902335456475583</v>
-      </c>
-      <c r="G64" s="86">
-        <f>B64+C64/100+D64/300</f>
+        <f t="shared" si="1"/>
         <v>64.86666666666666</v>
       </c>
+      <c r="G64" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H64" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I64" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J64" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K64" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="L64" s="67" t="s">
-        <v>232</v>
+        <v>209</v>
+      </c>
+      <c r="K64" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="L64" s="60" t="s">
+        <v>216</v>
       </c>
       <c r="M64" s="60" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="N64" s="60" t="s">
-        <v>218</v>
+        <v>103</v>
       </c>
       <c r="O64" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="P64" s="60" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="57">
         <v>45603</v>
       </c>
@@ -5199,40 +5104,36 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F65" s="86">
-        <f>C65/B65</f>
-        <v>31.914893617021278</v>
-      </c>
-      <c r="G65" s="86">
-        <f>B65+C65/100+D65/300</f>
+        <f t="shared" si="1"/>
         <v>33.9</v>
       </c>
+      <c r="G65" s="59" t="s">
+        <v>140</v>
+      </c>
       <c r="H65" s="59" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I65" s="59" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="J65" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="K65" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="L65" s="67" t="s">
-        <v>233</v>
+        <v>209</v>
+      </c>
+      <c r="K65" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="L65" s="60" t="s">
+        <v>217</v>
       </c>
       <c r="M65" s="60" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="N65" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="O65" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="P65" s="60"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O65" s="60"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>45641</v>
       </c>
@@ -5249,39 +5150,35 @@
         <v>0.19444444444444445</v>
       </c>
       <c r="F66" s="76">
-        <f>C66/B66</f>
-        <v>89.361702127659569</v>
-      </c>
-      <c r="G66" s="76">
-        <f>B66+C66/100+D66/300</f>
+        <f t="shared" ref="F66:F86" si="2">B66+C66/100+D66/300</f>
         <v>20.6</v>
       </c>
+      <c r="G66" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H66" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="L66" s="61" t="s">
-        <v>239</v>
-      </c>
-      <c r="M66" s="10" t="s">
-        <v>240</v>
+        <v>228</v>
+      </c>
+      <c r="K66" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="N66" s="10" t="s">
+        <v>206</v>
       </c>
       <c r="O66" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="P66" s="10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45660</v>
       </c>
@@ -5298,42 +5195,38 @@
         <v>0.26041666666666669</v>
       </c>
       <c r="F67" s="76">
-        <f>C67/B67</f>
-        <v>38.095238095238095</v>
-      </c>
-      <c r="G67" s="76">
-        <f>B67+C67/100+D67/300</f>
+        <f t="shared" si="2"/>
         <v>31.666666666666668</v>
       </c>
+      <c r="G67" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="H67" s="3" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="L67" s="61" t="s">
-        <v>244</v>
+        <v>233</v>
+      </c>
+      <c r="K67" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>235</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>351</v>
+        <v>206</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>45675</v>
       </c>
@@ -5350,39 +5243,35 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="F68" s="76">
-        <f>C68/B68</f>
-        <v>72.794117647058826</v>
-      </c>
-      <c r="G68" s="76">
-        <f>B68+C68/100+D68/300</f>
+        <f t="shared" si="2"/>
         <v>53.6</v>
       </c>
+      <c r="G68" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="H68" s="3" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="L68" s="61" t="s">
-        <v>266</v>
+        <v>251</v>
+      </c>
+      <c r="K68" s="61" t="s">
+        <v>252</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>267</v>
+        <v>329</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="O68" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="16">
         <v>45689</v>
       </c>
@@ -5399,40 +5288,38 @@
         <v>6.25E-2</v>
       </c>
       <c r="F69" s="78">
-        <f>C69/B69</f>
-        <v>137.73584905660377</v>
-      </c>
-      <c r="G69" s="78">
-        <f>B69+C69/100+D69/300</f>
+        <f t="shared" si="2"/>
         <v>12.666666666666666</v>
       </c>
+      <c r="G69" s="18" t="s">
+        <v>232</v>
+      </c>
       <c r="H69" s="18" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I69" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K69" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="L69" s="62" t="s">
-        <v>277</v>
+        <v>251</v>
+      </c>
+      <c r="K69" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>261</v>
       </c>
       <c r="M69" s="19" t="s">
-        <v>278</v>
+        <v>365</v>
       </c>
       <c r="N69" s="19" t="s">
-        <v>387</v>
+        <v>103</v>
       </c>
       <c r="O69" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="P69" s="19"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="16">
         <v>45689</v>
       </c>
@@ -5449,40 +5336,36 @@
         <v>0.25</v>
       </c>
       <c r="F70" s="78">
-        <f>C70/B70</f>
-        <v>39.698492462311563</v>
-      </c>
-      <c r="G70" s="78">
-        <f>B70+C70/100+D70/300</f>
+        <f t="shared" si="2"/>
         <v>32.799999999999997</v>
       </c>
+      <c r="G70" s="18" t="s">
+        <v>232</v>
+      </c>
       <c r="H70" s="18" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I70" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J70" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K70" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="L70" s="62" t="s">
-        <v>277</v>
+        <v>251</v>
+      </c>
+      <c r="K70" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="L70" s="19" t="s">
+        <v>402</v>
       </c>
       <c r="M70" s="19" t="s">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="N70" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="O70" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="P70" s="19"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O70" s="19"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>45697</v>
       </c>
@@ -5499,39 +5382,35 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F71" s="76">
-        <f>C71/B71</f>
-        <v>56.79012345679012</v>
-      </c>
-      <c r="G71" s="76">
-        <f>B71+C71/100+D71/300</f>
+        <f t="shared" si="2"/>
         <v>42.7</v>
       </c>
+      <c r="G71" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="H71" s="3" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="L71" s="61" t="s">
-        <v>345</v>
+        <v>233</v>
+      </c>
+      <c r="K71" s="61" t="s">
+        <v>326</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>327</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="O71" s="10" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="90">
         <v>45703</v>
       </c>
@@ -5548,42 +5427,38 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="F72" s="91">
-        <f>C72/B72</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="G72" s="91">
-        <f>B72+C72/100+D72/300</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
+      <c r="G72" s="93" t="s">
+        <v>232</v>
+      </c>
       <c r="H72" s="93" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I72" s="93" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J72" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="K72" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="L72" s="94" t="s">
+      <c r="K72" s="94" t="s">
         <v>66</v>
       </c>
+      <c r="L72" s="95" t="s">
+        <v>332</v>
+      </c>
       <c r="M72" s="95" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="N72" s="95" t="s">
-        <v>388</v>
+        <v>206</v>
       </c>
       <c r="O72" s="95" t="s">
-        <v>215</v>
-      </c>
-      <c r="P72" s="95" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="90">
         <v>45704</v>
       </c>
@@ -5600,42 +5475,634 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="F73" s="91">
-        <f>C73/B73</f>
-        <v>57.142857142857146</v>
-      </c>
-      <c r="G73" s="91">
-        <f>B73+C73/100+D73/300</f>
+        <f t="shared" si="2"/>
         <v>13.333333333333334</v>
       </c>
+      <c r="G73" s="93" t="s">
+        <v>232</v>
+      </c>
       <c r="H73" s="93" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="I73" s="93" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J73" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="K73" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="L73" s="95" t="s">
+        <v>333</v>
+      </c>
+      <c r="M73" s="95" t="s">
+        <v>366</v>
+      </c>
+      <c r="N73" s="95" t="s">
+        <v>206</v>
+      </c>
+      <c r="O73" s="95"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="99">
+        <v>45715</v>
+      </c>
+      <c r="B74" s="100">
+        <v>21.1</v>
+      </c>
+      <c r="C74" s="101">
+        <v>590</v>
+      </c>
+      <c r="D74" s="101">
+        <v>360</v>
+      </c>
+      <c r="E74" s="102">
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="F74" s="100">
+        <f t="shared" si="2"/>
+        <v>28.2</v>
+      </c>
+      <c r="G74" s="102" t="s">
+        <v>140</v>
+      </c>
+      <c r="H74" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" s="102" t="s">
+        <v>172</v>
+      </c>
+      <c r="J74" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="K74" s="103" t="s">
+        <v>370</v>
+      </c>
+      <c r="L74" s="104" t="s">
+        <v>372</v>
+      </c>
+      <c r="M74" s="104" t="s">
+        <v>421</v>
+      </c>
+      <c r="N74" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="O74" s="104"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="99">
+        <v>45716</v>
+      </c>
+      <c r="B75" s="100">
+        <v>35</v>
+      </c>
+      <c r="C75" s="101">
+        <v>1280</v>
+      </c>
+      <c r="D75" s="101">
+        <v>1290</v>
+      </c>
+      <c r="E75" s="102">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F75" s="100">
+        <f t="shared" si="2"/>
+        <v>52.099999999999994</v>
+      </c>
+      <c r="G75" s="102" t="s">
+        <v>140</v>
+      </c>
+      <c r="H75" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="I75" s="102" t="s">
+        <v>172</v>
+      </c>
+      <c r="J75" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="K75" s="103" t="s">
+        <v>371</v>
+      </c>
+      <c r="L75" s="104" t="s">
+        <v>375</v>
+      </c>
+      <c r="M75" s="104" t="s">
+        <v>421</v>
+      </c>
+      <c r="N75" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="O75" s="104"/>
+    </row>
+    <row r="76" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>45718</v>
+      </c>
+      <c r="B76" s="76">
+        <v>21.4</v>
+      </c>
+      <c r="C76" s="9">
+        <v>1260</v>
+      </c>
+      <c r="D76" s="9">
+        <v>1260</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0.34027777777777773</v>
+      </c>
+      <c r="F76" s="88">
+        <f t="shared" si="2"/>
+        <v>38.200000000000003</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I76" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K73" s="93" t="s">
-        <v>50</v>
-      </c>
-      <c r="L73" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="M73" s="95" t="s">
-        <v>354</v>
-      </c>
-      <c r="N73" s="95" t="s">
-        <v>388</v>
-      </c>
-      <c r="O73" s="95" t="s">
-        <v>215</v>
-      </c>
-      <c r="P73" s="95"/>
+      <c r="J76" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K76" s="61" t="s">
+        <v>377</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="N76" s="10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>45732</v>
+      </c>
+      <c r="B77" s="76">
+        <v>15.9</v>
+      </c>
+      <c r="C77" s="9">
+        <v>520</v>
+      </c>
+      <c r="D77" s="9">
+        <v>520</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F77" s="88">
+        <f t="shared" si="2"/>
+        <v>22.833333333333336</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K77" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>45746</v>
+      </c>
+      <c r="B78" s="76">
+        <v>23.4</v>
+      </c>
+      <c r="C78" s="9">
+        <v>1290</v>
+      </c>
+      <c r="D78" s="9">
+        <v>1290</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="F78" s="88">
+        <f t="shared" si="2"/>
+        <v>40.599999999999994</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K78" s="61" t="s">
+        <v>392</v>
+      </c>
+      <c r="L78" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="N78" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="106">
+        <v>45767</v>
+      </c>
+      <c r="B79" s="107">
+        <v>16.7</v>
+      </c>
+      <c r="C79" s="108">
+        <v>1140</v>
+      </c>
+      <c r="D79" s="108">
+        <v>180</v>
+      </c>
+      <c r="E79" s="109">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="F79" s="107">
+        <f t="shared" si="2"/>
+        <v>28.700000000000003</v>
+      </c>
+      <c r="G79" s="109" t="s">
+        <v>232</v>
+      </c>
+      <c r="H79" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" s="109" t="s">
+        <v>172</v>
+      </c>
+      <c r="J79" s="109" t="s">
+        <v>186</v>
+      </c>
+      <c r="K79" s="110" t="s">
+        <v>403</v>
+      </c>
+      <c r="L79" s="111" t="s">
+        <v>405</v>
+      </c>
+      <c r="M79" s="111" t="s">
+        <v>420</v>
+      </c>
+      <c r="N79" s="111" t="s">
+        <v>206</v>
+      </c>
+      <c r="O79" s="111" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="106">
+        <v>45768</v>
+      </c>
+      <c r="B80" s="107">
+        <v>22.5</v>
+      </c>
+      <c r="C80" s="108">
+        <v>60</v>
+      </c>
+      <c r="D80" s="108">
+        <v>1230</v>
+      </c>
+      <c r="E80" s="109">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="F80" s="107">
+        <f t="shared" si="2"/>
+        <v>27.200000000000003</v>
+      </c>
+      <c r="G80" s="109" t="s">
+        <v>232</v>
+      </c>
+      <c r="H80" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="I80" s="109" t="s">
+        <v>172</v>
+      </c>
+      <c r="J80" s="109" t="s">
+        <v>186</v>
+      </c>
+      <c r="K80" s="110" t="s">
+        <v>404</v>
+      </c>
+      <c r="L80" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="M80" s="111" t="s">
+        <v>420</v>
+      </c>
+      <c r="N80" s="111" t="s">
+        <v>206</v>
+      </c>
+      <c r="O80" s="111"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="112">
+        <v>45773</v>
+      </c>
+      <c r="B81" s="113">
+        <v>27.4</v>
+      </c>
+      <c r="C81" s="114">
+        <v>2270</v>
+      </c>
+      <c r="D81" s="114">
+        <v>920</v>
+      </c>
+      <c r="E81" s="115">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F81" s="113">
+        <f t="shared" si="2"/>
+        <v>53.166666666666664</v>
+      </c>
+      <c r="G81" s="115" t="s">
+        <v>232</v>
+      </c>
+      <c r="H81" s="115" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" s="115" t="s">
+        <v>45</v>
+      </c>
+      <c r="J81" s="115" t="s">
+        <v>251</v>
+      </c>
+      <c r="K81" s="116" t="s">
+        <v>260</v>
+      </c>
+      <c r="L81" s="117" t="s">
+        <v>418</v>
+      </c>
+      <c r="M81" s="117" t="s">
+        <v>236</v>
+      </c>
+      <c r="N81" s="117" t="s">
+        <v>103</v>
+      </c>
+      <c r="O81" s="117"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="112">
+        <v>45774</v>
+      </c>
+      <c r="B82" s="113">
+        <v>29.1</v>
+      </c>
+      <c r="C82" s="114">
+        <v>1160</v>
+      </c>
+      <c r="D82" s="114">
+        <v>2490</v>
+      </c>
+      <c r="E82" s="115">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F82" s="113">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="G82" s="115" t="s">
+        <v>232</v>
+      </c>
+      <c r="H82" s="115" t="s">
+        <v>43</v>
+      </c>
+      <c r="I82" s="115" t="s">
+        <v>45</v>
+      </c>
+      <c r="J82" s="115" t="s">
+        <v>251</v>
+      </c>
+      <c r="K82" s="116" t="s">
+        <v>417</v>
+      </c>
+      <c r="L82" s="117" t="s">
+        <v>419</v>
+      </c>
+      <c r="M82" s="117" t="s">
+        <v>236</v>
+      </c>
+      <c r="N82" s="117" t="s">
+        <v>103</v>
+      </c>
+      <c r="O82" s="117"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="24">
+        <v>45778</v>
+      </c>
+      <c r="B83" s="80">
+        <v>20</v>
+      </c>
+      <c r="C83" s="25">
+        <v>1850</v>
+      </c>
+      <c r="D83" s="25">
+        <v>590</v>
+      </c>
+      <c r="E83" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="F83" s="80">
+        <f t="shared" si="2"/>
+        <v>40.466666666666669</v>
+      </c>
+      <c r="G83" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="H83" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J83" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="K83" s="64" t="s">
+        <v>426</v>
+      </c>
+      <c r="L83" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="M83" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="N83" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="O83" s="27"/>
+    </row>
+    <row r="84" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="24">
+        <v>45779</v>
+      </c>
+      <c r="B84" s="80">
+        <v>22.713200000000001</v>
+      </c>
+      <c r="C84" s="25">
+        <v>1320</v>
+      </c>
+      <c r="D84" s="25">
+        <v>1170</v>
+      </c>
+      <c r="E84" s="26">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F84" s="80">
+        <f t="shared" si="2"/>
+        <v>39.813200000000002</v>
+      </c>
+      <c r="G84" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="H84" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I84" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J84" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="K84" s="64" t="s">
+        <v>427</v>
+      </c>
+      <c r="L84" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="M84" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="N84" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="O84" s="27"/>
+    </row>
+    <row r="85" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="24">
+        <v>45780</v>
+      </c>
+      <c r="B85" s="80">
+        <v>25.6</v>
+      </c>
+      <c r="C85" s="25">
+        <v>850</v>
+      </c>
+      <c r="D85" s="25">
+        <v>1580</v>
+      </c>
+      <c r="E85" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F85" s="80">
+        <f t="shared" si="2"/>
+        <v>39.366666666666667</v>
+      </c>
+      <c r="G85" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="H85" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J85" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="K85" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="L85" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="M85" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="N85" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="O85" s="27" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="24">
+        <v>45781</v>
+      </c>
+      <c r="B86" s="80">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C86" s="25">
+        <v>490</v>
+      </c>
+      <c r="D86" s="25">
+        <v>1120</v>
+      </c>
+      <c r="E86" s="26">
+        <v>0.25</v>
+      </c>
+      <c r="F86" s="80">
+        <f t="shared" si="2"/>
+        <v>27.033333333333331</v>
+      </c>
+      <c r="G86" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="H86" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I86" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J86" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="K86" s="64" t="s">
+        <v>428</v>
+      </c>
+      <c r="L86" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="M86" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="N86" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="O86" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P70" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P70">
+  <autoFilter ref="A1:O70">
+    <sortState ref="A2:O82">
       <sortCondition ref="A1:A65"/>
     </sortState>
   </autoFilter>
@@ -5645,17 +6112,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="36.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
@@ -5669,7 +6136,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
@@ -5680,11 +6147,11 @@
         <v>93</v>
       </c>
       <c r="D2" s="15">
-        <f t="shared" ref="D2:D27" si="0">IF(C2="Z", 1, IF(C2="S", 2, IF(C2="A", 3, IF(C2="B", 4, IF(C2="C", 5, IF(C2="D", 6, 7))))))</f>
+        <f t="shared" ref="D2:D30" si="0">IF(C2="Z", 1, IF(C2="S", 2, IF(C2="A", 3, IF(C2="B", 4, IF(C2="C", 5, IF(C2="D", 6, 7))))))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>38</v>
       </c>
@@ -5699,12 +6166,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>93</v>
@@ -5714,12 +6181,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>93</v>
@@ -5729,7 +6196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -5744,7 +6211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>34</v>
       </c>
@@ -5759,7 +6226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>40</v>
       </c>
@@ -5774,12 +6241,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>94</v>
@@ -5789,9 +6256,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>86</v>
@@ -5804,7 +6271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>83</v>
       </c>
@@ -5819,57 +6286,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>118</v>
+        <v>325</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="15">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>85</v>
+        <v>411</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D14" s="15">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>95</v>
@@ -5879,12 +6346,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>95</v>
@@ -5894,12 +6361,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>95</v>
@@ -5909,57 +6376,57 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D18" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D19" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D20" s="15">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>116</v>
@@ -5969,12 +6436,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>116</v>
@@ -5984,12 +6451,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>116</v>
@@ -5999,12 +6466,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>116</v>
@@ -6014,12 +6481,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>270</v>
+        <v>89</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>271</v>
+        <v>86</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>116</v>
@@ -6029,69 +6496,105 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>343</v>
+        <v>88</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D26" s="15">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>385</v>
+        <v>184</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D27" s="15">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D28" s="15"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D29" s="15"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D30" s="15"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="15">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="15">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D31" s="15"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D32" s="15"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D33" s="15"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D34" s="15"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35" s="15"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36" s="15"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D18" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D24">
+  <autoFilter ref="A1:D18">
+    <sortState ref="A2:D28">
       <sortCondition ref="D1:D18"/>
     </sortState>
   </autoFilter>
@@ -6118,15 +6621,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
@@ -6134,457 +6637,593 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="B2" s="5">
         <v>3172</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B3" s="5">
         <v>3045</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="B4" s="5">
         <v>2789</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="B5" s="5">
         <v>2685</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="B6" s="5">
         <v>2663</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B7" s="5">
         <v>2662</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="5">
         <v>2525</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="B9" s="5">
         <v>2459</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="B10" s="5">
         <v>2432</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B11" s="5">
         <v>2338</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="B12" s="5">
         <v>2284</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B13" s="5">
         <v>2276</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="B14" s="5">
         <v>2222</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B15" s="5">
         <v>2219</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B16" s="5">
         <v>2175</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="B17" s="5">
         <v>2156</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="B18" s="5">
         <v>2080</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="B19" s="5">
         <v>2051</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="B20" s="5">
         <v>2049</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B21" s="5">
         <v>2037</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B22" s="5">
         <v>1992</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="B23" s="5">
         <v>1976</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B24" s="5">
         <v>1966</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B27" s="5">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B28" s="5">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B29" s="5">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B30" s="5">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B33" s="5">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B34" s="5">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B35" s="5">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B36" s="5">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="5">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B38" s="5">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="5">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B40" s="5">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B41" s="5">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B42" s="5">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B43" s="5">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B44" s="5">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B45" s="5">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B46" s="5">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B47" s="5">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B48" s="5">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B49" s="5">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B50" s="5">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B51" s="5">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" s="5">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B53" s="5">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B54" s="5">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B55" s="5">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B56" s="5">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B57" s="5">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B58" s="5">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B59" s="5">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B25" s="5">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B26" s="5">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="B27" s="5">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B28" s="5">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B29" s="5">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B30" s="5">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="5">
-        <v>1635</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B32" s="5">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="5">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B34" s="5">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B35" s="5">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B36" s="5">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B37" s="5">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B38" s="5">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B39" s="5">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B40" s="5">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="B41" s="5">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B42" s="5">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B43" s="5">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B44" s="5">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B45" s="5">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B46" s="5">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B47" s="5">
+      <c r="B60" s="5">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B61" s="5">
         <v>1050</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B48" s="5">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B62" s="5">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B63" s="5">
         <v>1011</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B49" s="5">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B64" s="5">
         <v>805</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B50" s="5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B65" s="5">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" s="5">
         <v>656</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B51" s="5">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B67" s="5">
         <v>645</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B52" s="5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B68" s="5">
         <v>634</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B53" s="5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="5">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B70" s="5">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B71" s="5">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" s="5">
         <v>563</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B54" s="5">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B73" s="5">
         <v>433</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="B55" s="5">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="B56" s="5">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="B57" s="5">
-        <v>1959</v>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B74" s="5">
+        <v>1761</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B54">
+  <autoFilter ref="A1:B5">
+    <sortState ref="A2:B73">
       <sortCondition descending="1" ref="B1:B5"/>
     </sortState>
   </autoFilter>
@@ -6593,22 +7232,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="11.5703125" style="4"/>
+    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="12" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="12" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="B1" s="97" t="s">
         <v>6</v>
@@ -6620,565 +7259,564 @@
         <v>0</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="F1" s="96" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
+        <v>0</v>
+      </c>
+      <c r="B2" s="105" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>0</v>
+      </c>
+      <c r="B3" s="105" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
       <c r="B4" s="7" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>284</v>
+        <v>112</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="D6" s="6">
+        <v>220</v>
+      </c>
+      <c r="E6" s="7">
+        <v>14000</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+      <c r="D11" s="6">
+        <v>125</v>
+      </c>
+      <c r="E11" s="7">
+        <v>9000</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>2</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>281</v>
+        <v>1</v>
+      </c>
+      <c r="B12" s="98" t="s">
+        <v>395</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+      <c r="D12" s="6">
+        <v>45</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2500</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="6">
-        <v>220</v>
-      </c>
-      <c r="E14" s="7">
-        <v>14000</v>
-      </c>
-      <c r="F14" s="8">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>3</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>152</v>
+        <v>1</v>
+      </c>
+      <c r="B15" s="98" t="s">
+        <v>254</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+      <c r="D15" s="6">
+        <v>35</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>36</v>
+      <c r="B16" s="98" t="s">
+        <v>380</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>250</v>
+      <c r="B17" s="98" t="s">
+        <v>335</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>3</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>256</v>
+        <v>1</v>
+      </c>
+      <c r="B18" s="98" t="s">
+        <v>396</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>248</v>
+      <c r="B19" s="98" t="s">
+        <v>397</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="D22" s="6">
-        <v>125</v>
-      </c>
-      <c r="E22" s="7">
-        <v>9000</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2</v>
       </c>
-      <c r="B23" s="98" t="s">
-        <v>249</v>
+      <c r="B23" s="7" t="s">
+        <v>263</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D23" s="6">
-        <v>85</v>
-      </c>
-      <c r="E23" s="7">
-        <v>5000</v>
-      </c>
-      <c r="F23" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>1</v>
-      </c>
-      <c r="B24" s="98" t="s">
-        <v>201</v>
+        <v>2</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="D24" s="6">
-        <v>45</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2500</v>
-      </c>
-      <c r="F24" s="8">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>2</v>
       </c>
       <c r="B26" s="98" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="D26" s="6">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="E26" s="7">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F26" s="8">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>255</v>
+        <v>119</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>3</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>241</v>
+        <v>2</v>
+      </c>
+      <c r="B28" s="98" t="s">
+        <v>194</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+      <c r="F28" s="8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>110</v>
+        <v>2</v>
+      </c>
+      <c r="B29" s="98" t="s">
+        <v>259</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+      <c r="D29" s="6">
+        <v>90</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5000</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>119</v>
+        <v>356</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2</v>
       </c>
-      <c r="B31" s="98" t="s">
-        <v>247</v>
+      <c r="B31" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F31" s="8">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2</v>
       </c>
-      <c r="B32" s="98" t="s">
-        <v>257</v>
+      <c r="B32" s="7" t="s">
+        <v>359</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>3</v>
-      </c>
-      <c r="B33" s="98" t="s">
-        <v>272</v>
+        <v>2</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>389</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="D33" s="6">
-        <v>35</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1500</v>
-      </c>
-      <c r="F33" s="8">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2</v>
       </c>
       <c r="B34" s="98" t="s">
-        <v>202</v>
+        <v>398</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="F34" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>3</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>2</v>
-      </c>
-      <c r="B37" s="98" t="s">
-        <v>276</v>
+        <v>3</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D37" s="6">
-        <v>90</v>
-      </c>
-      <c r="E37" s="7">
-        <v>5000</v>
-      </c>
-      <c r="F37" s="8">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>1</v>
-      </c>
-      <c r="B38" s="98" t="s">
-        <v>269</v>
+        <v>3</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D38" s="6">
-        <v>35</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2000</v>
-      </c>
-      <c r="F38" s="8">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>2</v>
-      </c>
-      <c r="B39" s="98" t="s">
-        <v>342</v>
+        <v>3</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>3</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>355</v>
+        <v>149</v>
       </c>
       <c r="C40" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>3</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>3</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>3</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>3</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="5">
-        <v>1</v>
-      </c>
-      <c r="B41" s="98" t="s">
-        <v>356</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="5">
-        <v>2</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="5">
-        <v>2</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="5">
-        <v>2</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>382</v>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>3</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>3</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:F41">
+    <sortState ref="A2:F50">
+      <sortCondition ref="A1:A44"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Randonnée.xlsx
+++ b/data/Randonnée.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B32DC83-56ED-4128-BAC3-EFF6AF223D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Randonnées" sheetId="4" r:id="rId1"/>
@@ -14,16 +15,27 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plus beaux endroits'!$A$1:$D$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Randonnées!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Randonnées!$A$1:$P$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sommets!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$F$41</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="448">
   <si>
     <t>Km</t>
   </si>
@@ -1355,12 +1367,24 @@
   </si>
   <si>
     <t>500h</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Journée</t>
+  </si>
+  <si>
+    <t>Trek Refuge</t>
+  </si>
+  <si>
+    <t>Trek Bivouac</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[h]:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1406,7 +1430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1427,67 +1451,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE1FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEEEF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1C4B9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1499,13 +1463,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1625,10 +1583,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1656,56 +1613,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1717,55 +1628,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1793,71 +1659,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2000,6 +1828,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -2035,6 +1880,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2210,3899 +2072,4216 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O86"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P86"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="76" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="76" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.21875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="27.21875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="57.77734375" style="10" customWidth="1"/>
-    <col min="13" max="13" width="29.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" style="34" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="29.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="57.7109375" style="9" customWidth="1"/>
+    <col min="13" max="13" width="29.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="74" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:16" s="32" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="70" t="s">
+      <c r="E1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="71" t="s">
+      <c r="J1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="72" t="s">
+      <c r="K1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="73" t="s">
+      <c r="L1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="73" t="s">
+      <c r="M1" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="73" t="s">
+      <c r="N1" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="O1" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="O1" s="73" t="s">
+      <c r="P1" s="31" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="36">
         <v>44997</v>
       </c>
-      <c r="B2" s="76">
+      <c r="B2" s="37">
         <v>16.809999999999999</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="38">
         <v>983</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="38">
         <v>983</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="23">
         <v>0.15972222222222224</v>
       </c>
-      <c r="F2" s="76">
+      <c r="F2" s="37">
         <f t="shared" ref="F2:F33" si="0">B2+C2/100+D2/300</f>
         <v>29.916666666666668</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="61" t="s">
+      <c r="K2" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O2" s="19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="P2" s="19"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
         <v>45010</v>
       </c>
-      <c r="B3" s="76">
+      <c r="B3" s="35">
         <v>39.5</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="16">
         <v>2240</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="16">
         <v>2240</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="17">
         <v>0.4375</v>
       </c>
-      <c r="F3" s="76">
+      <c r="F3" s="35">
         <f t="shared" si="0"/>
         <v>69.36666666666666</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="61" t="s">
+      <c r="K3" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O3" s="18" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="P3" s="18"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="36">
         <v>45011</v>
       </c>
-      <c r="B4" s="76">
+      <c r="B4" s="37">
         <v>12.55</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="38">
         <v>537</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="38">
         <v>537</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="23">
         <v>0.15972222222222224</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="37">
         <f t="shared" si="0"/>
         <v>19.71</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="61" t="s">
+      <c r="K4" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O4" s="19" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="P4" s="19"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
         <v>45017</v>
       </c>
-      <c r="B5" s="76">
+      <c r="B5" s="35">
         <v>17.32</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="16">
         <v>834</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="16">
         <v>834</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="17">
         <v>0.25</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="35">
         <f t="shared" si="0"/>
         <v>28.44</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="H5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="61" t="s">
+      <c r="K5" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O5" s="18" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="P5" s="18"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="36">
         <v>45038</v>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="37">
         <v>15</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="38">
         <v>800</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="38">
         <v>800</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="23">
         <v>0.25</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="37">
         <f t="shared" si="0"/>
         <v>25.666666666666668</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="H6" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="K6" s="21"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O6" s="19" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="P6" s="19"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
         <v>45039</v>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="35">
         <v>18.5</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="16">
         <v>917</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="16">
         <v>917</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="17">
         <v>0.1875</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="35">
         <f t="shared" si="0"/>
         <v>30.726666666666667</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="K7" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O7" s="18" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="P7" s="18"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="36">
         <v>45060</v>
       </c>
-      <c r="B8" s="76">
+      <c r="B8" s="37">
         <v>18.02</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="38">
         <v>980</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="38">
         <v>980</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="23">
         <v>0.1875</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="37">
         <f t="shared" si="0"/>
         <v>31.086666666666666</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="H8" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="61" t="s">
+      <c r="K8" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O8" s="19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="P8" s="19"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
         <v>45073</v>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="35">
         <v>30.5</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="16">
         <v>2004</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="16">
         <v>2004</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="17">
         <v>0.34722222222222227</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="35">
         <f t="shared" si="0"/>
         <v>57.22</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="H9" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="61" t="s">
+      <c r="K9" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O9" s="18" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="P9" s="18"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="36">
         <v>45074</v>
       </c>
-      <c r="B10" s="76">
+      <c r="B10" s="37">
         <v>13</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="38">
         <v>583</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="38">
         <v>583</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="23">
         <v>0.125</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="37">
         <f t="shared" si="0"/>
         <v>20.773333333333333</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="H10" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="61" t="s">
+      <c r="K10" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O10" s="19" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="P10" s="19"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>45080</v>
       </c>
-      <c r="B11" s="76">
+      <c r="B11" s="35">
         <v>4.5</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="16">
         <v>550</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="16">
         <v>550</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="17">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="35">
         <f t="shared" si="0"/>
         <v>11.833333333333334</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="H11" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="61" t="s">
+      <c r="K11" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O11" s="18" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
+      <c r="P11" s="18"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="46">
         <v>45108</v>
       </c>
-      <c r="B12" s="77">
+      <c r="B12" s="47">
         <v>23.3</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="48">
         <v>1393</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="48">
         <v>854</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="49">
         <v>0.29166666666666669</v>
       </c>
-      <c r="F12" s="77">
+      <c r="F12" s="47">
         <f t="shared" si="0"/>
         <v>40.076666666666668</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H12" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="30" t="s">
+      <c r="H12" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="32" t="s">
+      <c r="K12" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="31" t="s">
+      <c r="L12" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="31" t="s">
+      <c r="M12" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N12" s="31" t="s">
+      <c r="N12" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O12" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O12" s="31" t="s">
+      <c r="P12" s="51" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="28">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="46">
         <v>45109</v>
       </c>
-      <c r="B13" s="77">
+      <c r="B13" s="47">
         <v>20.3</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="48">
         <v>2319</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="48">
         <v>1355</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="49">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F13" s="77">
+      <c r="F13" s="47">
         <f t="shared" si="0"/>
         <v>48.006666666666668</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="30" t="s">
+      <c r="H13" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="30" t="s">
+      <c r="J13" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="32" t="s">
+      <c r="K13" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="L13" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="31" t="s">
+      <c r="M13" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N13" s="31" t="s">
+      <c r="N13" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O13" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O13" s="31" t="s">
+      <c r="P13" s="51" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="28">
+    <row r="14" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="46">
         <v>45110</v>
       </c>
-      <c r="B14" s="77">
+      <c r="B14" s="47">
         <v>35.200000000000003</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="48">
         <v>2001</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="48">
         <v>2218</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="49">
         <v>0.38541666666666669</v>
       </c>
-      <c r="F14" s="77">
+      <c r="F14" s="47">
         <f t="shared" si="0"/>
         <v>62.603333333333339</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="30" t="s">
+      <c r="H14" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="32" t="s">
+      <c r="K14" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="31" t="s">
+      <c r="L14" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="31" t="s">
+      <c r="M14" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="31" t="s">
+      <c r="N14" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O14" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O14" s="31"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="28">
+      <c r="P14" s="51"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="46">
         <v>45111</v>
       </c>
-      <c r="B15" s="77">
+      <c r="B15" s="47">
         <v>32.700000000000003</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="48">
         <v>2086</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="48">
         <v>1741</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="49">
         <v>0.375</v>
       </c>
-      <c r="F15" s="77">
+      <c r="F15" s="47">
         <f t="shared" si="0"/>
         <v>59.363333333333337</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H15" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="30" t="s">
+      <c r="H15" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="30" t="s">
+      <c r="J15" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="L15" s="31" t="s">
+      <c r="L15" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="31" t="s">
+      <c r="M15" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N15" s="31" t="s">
+      <c r="N15" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O15" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="31"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="28">
+      <c r="P15" s="51"/>
+    </row>
+    <row r="16" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="46">
         <v>45112</v>
       </c>
-      <c r="B16" s="77">
+      <c r="B16" s="47">
         <v>27.1</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="48">
         <v>1832</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="48">
         <v>2748</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="49">
         <v>0.35416666666666669</v>
       </c>
-      <c r="F16" s="77">
+      <c r="F16" s="47">
         <f t="shared" si="0"/>
         <v>54.58</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H16" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="30" t="s">
+      <c r="H16" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="32" t="s">
+      <c r="K16" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="L16" s="31" t="s">
+      <c r="L16" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M16" s="31" t="s">
+      <c r="M16" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="31" t="s">
+      <c r="N16" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O16" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O16" s="31" t="s">
+      <c r="P16" s="51" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="28">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="46">
         <v>45113</v>
       </c>
-      <c r="B17" s="77">
+      <c r="B17" s="47">
         <v>25.3</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="48">
         <v>2075</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="48">
         <v>1656</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="49">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F17" s="77">
+      <c r="F17" s="47">
         <f t="shared" si="0"/>
         <v>51.569999999999993</v>
       </c>
-      <c r="G17" s="30" t="s">
+      <c r="G17" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H17" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="30" t="s">
+      <c r="H17" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="30" t="s">
+      <c r="J17" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="32" t="s">
+      <c r="K17" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L17" s="31" t="s">
+      <c r="L17" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="31" t="s">
+      <c r="M17" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N17" s="31" t="s">
+      <c r="N17" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O17" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O17" s="31"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="28">
+      <c r="P17" s="51"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="46">
         <v>45114</v>
       </c>
-      <c r="B18" s="77">
+      <c r="B18" s="47">
         <v>34.299999999999997</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="48">
         <v>2270</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="48">
         <v>1350</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="49">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F18" s="77">
+      <c r="F18" s="47">
         <f t="shared" si="0"/>
         <v>61.5</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H18" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="30" t="s">
+      <c r="H18" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J18" s="30" t="s">
+      <c r="J18" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="32" t="s">
+      <c r="K18" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="L18" s="31" t="s">
+      <c r="L18" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="31" t="s">
+      <c r="M18" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="31" t="s">
+      <c r="N18" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O18" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O18" s="31"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="28">
+      <c r="P18" s="51"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="46">
         <v>45115</v>
       </c>
-      <c r="B19" s="77">
-        <v>43</v>
-      </c>
-      <c r="C19" s="29">
+      <c r="B19" s="47">
+        <v>43</v>
+      </c>
+      <c r="C19" s="48">
         <v>1950</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="48">
         <v>1812</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="49">
         <v>0.42708333333333331</v>
       </c>
-      <c r="F19" s="77">
+      <c r="F19" s="47">
         <f t="shared" si="0"/>
         <v>68.540000000000006</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G19" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="30" t="s">
+      <c r="H19" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="30" t="s">
+      <c r="J19" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="K19" s="32" t="s">
+      <c r="K19" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="31" t="s">
+      <c r="L19" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="M19" s="31" t="s">
+      <c r="M19" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N19" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O19" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O19" s="31" t="s">
+      <c r="P19" s="51" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="28">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="46">
         <v>45116</v>
       </c>
-      <c r="B20" s="77">
+      <c r="B20" s="47">
         <v>32.200000000000003</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="48">
         <v>1213</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="48">
         <v>2440</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="49">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F20" s="77">
+      <c r="F20" s="47">
         <f t="shared" si="0"/>
         <v>52.463333333333338</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="30" t="s">
+      <c r="H20" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="30" t="s">
+      <c r="J20" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="K20" s="32" t="s">
+      <c r="K20" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="L20" s="31" t="s">
+      <c r="L20" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="M20" s="31" t="s">
+      <c r="M20" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N20" s="31" t="s">
+      <c r="N20" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="O20" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O20" s="31"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="87">
+      <c r="P20" s="51"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
         <v>45123</v>
       </c>
-      <c r="B21" s="88">
+      <c r="B21" s="35">
         <v>23</v>
       </c>
-      <c r="C21" s="89">
+      <c r="C21" s="16">
         <v>1183</v>
       </c>
-      <c r="D21" s="89">
+      <c r="D21" s="16">
         <v>1183</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F21" s="88">
+      <c r="F21" s="35">
         <f t="shared" si="0"/>
         <v>38.773333333333333</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H21" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="46" t="s">
+      <c r="H21" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="46" t="s">
+      <c r="J21" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="K21" s="44" t="s">
+      <c r="K21" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="L21" s="41" t="s">
+      <c r="L21" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="41" t="s">
+      <c r="M21" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="N21" s="41" t="s">
+      <c r="N21" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O21" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="O21" s="41"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="87">
+      <c r="P21" s="18"/>
+    </row>
+    <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
         <v>45124</v>
       </c>
-      <c r="B22" s="88">
+      <c r="B22" s="37">
         <v>21.15</v>
       </c>
-      <c r="C22" s="89">
+      <c r="C22" s="38">
         <v>1085</v>
       </c>
-      <c r="D22" s="89">
+      <c r="D22" s="38">
         <v>1245</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="23">
         <v>0.34722222222222227</v>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="37">
         <f t="shared" si="0"/>
         <v>36.15</v>
       </c>
-      <c r="G22" s="46" t="s">
+      <c r="G22" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H22" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="46" t="s">
+      <c r="H22" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J22" s="46" t="s">
+      <c r="J22" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="L22" s="41" t="s">
+      <c r="L22" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="M22" s="41" t="s">
+      <c r="M22" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="N22" s="41" t="s">
+      <c r="N22" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O22" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="O22" s="41"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="87">
+      <c r="P22" s="19"/>
+    </row>
+    <row r="23" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
         <v>45125</v>
       </c>
-      <c r="B23" s="88">
+      <c r="B23" s="35">
         <v>35.22</v>
       </c>
-      <c r="C23" s="89">
+      <c r="C23" s="16">
         <v>2140</v>
       </c>
-      <c r="D23" s="89">
+      <c r="D23" s="16">
         <v>2140</v>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="F23" s="88">
+      <c r="F23" s="35">
         <f t="shared" si="0"/>
         <v>63.75333333333333</v>
       </c>
-      <c r="G23" s="46" t="s">
+      <c r="G23" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H23" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="46" t="s">
+      <c r="H23" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="46" t="s">
+      <c r="J23" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="K23" s="44" t="s">
+      <c r="K23" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="L23" s="41" t="s">
+      <c r="L23" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="41" t="s">
+      <c r="M23" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="N23" s="41" t="s">
+      <c r="N23" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O23" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O23" s="41" t="s">
+      <c r="P23" s="18" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="87">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
         <v>45127</v>
       </c>
-      <c r="B24" s="88">
+      <c r="B24" s="37">
         <v>15.4</v>
       </c>
-      <c r="C24" s="89">
+      <c r="C24" s="38">
         <v>677</v>
       </c>
-      <c r="D24" s="89">
+      <c r="D24" s="38">
         <v>677</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="23">
         <v>0.22916666666666666</v>
       </c>
-      <c r="F24" s="88">
+      <c r="F24" s="37">
         <f t="shared" si="0"/>
         <v>24.426666666666669</v>
       </c>
-      <c r="G24" s="46" t="s">
+      <c r="G24" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H24" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" s="46" t="s">
+      <c r="H24" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J24" s="46" t="s">
+      <c r="J24" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="K24" s="44" t="s">
+      <c r="K24" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="L24" s="41" t="s">
+      <c r="L24" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="M24" s="41" t="s">
+      <c r="M24" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="N24" s="41" t="s">
+      <c r="N24" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O24" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="O24" s="41"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="P24" s="19"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
         <v>45150</v>
       </c>
-      <c r="B25" s="76">
+      <c r="B25" s="35">
         <v>18.54</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="16">
         <v>760</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="16">
         <v>760</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="17">
         <v>0.25</v>
       </c>
-      <c r="F25" s="76">
+      <c r="F25" s="35">
         <f t="shared" si="0"/>
         <v>28.673333333333332</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="H25" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="61" t="s">
+      <c r="K25" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="L25" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="M25" s="18"/>
+      <c r="N25" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O25" s="18" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="P25" s="18"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
         <v>45199</v>
       </c>
-      <c r="B26" s="76">
+      <c r="B26" s="37">
         <v>8.85</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="38">
         <v>547</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="38">
         <v>547</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="23">
         <v>0.10416666666666667</v>
       </c>
-      <c r="F26" s="76">
+      <c r="F26" s="37">
         <f t="shared" si="0"/>
         <v>16.143333333333334</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="H26" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K26" s="61" t="s">
+      <c r="K26" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N26" s="10" t="s">
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O26" s="19" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
+      <c r="P26" s="19"/>
+    </row>
+    <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
         <v>45205</v>
       </c>
-      <c r="B27" s="78">
+      <c r="B27" s="35">
         <v>14.5</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="16">
         <v>1900</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="16">
         <v>750</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="17">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F27" s="78">
+      <c r="F27" s="35">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" s="18" t="s">
+      <c r="H27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J27" s="18" t="s">
+      <c r="J27" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="K27" s="62" t="s">
+      <c r="K27" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="M27" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="N27" s="19" t="s">
+      <c r="N27" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O27" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O27" s="19"/>
-    </row>
-    <row r="28" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
+      <c r="P27" s="18"/>
+    </row>
+    <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
         <v>45206</v>
       </c>
-      <c r="B28" s="78">
+      <c r="B28" s="35">
         <v>26.5</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="16">
         <v>2450</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="16">
         <v>2475</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="17">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F28" s="78">
+      <c r="F28" s="35">
         <f t="shared" si="0"/>
         <v>59.25</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I28" s="18" t="s">
+      <c r="H28" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="18" t="s">
+      <c r="J28" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="K28" s="62" t="s">
+      <c r="K28" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="L28" s="19" t="s">
+      <c r="L28" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="N28" s="19" t="s">
+      <c r="N28" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O28" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O28" s="19" t="s">
+      <c r="P28" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
+    <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
         <v>45207</v>
       </c>
-      <c r="B29" s="78">
+      <c r="B29" s="35">
         <v>27</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="16">
         <v>1700</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="16">
         <v>2300</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="F29" s="78">
+      <c r="F29" s="35">
         <f t="shared" si="0"/>
         <v>51.666666666666664</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H29" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I29" s="18" t="s">
+      <c r="H29" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="J29" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="K29" s="62" t="s">
+      <c r="K29" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="L29" s="19" t="s">
+      <c r="L29" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="M29" s="19" t="s">
+      <c r="M29" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="N29" s="19" t="s">
+      <c r="N29" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O29" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O29" s="19"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="16">
+      <c r="P29" s="18"/>
+    </row>
+    <row r="30" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
         <v>45208</v>
       </c>
-      <c r="B30" s="78">
+      <c r="B30" s="35">
         <v>22</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="16">
         <v>725</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="16">
         <v>1975</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="17">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F30" s="78">
+      <c r="F30" s="35">
         <f t="shared" si="0"/>
         <v>35.833333333333336</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H30" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I30" s="18" t="s">
+      <c r="H30" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J30" s="18" t="s">
+      <c r="J30" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="K30" s="62" t="s">
+      <c r="K30" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="M30" s="19" t="s">
+      <c r="M30" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="N30" s="19" t="s">
+      <c r="N30" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O30" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O30" s="19"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+      <c r="P30" s="18"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="36">
         <v>45220</v>
       </c>
-      <c r="B31" s="76">
+      <c r="B31" s="37">
         <v>12.5</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="38">
         <v>765</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="38">
         <v>765</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="23">
         <v>0.14583333333333334</v>
       </c>
-      <c r="F31" s="76">
+      <c r="F31" s="37">
         <f t="shared" si="0"/>
         <v>22.7</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="H31" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I31" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="K31" s="61" t="s">
+      <c r="K31" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="N31" s="10" t="s">
+      <c r="M31" s="19"/>
+      <c r="N31" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O31" s="19" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="P31" s="19"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
         <v>45227</v>
       </c>
-      <c r="B32" s="76">
+      <c r="B32" s="35">
         <v>8.5</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="16">
         <v>325</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="16">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="17">
         <v>0.14583333333333334</v>
       </c>
-      <c r="F32" s="76">
+      <c r="F32" s="35">
         <f t="shared" si="0"/>
         <v>12.75</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="H32" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="K32" s="61" t="s">
+      <c r="K32" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="L32" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="N32" s="10" t="s">
+      <c r="M32" s="18"/>
+      <c r="N32" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O32" s="18" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="P32" s="18"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="36">
         <v>45235</v>
       </c>
-      <c r="B33" s="76">
+      <c r="B33" s="37">
         <v>15</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="38">
         <v>630</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="38">
         <v>630</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="23">
         <v>0.11805555555555557</v>
       </c>
-      <c r="F33" s="76">
+      <c r="F33" s="37">
         <f t="shared" si="0"/>
         <v>23.400000000000002</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" s="3" t="s">
+      <c r="H33" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="K33" s="61" t="s">
+      <c r="K33" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="L33" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="N33" s="10" t="s">
+      <c r="M33" s="19"/>
+      <c r="N33" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O33" s="19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+      <c r="P33" s="19"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="15">
         <v>45339</v>
       </c>
-      <c r="B34" s="76">
+      <c r="B34" s="35">
         <v>8.5</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="16">
         <v>540</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="16">
         <v>540</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="17">
         <v>9.7222222222222224E-2</v>
       </c>
-      <c r="F34" s="76">
+      <c r="F34" s="35">
         <f t="shared" ref="F34:F65" si="1">B34+C34/100+D34/300</f>
         <v>15.700000000000001</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="H34" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K34" s="61" t="s">
+      <c r="K34" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="L34" s="10" t="s">
+      <c r="L34" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="N34" s="10" t="s">
+      <c r="M34" s="18"/>
+      <c r="N34" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O34" s="18" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="P34" s="18"/>
+    </row>
+    <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="36">
         <v>45347</v>
       </c>
-      <c r="B35" s="76">
+      <c r="B35" s="37">
         <v>8</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="38">
         <v>600</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="38">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="23">
         <v>0.16666666666666666</v>
       </c>
-      <c r="F35" s="76">
+      <c r="F35" s="37">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I35" s="3" t="s">
+      <c r="H35" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I35" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K35" s="61" t="s">
+      <c r="K35" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="L35" s="10" t="s">
+      <c r="L35" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="N35" s="10" t="s">
+      <c r="M35" s="19"/>
+      <c r="N35" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O35" s="19" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+      <c r="P35" s="19"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
         <v>45374</v>
       </c>
-      <c r="B36" s="76">
+      <c r="B36" s="35">
         <v>23</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="16">
         <v>800</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="16">
         <v>800</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="17">
         <v>0.25</v>
       </c>
-      <c r="F36" s="76">
+      <c r="F36" s="35">
         <f t="shared" si="1"/>
         <v>33.666666666666664</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I36" s="3" t="s">
+      <c r="H36" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="K36" s="61" t="s">
+      <c r="K36" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="L36" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="M36" s="18"/>
+      <c r="N36" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O36" s="18" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="P36" s="18"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="36">
         <v>45388</v>
       </c>
-      <c r="B37" s="76">
+      <c r="B37" s="37">
         <v>15</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="38">
         <v>450</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="38">
         <v>450</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="23">
         <v>0.20833333333333334</v>
       </c>
-      <c r="F37" s="76">
+      <c r="F37" s="37">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" s="3" t="s">
+      <c r="H37" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I37" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="K37" s="61" t="s">
+      <c r="K37" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="L37" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="N37" s="10" t="s">
+      <c r="M37" s="19"/>
+      <c r="N37" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O37" s="19" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="20">
+      <c r="P37" s="19"/>
+    </row>
+    <row r="38" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="15">
         <v>45416</v>
       </c>
-      <c r="B38" s="79">
+      <c r="B38" s="35">
         <v>28</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="16">
         <v>1450</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="16">
         <v>1100</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="17">
         <v>0.375</v>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="35">
         <f t="shared" si="1"/>
         <v>46.166666666666664</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H38" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I38" s="22" t="s">
+      <c r="H38" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I38" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="22" t="s">
+      <c r="J38" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="K38" s="63" t="s">
+      <c r="K38" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="23" t="s">
+      <c r="L38" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="M38" s="23" t="s">
+      <c r="M38" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="N38" s="23" t="s">
+      <c r="N38" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O38" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="O38" s="23" t="s">
+      <c r="P38" s="18" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="20">
+    <row r="39" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
         <v>45417</v>
       </c>
-      <c r="B39" s="79">
+      <c r="B39" s="35">
         <v>27</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="16">
         <v>800</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="16">
         <v>900</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="17">
         <v>0.375</v>
       </c>
-      <c r="F39" s="79">
+      <c r="F39" s="35">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H39" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="22" t="s">
+      <c r="H39" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="22" t="s">
+      <c r="J39" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="K39" s="63" t="s">
+      <c r="K39" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="23" t="s">
+      <c r="L39" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="M39" s="23" t="s">
+      <c r="M39" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="N39" s="23" t="s">
+      <c r="N39" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O39" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="O39" s="23"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="20">
+      <c r="P39" s="18"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
         <v>45418</v>
       </c>
-      <c r="B40" s="79">
+      <c r="B40" s="35">
         <v>30</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="16">
         <v>1250</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="16">
         <v>1500</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="17">
         <v>0.375</v>
       </c>
-      <c r="F40" s="79">
+      <c r="F40" s="35">
         <f t="shared" si="1"/>
         <v>47.5</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H40" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="22" t="s">
+      <c r="H40" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J40" s="22" t="s">
+      <c r="J40" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="K40" s="63" t="s">
+      <c r="K40" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="L40" s="23" t="s">
+      <c r="L40" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="M40" s="23" t="s">
+      <c r="M40" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="N40" s="23" t="s">
+      <c r="N40" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O40" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="O40" s="23"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="24">
+      <c r="P40" s="18"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="46">
         <v>45420</v>
       </c>
-      <c r="B41" s="80">
+      <c r="B41" s="47">
         <v>22</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="48">
         <v>950</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="48">
         <v>750</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="49">
         <v>0.375</v>
       </c>
-      <c r="F41" s="80">
+      <c r="F41" s="47">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="G41" s="26" t="s">
+      <c r="G41" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H41" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="26" t="s">
+      <c r="H41" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J41" s="26" t="s">
+      <c r="J41" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K41" s="64" t="s">
+      <c r="K41" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="L41" s="27" t="s">
+      <c r="L41" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="M41" s="27" t="s">
+      <c r="M41" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="N41" s="27" t="s">
+      <c r="N41" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O41" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="O41" s="27" t="s">
+      <c r="P41" s="51" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="24">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="46">
         <v>45421</v>
       </c>
-      <c r="B42" s="80">
+      <c r="B42" s="47">
         <v>26</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="48">
         <v>1250</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="48">
         <v>900</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="49">
         <v>0.5</v>
       </c>
-      <c r="F42" s="80">
+      <c r="F42" s="47">
         <f t="shared" si="1"/>
         <v>41.5</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="G42" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H42" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" s="26" t="s">
+      <c r="H42" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J42" s="26" t="s">
+      <c r="J42" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K42" s="64" t="s">
+      <c r="K42" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="L42" s="27" t="s">
+      <c r="L42" s="51" t="s">
         <v>142</v>
       </c>
-      <c r="M42" s="27" t="s">
+      <c r="M42" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="N42" s="27" t="s">
+      <c r="N42" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O42" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="O42" s="27"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="24">
+      <c r="P42" s="51"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="46">
         <v>45422</v>
       </c>
-      <c r="B43" s="80">
+      <c r="B43" s="47">
         <v>22</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="48">
         <v>800</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="48">
         <v>1100</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="49">
         <v>0.40625</v>
       </c>
-      <c r="F43" s="80">
+      <c r="F43" s="47">
         <f t="shared" si="1"/>
         <v>33.666666666666664</v>
       </c>
-      <c r="G43" s="26" t="s">
+      <c r="G43" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H43" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I43" s="26" t="s">
+      <c r="H43" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I43" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J43" s="26" t="s">
+      <c r="J43" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K43" s="64" t="s">
+      <c r="K43" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="L43" s="27" t="s">
+      <c r="L43" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="M43" s="27" t="s">
+      <c r="M43" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="N43" s="27" t="s">
+      <c r="N43" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O43" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="O43" s="27"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="24">
+      <c r="P43" s="51"/>
+    </row>
+    <row r="44" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="46">
         <v>45423</v>
       </c>
-      <c r="B44" s="80">
+      <c r="B44" s="47">
         <v>21</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="48">
         <v>1300</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="48">
         <v>1150</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="49">
         <v>0.38541666666666669</v>
       </c>
-      <c r="F44" s="80">
+      <c r="F44" s="47">
         <f t="shared" si="1"/>
         <v>37.833333333333336</v>
       </c>
-      <c r="G44" s="26" t="s">
+      <c r="G44" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H44" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" s="26" t="s">
+      <c r="H44" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I44" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J44" s="26" t="s">
+      <c r="J44" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="L44" s="27" t="s">
+      <c r="L44" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="M44" s="27" t="s">
+      <c r="M44" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="N44" s="27" t="s">
+      <c r="N44" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O44" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="O44" s="27"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="24">
+      <c r="P44" s="51"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="46">
         <v>45424</v>
       </c>
-      <c r="B45" s="80">
+      <c r="B45" s="47">
         <v>7</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="48">
         <v>10</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="48">
         <v>300</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="49">
         <v>7.2916666666666671E-2</v>
       </c>
-      <c r="F45" s="80">
+      <c r="F45" s="47">
         <f t="shared" si="1"/>
         <v>8.1</v>
       </c>
-      <c r="G45" s="26" t="s">
+      <c r="G45" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H45" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I45" s="26" t="s">
+      <c r="H45" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I45" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J45" s="26" t="s">
+      <c r="J45" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K45" s="64" t="s">
+      <c r="K45" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="L45" s="27" t="s">
+      <c r="L45" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="M45" s="27" t="s">
+      <c r="M45" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="N45" s="27" t="s">
+      <c r="N45" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O45" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="O45" s="27"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="33">
+      <c r="P45" s="51"/>
+    </row>
+    <row r="46" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="15">
         <v>45446</v>
       </c>
-      <c r="B46" s="81">
+      <c r="B46" s="35">
         <v>26.7</v>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="16">
         <v>2200</v>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="16">
         <v>1250</v>
       </c>
-      <c r="E46" s="35">
+      <c r="E46" s="17">
         <v>0.34375</v>
       </c>
-      <c r="F46" s="81">
+      <c r="F46" s="35">
         <f t="shared" si="1"/>
         <v>52.866666666666667</v>
       </c>
-      <c r="G46" s="35" t="s">
+      <c r="G46" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H46" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I46" s="35" t="s">
+      <c r="H46" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J46" s="35" t="s">
+      <c r="J46" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="K46" s="65" t="s">
+      <c r="K46" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="L46" s="36" t="s">
+      <c r="L46" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="M46" s="36" t="s">
+      <c r="M46" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="N46" s="36" t="s">
+      <c r="N46" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O46" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O46" s="36" t="s">
+      <c r="P46" s="18" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="33">
+    <row r="47" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="15">
         <v>45447</v>
       </c>
-      <c r="B47" s="81">
+      <c r="B47" s="35">
         <v>40.4</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="16">
         <v>2590</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="16">
         <v>2710</v>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="17">
         <v>0.52083333333333337</v>
       </c>
-      <c r="F47" s="81">
+      <c r="F47" s="35">
         <f t="shared" si="1"/>
         <v>75.333333333333329</v>
       </c>
-      <c r="G47" s="35" t="s">
+      <c r="G47" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H47" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I47" s="35" t="s">
+      <c r="H47" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J47" s="35" t="s">
+      <c r="J47" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="K47" s="65"/>
-      <c r="L47" s="36" t="s">
+      <c r="K47" s="25"/>
+      <c r="L47" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="M47" s="36" t="s">
+      <c r="M47" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="N47" s="36" t="s">
+      <c r="N47" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O47" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O47" s="36" t="s">
+      <c r="P47" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="33">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="15">
         <v>45448</v>
       </c>
-      <c r="B48" s="81">
+      <c r="B48" s="35">
         <v>32.200000000000003</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="16">
         <v>2050</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="16">
         <v>2370</v>
       </c>
-      <c r="E48" s="35">
+      <c r="E48" s="17">
         <v>0.51041666666666663</v>
       </c>
-      <c r="F48" s="81">
+      <c r="F48" s="35">
         <f t="shared" si="1"/>
         <v>60.6</v>
       </c>
-      <c r="G48" s="35" t="s">
+      <c r="G48" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H48" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I48" s="35" t="s">
+      <c r="H48" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J48" s="35" t="s">
+      <c r="J48" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="K48" s="65" t="s">
+      <c r="K48" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="L48" s="36" t="s">
+      <c r="L48" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="M48" s="36" t="s">
+      <c r="M48" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="N48" s="36" t="s">
+      <c r="N48" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O48" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O48" s="36"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="33">
+      <c r="P48" s="18"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="15">
         <v>45449</v>
       </c>
-      <c r="B49" s="81">
+      <c r="B49" s="35">
         <v>33.799999999999997</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="16">
         <v>1700</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="16">
         <v>1290</v>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="17">
         <v>0.48958333333333331</v>
       </c>
-      <c r="F49" s="81">
+      <c r="F49" s="35">
         <f t="shared" si="1"/>
         <v>55.099999999999994</v>
       </c>
-      <c r="G49" s="35" t="s">
+      <c r="G49" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H49" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I49" s="35" t="s">
+      <c r="H49" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="35" t="s">
+      <c r="J49" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="K49" s="65" t="s">
+      <c r="K49" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L49" s="36" t="s">
+      <c r="L49" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="M49" s="36" t="s">
+      <c r="M49" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="N49" s="36" t="s">
+      <c r="N49" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O49" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O49" s="36" t="s">
+      <c r="P49" s="18" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="39">
+    <row r="50" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="46">
         <v>45535</v>
       </c>
-      <c r="B50" s="82">
+      <c r="B50" s="47">
         <v>23.5</v>
       </c>
-      <c r="C50" s="40">
+      <c r="C50" s="48">
         <v>1500</v>
       </c>
-      <c r="D50" s="40">
+      <c r="D50" s="48">
         <v>1350</v>
       </c>
-      <c r="E50" s="37">
+      <c r="E50" s="49">
         <v>0.51041666666666663</v>
       </c>
-      <c r="F50" s="82">
+      <c r="F50" s="47">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="G50" s="37" t="s">
+      <c r="G50" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H50" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="I50" s="37" t="s">
+      <c r="H50" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J50" s="37" t="s">
+      <c r="J50" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="K50" s="66" t="s">
+      <c r="K50" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="L50" s="38" t="s">
+      <c r="L50" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="M50" s="38" t="s">
+      <c r="M50" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="N50" s="38" t="s">
+      <c r="N50" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O50" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="O50" s="38"/>
-    </row>
-    <row r="51" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="39">
+      <c r="P50" s="51"/>
+    </row>
+    <row r="51" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="46">
         <v>45536</v>
       </c>
-      <c r="B51" s="82">
+      <c r="B51" s="47">
         <v>20</v>
       </c>
-      <c r="C51" s="40">
+      <c r="C51" s="48">
         <v>1250</v>
       </c>
-      <c r="D51" s="40">
+      <c r="D51" s="48">
         <v>1200</v>
       </c>
-      <c r="E51" s="37">
+      <c r="E51" s="49">
         <v>0.35069444444444442</v>
       </c>
-      <c r="F51" s="82">
+      <c r="F51" s="47">
         <f t="shared" si="1"/>
         <v>36.5</v>
       </c>
-      <c r="G51" s="37" t="s">
+      <c r="G51" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H51" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="I51" s="37" t="s">
+      <c r="H51" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I51" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J51" s="37" t="s">
+      <c r="J51" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="K51" s="66" t="s">
+      <c r="K51" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L51" s="38" t="s">
+      <c r="L51" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="M51" s="38" t="s">
+      <c r="M51" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="N51" s="38" t="s">
+      <c r="N51" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O51" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="O51" s="38"/>
-    </row>
-    <row r="52" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="39">
+      <c r="P51" s="51"/>
+    </row>
+    <row r="52" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="46">
         <v>45537</v>
       </c>
-      <c r="B52" s="82">
+      <c r="B52" s="47">
         <v>6.5</v>
       </c>
-      <c r="C52" s="40">
+      <c r="C52" s="48">
         <v>0</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="48">
         <v>250</v>
       </c>
-      <c r="E52" s="37">
+      <c r="E52" s="49">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F52" s="82">
+      <c r="F52" s="47">
         <f t="shared" si="1"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="G52" s="37" t="s">
+      <c r="G52" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H52" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="I52" s="37" t="s">
+      <c r="H52" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J52" s="37" t="s">
+      <c r="J52" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="K52" s="66" t="s">
+      <c r="K52" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="L52" s="38" t="s">
+      <c r="L52" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="M52" s="38" t="s">
+      <c r="M52" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="N52" s="38" t="s">
+      <c r="N52" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O52" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="O52" s="38"/>
-    </row>
-    <row r="53" spans="1:15" s="45" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="42">
+      <c r="P52" s="51"/>
+    </row>
+    <row r="53" spans="1:16" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="43">
         <v>45540</v>
       </c>
-      <c r="B53" s="83">
+      <c r="B53" s="44">
         <v>65.5</v>
       </c>
-      <c r="C53" s="43">
+      <c r="C53" s="45">
         <v>1850</v>
       </c>
-      <c r="D53" s="43">
+      <c r="D53" s="45">
         <v>1700</v>
       </c>
-      <c r="E53" s="44">
+      <c r="E53" s="25">
         <v>0.59375</v>
       </c>
-      <c r="F53" s="83">
+      <c r="F53" s="44">
         <f t="shared" si="1"/>
         <v>89.666666666666671</v>
       </c>
-      <c r="G53" s="44" t="s">
+      <c r="G53" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="H53" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="I53" s="44" t="s">
+      <c r="H53" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I53" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="J53" s="44" t="s">
+      <c r="J53" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="K53" s="44" t="s">
+      <c r="K53" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="L53" s="41" t="s">
+      <c r="L53" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M53" s="41" t="s">
+      <c r="M53" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="N53" s="41" t="s">
+      <c r="N53" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O53" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O53" s="41" t="s">
+      <c r="P53" s="18" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="42">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="20">
         <v>45542</v>
       </c>
-      <c r="B54" s="76">
+      <c r="B54" s="37">
         <v>18.5</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="38">
         <v>513</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="38">
         <v>513</v>
       </c>
-      <c r="E54" s="46">
+      <c r="E54" s="23">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F54" s="76">
+      <c r="F54" s="37">
         <f t="shared" si="1"/>
         <v>25.34</v>
       </c>
-      <c r="G54" s="44" t="s">
+      <c r="G54" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="H54" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="I54" s="44" t="s">
+      <c r="H54" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I54" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="K54" s="61" t="s">
+      <c r="K54" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="L54" s="10" t="s">
+      <c r="L54" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="M54" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="N54" s="10" t="s">
+      <c r="N54" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O54" s="19" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="47">
+      <c r="P54" s="19"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="15">
         <v>45556</v>
       </c>
-      <c r="B55" s="84">
+      <c r="B55" s="35">
         <v>35.5</v>
       </c>
-      <c r="C55" s="48">
+      <c r="C55" s="16">
         <v>1770</v>
       </c>
-      <c r="D55" s="48">
+      <c r="D55" s="16">
         <v>680</v>
       </c>
-      <c r="E55" s="49">
+      <c r="E55" s="17">
         <v>0.4375</v>
       </c>
-      <c r="F55" s="84">
+      <c r="F55" s="35">
         <f t="shared" si="1"/>
         <v>55.466666666666669</v>
       </c>
-      <c r="G55" s="50" t="s">
+      <c r="G55" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="I55" s="50" t="s">
+      <c r="H55" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I55" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="J55" s="49" t="s">
+      <c r="J55" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="K55" s="50" t="s">
+      <c r="K55" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="L55" s="51" t="s">
+      <c r="L55" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M55" s="51" t="s">
+      <c r="M55" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="N55" s="51" t="s">
+      <c r="N55" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O55" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O55" s="51"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="47">
+      <c r="P55" s="18"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="15">
         <v>45557</v>
       </c>
-      <c r="B56" s="84">
+      <c r="B56" s="35">
         <v>30.1</v>
       </c>
-      <c r="C56" s="48">
+      <c r="C56" s="16">
         <v>390</v>
       </c>
-      <c r="D56" s="48">
+      <c r="D56" s="16">
         <v>1140</v>
       </c>
-      <c r="E56" s="50">
+      <c r="E56" s="25">
         <v>0.30208333333333331</v>
       </c>
-      <c r="F56" s="84">
+      <c r="F56" s="35">
         <f t="shared" si="1"/>
         <v>37.799999999999997</v>
       </c>
-      <c r="G56" s="50" t="s">
+      <c r="G56" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="H56" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="I56" s="50" t="s">
+      <c r="H56" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I56" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="J56" s="49" t="s">
+      <c r="J56" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="K56" s="50" t="s">
+      <c r="K56" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="L56" s="51" t="s">
+      <c r="L56" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="M56" s="51" t="s">
+      <c r="M56" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="N56" s="51" t="s">
+      <c r="N56" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O56" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O56" s="51"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="52">
+      <c r="P56" s="18"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="46">
         <v>45562</v>
       </c>
-      <c r="B57" s="85">
+      <c r="B57" s="47">
         <v>23.35</v>
       </c>
-      <c r="C57" s="53">
+      <c r="C57" s="48">
         <v>2520</v>
       </c>
-      <c r="D57" s="53">
+      <c r="D57" s="48">
         <v>1760</v>
       </c>
-      <c r="E57" s="54">
+      <c r="E57" s="49">
         <v>0.44791666666666669</v>
       </c>
-      <c r="F57" s="85">
+      <c r="F57" s="47">
         <f t="shared" si="1"/>
         <v>54.416666666666664</v>
       </c>
-      <c r="G57" s="55" t="s">
+      <c r="G57" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="H57" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="I57" s="54" t="s">
+      <c r="H57" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J57" s="54" t="s">
+      <c r="J57" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="K57" s="55" t="s">
+      <c r="K57" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="L57" s="56" t="s">
+      <c r="L57" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="M57" s="56" t="s">
+      <c r="M57" s="51" t="s">
         <v>368</v>
       </c>
-      <c r="N57" s="56" t="s">
+      <c r="N57" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O57" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="O57" s="56"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="52">
+      <c r="P57" s="51"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="46">
         <v>45563</v>
       </c>
-      <c r="B58" s="85">
+      <c r="B58" s="47">
         <v>27</v>
       </c>
-      <c r="C58" s="53">
+      <c r="C58" s="48">
         <v>1200</v>
       </c>
-      <c r="D58" s="53">
+      <c r="D58" s="48">
         <v>1960</v>
       </c>
-      <c r="E58" s="54">
+      <c r="E58" s="49">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F58" s="85">
+      <c r="F58" s="47">
         <f t="shared" si="1"/>
         <v>45.533333333333331</v>
       </c>
-      <c r="G58" s="55" t="s">
+      <c r="G58" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="H58" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" s="54" t="s">
+      <c r="H58" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J58" s="54" t="s">
+      <c r="J58" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="K58" s="55" t="s">
+      <c r="K58" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="L58" s="56" t="s">
+      <c r="L58" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="M58" s="56" t="s">
+      <c r="M58" s="51" t="s">
         <v>368</v>
       </c>
-      <c r="N58" s="56" t="s">
+      <c r="N58" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O58" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="O58" s="56"/>
-    </row>
-    <row r="59" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="57">
+      <c r="P58" s="51"/>
+    </row>
+    <row r="59" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
         <v>45597</v>
       </c>
-      <c r="B59" s="86">
+      <c r="B59" s="35">
         <v>24.8</v>
       </c>
-      <c r="C59" s="58">
+      <c r="C59" s="16">
         <v>860</v>
       </c>
-      <c r="D59" s="58">
+      <c r="D59" s="16">
         <v>550</v>
       </c>
-      <c r="E59" s="59">
+      <c r="E59" s="17">
         <v>0.22916666666666666</v>
       </c>
-      <c r="F59" s="86">
+      <c r="F59" s="35">
         <f t="shared" si="1"/>
         <v>35.233333333333334</v>
       </c>
-      <c r="G59" s="59" t="s">
+      <c r="G59" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H59" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I59" s="59" t="s">
+      <c r="H59" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I59" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J59" s="59" t="s">
+      <c r="J59" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K59" s="67" t="s">
+      <c r="K59" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="L59" s="60" t="s">
+      <c r="L59" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="M59" s="60" t="s">
+      <c r="M59" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N59" s="60" t="s">
+      <c r="N59" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O59" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O59" s="60"/>
-    </row>
-    <row r="60" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="57">
+      <c r="P59" s="18"/>
+    </row>
+    <row r="60" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="15">
         <v>45598</v>
       </c>
-      <c r="B60" s="86">
+      <c r="B60" s="35">
         <v>42.1</v>
       </c>
-      <c r="C60" s="58">
+      <c r="C60" s="16">
         <v>940</v>
       </c>
-      <c r="D60" s="58">
+      <c r="D60" s="16">
         <v>830</v>
       </c>
-      <c r="E60" s="59">
+      <c r="E60" s="17">
         <v>0.4375</v>
       </c>
-      <c r="F60" s="86">
+      <c r="F60" s="35">
         <f t="shared" si="1"/>
         <v>54.266666666666666</v>
       </c>
-      <c r="G60" s="59" t="s">
+      <c r="G60" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H60" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I60" s="59" t="s">
+      <c r="H60" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I60" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J60" s="59" t="s">
+      <c r="J60" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K60" s="67" t="s">
+      <c r="K60" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="L60" s="60" t="s">
+      <c r="L60" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="M60" s="60" t="s">
+      <c r="M60" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N60" s="60" t="s">
+      <c r="N60" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O60" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O60" s="60"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" s="57">
+      <c r="P60" s="18"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="15">
         <v>45599</v>
       </c>
-      <c r="B61" s="86">
+      <c r="B61" s="35">
         <v>48.9</v>
       </c>
-      <c r="C61" s="58">
+      <c r="C61" s="16">
         <v>1210</v>
       </c>
-      <c r="D61" s="58">
+      <c r="D61" s="16">
         <v>1160</v>
       </c>
-      <c r="E61" s="59">
+      <c r="E61" s="17">
         <v>0.46875</v>
       </c>
-      <c r="F61" s="86">
+      <c r="F61" s="35">
         <f t="shared" si="1"/>
         <v>64.86666666666666</v>
       </c>
-      <c r="G61" s="59" t="s">
+      <c r="G61" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H61" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I61" s="59" t="s">
+      <c r="H61" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I61" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J61" s="59" t="s">
+      <c r="J61" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K61" s="67" t="s">
+      <c r="K61" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="L61" s="60" t="s">
+      <c r="L61" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="M61" s="60" t="s">
+      <c r="M61" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N61" s="60" t="s">
+      <c r="N61" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O61" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O61" s="60"/>
-    </row>
-    <row r="62" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="57">
+      <c r="P61" s="18"/>
+    </row>
+    <row r="62" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="15">
         <v>45600</v>
       </c>
-      <c r="B62" s="86">
+      <c r="B62" s="35">
         <v>44.3</v>
       </c>
-      <c r="C62" s="58">
+      <c r="C62" s="16">
         <v>1520</v>
       </c>
-      <c r="D62" s="58">
+      <c r="D62" s="16">
         <v>1130</v>
       </c>
-      <c r="E62" s="59">
+      <c r="E62" s="17">
         <v>0.46527777777777773</v>
       </c>
-      <c r="F62" s="86">
+      <c r="F62" s="35">
         <f t="shared" si="1"/>
         <v>63.266666666666666</v>
       </c>
-      <c r="G62" s="59" t="s">
+      <c r="G62" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H62" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I62" s="59" t="s">
+      <c r="H62" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I62" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J62" s="59" t="s">
+      <c r="J62" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K62" s="67" t="s">
+      <c r="K62" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="L62" s="60" t="s">
+      <c r="L62" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="M62" s="60" t="s">
+      <c r="M62" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N62" s="60" t="s">
+      <c r="N62" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O62" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O62" s="60"/>
-    </row>
-    <row r="63" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="57">
+      <c r="P62" s="18"/>
+    </row>
+    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="15">
         <v>45601</v>
       </c>
-      <c r="B63" s="86">
+      <c r="B63" s="35">
         <v>46.9</v>
       </c>
-      <c r="C63" s="58">
+      <c r="C63" s="16">
         <v>1010</v>
       </c>
-      <c r="D63" s="58">
+      <c r="D63" s="16">
         <v>1780</v>
       </c>
-      <c r="E63" s="59">
+      <c r="E63" s="17">
         <v>0.49305555555555558</v>
       </c>
-      <c r="F63" s="86">
+      <c r="F63" s="35">
         <f t="shared" si="1"/>
         <v>62.933333333333337</v>
       </c>
-      <c r="G63" s="59" t="s">
+      <c r="G63" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H63" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I63" s="59" t="s">
+      <c r="H63" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J63" s="59" t="s">
+      <c r="J63" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K63" s="67" t="s">
+      <c r="K63" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="L63" s="60" t="s">
+      <c r="L63" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="M63" s="60" t="s">
+      <c r="M63" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N63" s="60" t="s">
+      <c r="N63" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O63" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O63" s="60"/>
-    </row>
-    <row r="64" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="57">
+      <c r="P63" s="18"/>
+    </row>
+    <row r="64" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="15">
         <v>45602</v>
       </c>
-      <c r="B64" s="86">
+      <c r="B64" s="35">
         <v>47.1</v>
       </c>
-      <c r="C64" s="58">
+      <c r="C64" s="16">
         <v>1220</v>
       </c>
-      <c r="D64" s="58">
+      <c r="D64" s="16">
         <v>1670</v>
       </c>
-      <c r="E64" s="59">
+      <c r="E64" s="17">
         <v>0.47569444444444442</v>
       </c>
-      <c r="F64" s="86">
+      <c r="F64" s="35">
         <f t="shared" si="1"/>
         <v>64.86666666666666</v>
       </c>
-      <c r="G64" s="59" t="s">
+      <c r="G64" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H64" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I64" s="59" t="s">
+      <c r="H64" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I64" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J64" s="59" t="s">
+      <c r="J64" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K64" s="67" t="s">
+      <c r="K64" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="L64" s="60" t="s">
+      <c r="L64" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="M64" s="60" t="s">
+      <c r="M64" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N64" s="60" t="s">
+      <c r="N64" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O64" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O64" s="60" t="s">
+      <c r="P64" s="18" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" s="57">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="15">
         <v>45603</v>
       </c>
-      <c r="B65" s="86">
+      <c r="B65" s="35">
         <v>23.5</v>
       </c>
-      <c r="C65" s="58">
+      <c r="C65" s="16">
         <v>750</v>
       </c>
-      <c r="D65" s="58">
+      <c r="D65" s="16">
         <v>870</v>
       </c>
-      <c r="E65" s="59">
+      <c r="E65" s="17">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F65" s="86">
+      <c r="F65" s="35">
         <f t="shared" si="1"/>
         <v>33.9</v>
       </c>
-      <c r="G65" s="59" t="s">
+      <c r="G65" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H65" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="I65" s="59" t="s">
+      <c r="H65" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I65" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="J65" s="59" t="s">
+      <c r="J65" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K65" s="67" t="s">
+      <c r="K65" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="L65" s="60" t="s">
+      <c r="L65" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="M65" s="60" t="s">
+      <c r="M65" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="N65" s="60" t="s">
+      <c r="N65" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O65" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O65" s="60"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+      <c r="P65" s="18"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="36">
         <v>45641</v>
       </c>
-      <c r="B66" s="76">
+      <c r="B66" s="37">
         <v>9.4</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="38">
         <v>840</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="38">
         <v>840</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="23">
         <v>0.19444444444444445</v>
       </c>
-      <c r="F66" s="76">
+      <c r="F66" s="37">
         <f t="shared" ref="F66:F86" si="2">B66+C66/100+D66/300</f>
         <v>20.6</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I66" s="3" t="s">
+      <c r="H66" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I66" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="K66" s="61" t="s">
+      <c r="K66" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="L66" s="10" t="s">
+      <c r="L66" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="N66" s="10" t="s">
+      <c r="M66" s="19"/>
+      <c r="N66" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O66" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="O66" s="10" t="s">
+      <c r="P66" s="19" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="15">
         <v>45660</v>
       </c>
-      <c r="B67" s="76">
+      <c r="B67" s="35">
         <v>21</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="16">
         <v>800</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="16">
         <v>800</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="17">
         <v>0.26041666666666669</v>
       </c>
-      <c r="F67" s="76">
+      <c r="F67" s="35">
         <f t="shared" si="2"/>
         <v>31.666666666666668</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I67" s="3" t="s">
+      <c r="H67" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I67" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="K67" s="61" t="s">
+      <c r="K67" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="L67" s="10" t="s">
+      <c r="L67" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="M67" s="10" t="s">
+      <c r="M67" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="N67" s="10" t="s">
+      <c r="N67" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O67" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="O67" s="10" t="s">
+      <c r="P67" s="18" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
+    <row r="68" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="36">
         <v>45675</v>
       </c>
-      <c r="B68" s="76">
+      <c r="B68" s="37">
         <v>27.2</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="38">
         <v>1980</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="38">
         <v>1980</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="23">
         <v>0.35416666666666669</v>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="37">
         <f t="shared" si="2"/>
         <v>53.6</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I68" s="3" t="s">
+      <c r="H68" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I68" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="K68" s="61" t="s">
+      <c r="K68" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="L68" s="10" t="s">
+      <c r="L68" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="M68" s="10" t="s">
+      <c r="M68" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="N68" s="10" t="s">
+      <c r="N68" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O68" s="19" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="16">
+      <c r="P68" s="19"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="15">
         <v>45689</v>
       </c>
-      <c r="B69" s="78">
+      <c r="B69" s="35">
         <v>5.3</v>
       </c>
-      <c r="C69" s="17">
+      <c r="C69" s="16">
         <v>730</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D69" s="16">
         <v>20</v>
       </c>
-      <c r="E69" s="18">
+      <c r="E69" s="17">
         <v>6.25E-2</v>
       </c>
-      <c r="F69" s="78">
+      <c r="F69" s="35">
         <f t="shared" si="2"/>
         <v>12.666666666666666</v>
       </c>
-      <c r="G69" s="18" t="s">
+      <c r="G69" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H69" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I69" s="18" t="s">
+      <c r="H69" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I69" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J69" s="18" t="s">
+      <c r="J69" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="K69" s="62" t="s">
+      <c r="K69" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="L69" s="19" t="s">
+      <c r="L69" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="M69" s="19" t="s">
+      <c r="M69" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="N69" s="19" t="s">
+      <c r="N69" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O69" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O69" s="19" t="s">
+      <c r="P69" s="18" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="15">
         <v>45689</v>
       </c>
-      <c r="B70" s="78">
+      <c r="B70" s="35">
         <v>19.899999999999999</v>
       </c>
-      <c r="C70" s="17">
+      <c r="C70" s="16">
         <v>790</v>
       </c>
-      <c r="D70" s="17">
+      <c r="D70" s="16">
         <v>1500</v>
       </c>
-      <c r="E70" s="18">
+      <c r="E70" s="17">
         <v>0.25</v>
       </c>
-      <c r="F70" s="78">
+      <c r="F70" s="35">
         <f t="shared" si="2"/>
         <v>32.799999999999997</v>
       </c>
-      <c r="G70" s="18" t="s">
+      <c r="G70" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H70" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I70" s="18" t="s">
+      <c r="H70" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I70" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J70" s="18" t="s">
+      <c r="J70" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="K70" s="62" t="s">
+      <c r="K70" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="L70" s="19" t="s">
+      <c r="L70" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="M70" s="19" t="s">
+      <c r="M70" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="N70" s="19" t="s">
+      <c r="N70" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O70" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O70" s="19"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
+      <c r="P70" s="18"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="36">
         <v>45697</v>
       </c>
-      <c r="B71" s="76">
+      <c r="B71" s="37">
         <v>24.3</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="38">
         <v>1380</v>
       </c>
-      <c r="D71" s="9">
+      <c r="D71" s="38">
         <v>1380</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="23">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F71" s="76">
+      <c r="F71" s="37">
         <f t="shared" si="2"/>
         <v>42.7</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I71" s="3" t="s">
+      <c r="H71" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I71" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="K71" s="61" t="s">
+      <c r="K71" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="L71" s="10" t="s">
+      <c r="L71" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="M71" s="10" t="s">
+      <c r="M71" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="N71" s="10" t="s">
+      <c r="N71" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O71" s="19" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="90">
+      <c r="P71" s="19"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="15">
         <v>45703</v>
       </c>
-      <c r="B72" s="91">
+      <c r="B72" s="35">
         <v>7</v>
       </c>
-      <c r="C72" s="92">
+      <c r="C72" s="16">
         <v>600</v>
       </c>
-      <c r="D72" s="92">
+      <c r="D72" s="16">
         <v>300</v>
       </c>
-      <c r="E72" s="93">
+      <c r="E72" s="17">
         <v>0.29166666666666669</v>
       </c>
-      <c r="F72" s="91">
+      <c r="F72" s="35">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="G72" s="93" t="s">
+      <c r="G72" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H72" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="I72" s="93" t="s">
+      <c r="H72" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J72" s="93" t="s">
+      <c r="J72" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K72" s="94" t="s">
+      <c r="K72" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="L72" s="95" t="s">
+      <c r="L72" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="M72" s="95" t="s">
+      <c r="M72" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="N72" s="95" t="s">
+      <c r="N72" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O72" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="O72" s="95" t="s">
+      <c r="P72" s="18" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="90">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="15">
         <v>45704</v>
       </c>
-      <c r="B73" s="91">
+      <c r="B73" s="35">
         <v>7</v>
       </c>
-      <c r="C73" s="92">
+      <c r="C73" s="16">
         <v>400</v>
       </c>
-      <c r="D73" s="92">
+      <c r="D73" s="16">
         <v>700</v>
       </c>
-      <c r="E73" s="93">
+      <c r="E73" s="17">
         <v>0.20833333333333334</v>
       </c>
-      <c r="F73" s="91">
+      <c r="F73" s="35">
         <f t="shared" si="2"/>
         <v>13.333333333333334</v>
       </c>
-      <c r="G73" s="93" t="s">
+      <c r="G73" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H73" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="I73" s="93" t="s">
+      <c r="H73" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I73" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J73" s="93" t="s">
+      <c r="J73" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K73" s="94" t="s">
+      <c r="K73" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="L73" s="95" t="s">
+      <c r="L73" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="M73" s="95" t="s">
+      <c r="M73" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="N73" s="95" t="s">
+      <c r="N73" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="O73" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="O73" s="95"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="99">
+      <c r="P73" s="18"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="46">
         <v>45715</v>
       </c>
-      <c r="B74" s="100">
+      <c r="B74" s="47">
         <v>21.1</v>
       </c>
-      <c r="C74" s="101">
+      <c r="C74" s="48">
         <v>590</v>
       </c>
-      <c r="D74" s="101">
+      <c r="D74" s="48">
         <v>360</v>
       </c>
-      <c r="E74" s="102">
+      <c r="E74" s="49">
         <v>0.19444444444444445</v>
       </c>
-      <c r="F74" s="100">
+      <c r="F74" s="47">
         <f t="shared" si="2"/>
         <v>28.2</v>
       </c>
-      <c r="G74" s="102" t="s">
+      <c r="G74" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H74" s="102" t="s">
-        <v>43</v>
-      </c>
-      <c r="I74" s="102" t="s">
+      <c r="H74" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="J74" s="102" t="s">
+      <c r="J74" s="49" t="s">
         <v>369</v>
       </c>
-      <c r="K74" s="103" t="s">
+      <c r="K74" s="50" t="s">
         <v>370</v>
       </c>
-      <c r="L74" s="104" t="s">
+      <c r="L74" s="51" t="s">
         <v>372</v>
       </c>
-      <c r="M74" s="104" t="s">
+      <c r="M74" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="N74" s="104" t="s">
+      <c r="N74" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O74" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O74" s="104"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="99">
+      <c r="P74" s="51"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="46">
         <v>45716</v>
       </c>
-      <c r="B75" s="100">
+      <c r="B75" s="47">
         <v>35</v>
       </c>
-      <c r="C75" s="101">
+      <c r="C75" s="48">
         <v>1280</v>
       </c>
-      <c r="D75" s="101">
+      <c r="D75" s="48">
         <v>1290</v>
       </c>
-      <c r="E75" s="102">
+      <c r="E75" s="49">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F75" s="100">
+      <c r="F75" s="47">
         <f t="shared" si="2"/>
         <v>52.099999999999994</v>
       </c>
-      <c r="G75" s="102" t="s">
+      <c r="G75" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="H75" s="102" t="s">
-        <v>43</v>
-      </c>
-      <c r="I75" s="102" t="s">
+      <c r="H75" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I75" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="J75" s="102" t="s">
+      <c r="J75" s="49" t="s">
         <v>369</v>
       </c>
-      <c r="K75" s="103" t="s">
+      <c r="K75" s="50" t="s">
         <v>371</v>
       </c>
-      <c r="L75" s="104" t="s">
+      <c r="L75" s="51" t="s">
         <v>375</v>
       </c>
-      <c r="M75" s="104" t="s">
+      <c r="M75" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="N75" s="104" t="s">
+      <c r="N75" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O75" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="O75" s="104"/>
-    </row>
-    <row r="76" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+      <c r="P75" s="51"/>
+    </row>
+    <row r="76" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="15">
         <v>45718</v>
       </c>
-      <c r="B76" s="76">
+      <c r="B76" s="35">
         <v>21.4</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="16">
         <v>1260</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="16">
         <v>1260</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="17">
         <v>0.34027777777777773</v>
       </c>
-      <c r="F76" s="88">
+      <c r="F76" s="35">
         <f t="shared" si="2"/>
         <v>38.200000000000003</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I76" s="3" t="s">
+      <c r="H76" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I76" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="K76" s="61" t="s">
+      <c r="K76" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="L76" s="10" t="s">
+      <c r="L76" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="M76" s="10" t="s">
+      <c r="M76" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="N76" s="10" t="s">
+      <c r="N76" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O76" s="18" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
+      <c r="P76" s="18"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="36">
         <v>45732</v>
       </c>
-      <c r="B77" s="76">
+      <c r="B77" s="37">
         <v>15.9</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="38">
         <v>520</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="38">
         <v>520</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="23">
         <v>0.16666666666666666</v>
       </c>
-      <c r="F77" s="88">
+      <c r="F77" s="37">
         <f t="shared" si="2"/>
         <v>22.833333333333336</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I77" s="3" t="s">
+      <c r="H77" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I77" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="K77" s="61" t="s">
+      <c r="K77" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="L77" s="10" t="s">
+      <c r="L77" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="M77" s="10" t="s">
+      <c r="M77" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="N77" s="10" t="s">
+      <c r="N77" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="O77" s="19" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
+      <c r="P77" s="19"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="15">
         <v>45746</v>
       </c>
-      <c r="B78" s="76">
+      <c r="B78" s="35">
         <v>23.4</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="16">
         <v>1290</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="16">
         <v>1290</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78" s="17">
         <v>0.3125</v>
       </c>
-      <c r="F78" s="88">
+      <c r="F78" s="35">
         <f t="shared" si="2"/>
         <v>40.599999999999994</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I78" s="3" t="s">
+      <c r="H78" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I78" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J78" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="K78" s="61" t="s">
+      <c r="K78" s="25" t="s">
         <v>392</v>
       </c>
-      <c r="L78" s="10" t="s">
+      <c r="L78" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="N78" s="10" t="s">
+      <c r="M78" s="18"/>
+      <c r="N78" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="O78" s="18" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="106">
+      <c r="P78" s="18"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="46">
         <v>45767</v>
       </c>
-      <c r="B79" s="107">
+      <c r="B79" s="47">
         <v>16.7</v>
       </c>
-      <c r="C79" s="108">
+      <c r="C79" s="48">
         <v>1140</v>
       </c>
-      <c r="D79" s="108">
+      <c r="D79" s="48">
         <v>180</v>
       </c>
-      <c r="E79" s="109">
+      <c r="E79" s="49">
         <v>0.22916666666666666</v>
       </c>
-      <c r="F79" s="107">
+      <c r="F79" s="47">
         <f t="shared" si="2"/>
         <v>28.700000000000003</v>
       </c>
-      <c r="G79" s="109" t="s">
+      <c r="G79" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H79" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="I79" s="109" t="s">
+      <c r="H79" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="J79" s="109" t="s">
+      <c r="J79" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="K79" s="110" t="s">
+      <c r="K79" s="50" t="s">
         <v>403</v>
       </c>
-      <c r="L79" s="111" t="s">
+      <c r="L79" s="51" t="s">
         <v>405</v>
       </c>
-      <c r="M79" s="111" t="s">
+      <c r="M79" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="N79" s="111" t="s">
+      <c r="N79" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O79" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="O79" s="111" t="s">
+      <c r="P79" s="51" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A80" s="106">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="46">
         <v>45768</v>
       </c>
-      <c r="B80" s="107">
+      <c r="B80" s="47">
         <v>22.5</v>
       </c>
-      <c r="C80" s="108">
+      <c r="C80" s="48">
         <v>60</v>
       </c>
-      <c r="D80" s="108">
+      <c r="D80" s="48">
         <v>1230</v>
       </c>
-      <c r="E80" s="109">
+      <c r="E80" s="49">
         <v>0.2986111111111111</v>
       </c>
-      <c r="F80" s="107">
+      <c r="F80" s="47">
         <f t="shared" si="2"/>
         <v>27.200000000000003</v>
       </c>
-      <c r="G80" s="109" t="s">
+      <c r="G80" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H80" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="I80" s="109" t="s">
+      <c r="H80" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I80" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="J80" s="109" t="s">
+      <c r="J80" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="K80" s="110" t="s">
+      <c r="K80" s="50" t="s">
         <v>404</v>
       </c>
-      <c r="L80" s="111" t="s">
+      <c r="L80" s="51" t="s">
         <v>406</v>
       </c>
-      <c r="M80" s="111" t="s">
+      <c r="M80" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="N80" s="111" t="s">
+      <c r="N80" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O80" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="O80" s="111"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A81" s="112">
+      <c r="P80" s="51"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="15">
         <v>45773</v>
       </c>
-      <c r="B81" s="113">
+      <c r="B81" s="35">
         <v>27.4</v>
       </c>
-      <c r="C81" s="114">
+      <c r="C81" s="16">
         <v>2270</v>
       </c>
-      <c r="D81" s="114">
+      <c r="D81" s="16">
         <v>920</v>
       </c>
-      <c r="E81" s="115">
+      <c r="E81" s="17">
         <v>0.35416666666666669</v>
       </c>
-      <c r="F81" s="113">
+      <c r="F81" s="35">
         <f t="shared" si="2"/>
         <v>53.166666666666664</v>
       </c>
-      <c r="G81" s="115" t="s">
+      <c r="G81" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H81" s="115" t="s">
-        <v>43</v>
-      </c>
-      <c r="I81" s="115" t="s">
+      <c r="H81" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J81" s="115" t="s">
+      <c r="J81" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="K81" s="116" t="s">
+      <c r="K81" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="L81" s="117" t="s">
+      <c r="L81" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="M81" s="117" t="s">
+      <c r="M81" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="N81" s="117" t="s">
+      <c r="N81" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O81" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O81" s="117"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A82" s="112">
+      <c r="P81" s="18"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="15">
         <v>45774</v>
       </c>
-      <c r="B82" s="113">
+      <c r="B82" s="35">
         <v>29.1</v>
       </c>
-      <c r="C82" s="114">
+      <c r="C82" s="16">
         <v>1160</v>
       </c>
-      <c r="D82" s="114">
+      <c r="D82" s="16">
         <v>2490</v>
       </c>
-      <c r="E82" s="115">
+      <c r="E82" s="17">
         <v>0.33333333333333331</v>
       </c>
-      <c r="F82" s="113">
+      <c r="F82" s="35">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="G82" s="115" t="s">
+      <c r="G82" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="H82" s="115" t="s">
-        <v>43</v>
-      </c>
-      <c r="I82" s="115" t="s">
+      <c r="H82" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I82" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J82" s="115" t="s">
+      <c r="J82" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="K82" s="116" t="s">
+      <c r="K82" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="L82" s="117" t="s">
+      <c r="L82" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="M82" s="117" t="s">
+      <c r="M82" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="N82" s="117" t="s">
+      <c r="N82" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="O82" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="O82" s="117"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A83" s="24">
+      <c r="P82" s="18"/>
+    </row>
+    <row r="83" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="46">
         <v>45778</v>
       </c>
-      <c r="B83" s="80">
+      <c r="B83" s="47">
         <v>20</v>
       </c>
-      <c r="C83" s="25">
+      <c r="C83" s="48">
         <v>1850</v>
       </c>
-      <c r="D83" s="25">
+      <c r="D83" s="48">
         <v>590</v>
       </c>
-      <c r="E83" s="26" t="s">
+      <c r="E83" s="49" t="s">
         <v>434</v>
       </c>
-      <c r="F83" s="80">
+      <c r="F83" s="47">
         <f t="shared" si="2"/>
         <v>40.466666666666669</v>
       </c>
-      <c r="G83" s="26" t="s">
+      <c r="G83" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H83" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I83" s="26" t="s">
+      <c r="H83" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J83" s="26" t="s">
+      <c r="J83" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="K83" s="64" t="s">
+      <c r="K83" s="50" t="s">
         <v>426</v>
       </c>
-      <c r="L83" s="27" t="s">
+      <c r="L83" s="51" t="s">
         <v>430</v>
       </c>
-      <c r="M83" s="27" t="s">
+      <c r="M83" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="N83" s="27" t="s">
+      <c r="N83" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O83" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="O83" s="27"/>
-    </row>
-    <row r="84" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A84" s="24">
+      <c r="P83" s="51"/>
+    </row>
+    <row r="84" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A84" s="46">
         <v>45779</v>
       </c>
-      <c r="B84" s="80">
+      <c r="B84" s="47">
         <v>22.713200000000001</v>
       </c>
-      <c r="C84" s="25">
+      <c r="C84" s="48">
         <v>1320</v>
       </c>
-      <c r="D84" s="25">
+      <c r="D84" s="48">
         <v>1170</v>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="49">
         <v>0.42708333333333331</v>
       </c>
-      <c r="F84" s="80">
+      <c r="F84" s="47">
         <f t="shared" si="2"/>
         <v>39.813200000000002</v>
       </c>
-      <c r="G84" s="26" t="s">
+      <c r="G84" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H84" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I84" s="26" t="s">
+      <c r="H84" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I84" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J84" s="26" t="s">
+      <c r="J84" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="K84" s="64" t="s">
+      <c r="K84" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="L84" s="27" t="s">
+      <c r="L84" s="51" t="s">
         <v>431</v>
       </c>
-      <c r="M84" s="27" t="s">
+      <c r="M84" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="N84" s="27" t="s">
+      <c r="N84" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O84" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="O84" s="27"/>
-    </row>
-    <row r="85" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="24">
+      <c r="P84" s="51"/>
+    </row>
+    <row r="85" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="46">
         <v>45780</v>
       </c>
-      <c r="B85" s="80">
+      <c r="B85" s="47">
         <v>25.6</v>
       </c>
-      <c r="C85" s="25">
+      <c r="C85" s="48">
         <v>850</v>
       </c>
-      <c r="D85" s="25">
+      <c r="D85" s="48">
         <v>1580</v>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="49">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F85" s="80">
+      <c r="F85" s="47">
         <f t="shared" si="2"/>
         <v>39.366666666666667</v>
       </c>
-      <c r="G85" s="26" t="s">
+      <c r="G85" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H85" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I85" s="26" t="s">
+      <c r="H85" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J85" s="26" t="s">
+      <c r="J85" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="K85" s="64" t="s">
+      <c r="K85" s="50" t="s">
         <v>429</v>
       </c>
-      <c r="L85" s="27" t="s">
+      <c r="L85" s="51" t="s">
         <v>432</v>
       </c>
-      <c r="M85" s="27" t="s">
+      <c r="M85" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="N85" s="27" t="s">
+      <c r="N85" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O85" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="O85" s="27" t="s">
+      <c r="P85" s="51" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A86" s="24">
+    <row r="86" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A86" s="46">
         <v>45781</v>
       </c>
-      <c r="B86" s="80">
+      <c r="B86" s="47">
         <v>18.399999999999999</v>
       </c>
-      <c r="C86" s="25">
+      <c r="C86" s="48">
         <v>490</v>
       </c>
-      <c r="D86" s="25">
+      <c r="D86" s="48">
         <v>1120</v>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="49">
         <v>0.25</v>
       </c>
-      <c r="F86" s="80">
+      <c r="F86" s="47">
         <f t="shared" si="2"/>
         <v>27.033333333333331</v>
       </c>
-      <c r="G86" s="26" t="s">
+      <c r="G86" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="H86" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="I86" s="26" t="s">
+      <c r="H86" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I86" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J86" s="26" t="s">
+      <c r="J86" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="K86" s="64" t="s">
+      <c r="K86" s="50" t="s">
         <v>428</v>
       </c>
-      <c r="L86" s="27" t="s">
+      <c r="L86" s="51" t="s">
         <v>433</v>
       </c>
-      <c r="M86" s="27" t="s">
+      <c r="M86" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="N86" s="27" t="s">
+      <c r="N86" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="O86" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="O86" s="27"/>
+      <c r="P86" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O70">
-    <sortState ref="A2:O82">
+  <autoFilter ref="A1:P70" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P82">
       <sortCondition ref="A1:A65"/>
     </sortState>
   </autoFilter>
@@ -6112,489 +6291,489 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <f t="shared" ref="D2:D30" si="0">IF(C2="Z", 1, IF(C2="S", 2, IF(C2="A", 3, IF(C2="B", 4, IF(C2="C", 5, IF(C2="D", 6, 7))))))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="15"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D32" s="15"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34" s="15"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D36" s="15"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D37" s="15"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D32" s="14"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="14"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="14"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="14"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D18">
-    <sortState ref="A2:D28">
+  <autoFilter ref="A1:D18" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D28">
       <sortCondition ref="D1:D18"/>
     </sortState>
   </autoFilter>
@@ -6621,609 +6800,609 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>3172</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>3045</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2789</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2685</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>2663</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>2662</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>2525</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>2459</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>2432</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>2338</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>2284</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>2276</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>2222</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>2219</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>2175</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>2156</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>2080</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>2051</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>2049</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>2037</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>1992</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>1976</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>1966</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>1959</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>1930</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>1920</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>1901</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>1850</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>1844</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>1838</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>1821</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>1811</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>1776</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>1771</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>1699</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>1635</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="4">
         <v>1597</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>1570</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>1566</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <v>1548</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <v>1534</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="4">
         <v>1534</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <v>1435</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <v>1432</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="4">
         <v>1430</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="4">
         <v>1421</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="4">
         <v>1413</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="4">
         <v>1390</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="4">
         <v>1379</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="4">
         <v>1365</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="4">
         <v>1364</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="4">
         <v>1357</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="4">
         <v>1342</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="4">
         <v>1304</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="4">
         <v>1297</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="4">
         <v>1291</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="4">
         <v>1213</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="4">
         <v>1213</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="4">
         <v>1089</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="4">
         <v>1050</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="4">
         <v>1049</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="4">
         <v>1011</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="4">
         <v>805</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="4">
         <v>718</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="4">
         <v>656</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="4">
         <v>645</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="4">
         <v>634</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="4">
         <v>626</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70" s="4">
         <v>609</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="4">
         <v>566</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="4">
         <v>563</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="4">
         <v>433</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="4">
         <v>1761</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5">
-    <sortState ref="A2:B73">
+  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B73">
       <sortCondition descending="1" ref="B1:B5"/>
     </sortState>
   </autoFilter>
@@ -7232,588 +7411,588 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="4"/>
+    <col min="1" max="1" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="11.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="12" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:6" s="11" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="F1" s="39" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="42" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>0</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="42" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>220</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>14000</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>2900</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
         <v>1</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>125</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>9000</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>2500</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>1</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="41" t="s">
         <v>395</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>45</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>2500</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>2300</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
         <v>1</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>1</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
         <v>1</v>
       </c>
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>35</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>2000</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>1</v>
       </c>
-      <c r="B16" s="98" t="s">
+      <c r="B16" s="41" t="s">
         <v>380</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>1</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="41" t="s">
         <v>335</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="41" t="s">
         <v>396</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="41" t="s">
         <v>397</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
         <v>2</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>2</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
         <v>2</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
         <v>2</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
         <v>2</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
         <v>2</v>
       </c>
-      <c r="B26" s="98" t="s">
+      <c r="B26" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>85</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="6">
         <v>5000</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="7">
         <v>2000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
         <v>2</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
         <v>2</v>
       </c>
-      <c r="B28" s="98" t="s">
+      <c r="B28" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="7">
         <v>2000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
         <v>2</v>
       </c>
-      <c r="B29" s="98" t="s">
+      <c r="B29" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>90</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="6">
         <v>5000</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="7">
         <v>2300</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
         <v>2</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
         <v>2</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
         <v>2</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
         <v>2</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
         <v>2</v>
       </c>
-      <c r="B34" s="98" t="s">
+      <c r="B34" s="41" t="s">
         <v>398</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
         <v>3</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
         <v>3</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
         <v>3</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
         <v>3</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
         <v>3</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
         <v>3</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
         <v>3</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
         <v>3</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
         <v>3</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
         <v>3</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
         <v>3</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
         <v>3</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>113</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41">
-    <sortState ref="A2:F50">
+  <autoFilter ref="A1:F41" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F50">
       <sortCondition ref="A1:A44"/>
     </sortState>
   </autoFilter>

--- a/data/Randonnée.xlsx
+++ b/data/Randonnée.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B32DC83-56ED-4128-BAC3-EFF6AF223D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A60E84-451F-4491-AE9B-0024578B9116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Randonnées!$A$1:$P$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sommets!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wish List'!$A$1:$F$41</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sommets!$B$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sommets!$B$2:$B$74</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sommets!$B$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sommets!$B$2:$B$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1752,6 +1756,681 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{521C195A-0735-4029-B209-826922D9CC40}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:v>Altitude (m)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r" underflow="500" overflow="3000">
+              <cx:binSize val="500"/>
+            </cx:binning>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Graphique 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{172EA161-DA22-4ECC-8F00-14559CC27EFB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3876675" y="862012"/>
+              <a:ext cx="5476875" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
+La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -7407,6 +8086,7 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
